--- a/MISUO - Amr Mohamed Basyouni Shaaban.xlsx
+++ b/MISUO - Amr Mohamed Basyouni Shaaban.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AmrShaabanHPVictus\Desktop\data_analysis\projects\misuo_dashboard_dataanalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F3C4354-8170-4598-A468-9CE4B58B0367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C32B65A-3036-471D-AA1F-5877915E505C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1703,7 +1703,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1911,15 +1911,14 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
@@ -2797,6 +2796,15 @@
       </border>
     </dxf>
     <dxf>
+      <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2881,15 +2889,6 @@
         <top/>
         <bottom/>
       </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="13" formatCode="0%"/>
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
@@ -3651,8 +3650,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.37373447069116361"/>
-          <c:y val="0.12113429571303587"/>
+          <c:x val="0.45706780402449693"/>
+          <c:y val="0.10090191702172231"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -4672,6 +4671,16 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.70318591426071742"/>
+          <c:y val="0.2614140691091299"/>
+          <c:w val="0.27459186351706039"/>
+          <c:h val="0.44872508188542548"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -5941,6 +5950,14 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.47557813159790358"/>
+          <c:y val="5.9724677272483796E-2"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -6137,7 +6154,17 @@
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.783385909568875E-2"/>
+          <c:y val="0.27306634262605978"/>
+          <c:w val="0.66400266607052671"/>
+          <c:h val="0.13499986389084648"/>
+        </c:manualLayout>
+      </c:layout>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -6382,6 +6409,16 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.77967038426190405"/>
+          <c:y val="0.27028871391076115"/>
+          <c:w val="0.18878387441317471"/>
+          <c:h val="0.11989876265466817"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -6515,6 +6552,14 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.33882320309330421"/>
+          <c:y val="0.15093028312289367"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -6713,7 +6758,17 @@
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.0758836533445935E-3"/>
+          <c:y val="0.4228416344406653"/>
+          <c:w val="0.66505926146024197"/>
+          <c:h val="0.26240626171728532"/>
+        </c:manualLayout>
+      </c:layout>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -6919,6 +6974,16 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.76463979068862453"/>
+          <c:y val="0.50874360401919461"/>
+          <c:w val="0.18819021443074332"/>
+          <c:h val="9.537401574803149E-2"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -7236,7 +7301,17 @@
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.3140096618357488E-2"/>
+          <c:y val="0.41209802579025445"/>
+          <c:w val="0.69127201491117962"/>
+          <c:h val="8.5603103959831103E-2"/>
+        </c:manualLayout>
+      </c:layout>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -7803,7 +7878,17 @@
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.46779543418099928"/>
+          <c:y val="0.24166284432892488"/>
+          <c:w val="0.20390647921275701"/>
+          <c:h val="0.45898440486201358"/>
+        </c:manualLayout>
+      </c:layout>
       <c:barChart>
         <c:barDir val="bar"/>
         <c:grouping val="clustered"/>
@@ -8050,8 +8135,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="0.66666666666666674"/>
-          <c:y val="0.19023147987558825"/>
+          <c:x val="2.7190332326284018E-2"/>
+          <c:y val="0.17405014907117192"/>
           <c:w val="0.30312185297079558"/>
           <c:h val="0.33223548047683465"/>
         </c:manualLayout>
@@ -8185,6 +8270,14 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.3513725490196079"/>
+          <c:y val="7.5805439718617293E-2"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -8383,7 +8476,17 @@
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.11013933920024703"/>
+          <c:y val="0.25086340125552414"/>
+          <c:w val="0.60794917680744454"/>
+          <c:h val="0.17892008705750256"/>
+        </c:manualLayout>
+      </c:layout>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -8625,6 +8728,16 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.79457503473830482"/>
+          <c:y val="0.26991830842569992"/>
+          <c:w val="0.17601320055581288"/>
+          <c:h val="0.12394604690413132"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -8754,6 +8867,14 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.4994408168491134"/>
+          <c:y val="4.4533367755260109E-2"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -8952,7 +9073,17 @@
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="4.7843287881697713E-2"/>
+          <c:y val="0.25896870473158068"/>
+          <c:w val="0.73708885474681518"/>
+          <c:h val="0.12961791661288241"/>
+        </c:manualLayout>
+      </c:layout>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -9212,6 +9343,16 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.82964758978298447"/>
+          <c:y val="0.21417322834645666"/>
+          <c:w val="0.14596216631457654"/>
+          <c:h val="8.0260100684135791E-2"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -9341,6 +9482,14 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.35945790080738177"/>
+          <c:y val="9.9478925428439086E-2"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -9539,7 +9688,17 @@
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.70680693139164052"/>
+          <c:y val="0.23636545120139285"/>
+          <c:w val="0.10356334490446757"/>
+          <c:h val="0.70557070383869858"/>
+        </c:manualLayout>
+      </c:layout>
       <c:barChart>
         <c:barDir val="bar"/>
         <c:grouping val="clustered"/>
@@ -24063,8 +24222,8 @@
       <xdr:row>23</xdr:row>
       <xdr:rowOff>20955</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="12" name="المدينة">
@@ -24087,7 +24246,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -24141,8 +24300,8 @@
       <xdr:row>34</xdr:row>
       <xdr:rowOff>36195</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="13" name="Column1">
@@ -24165,7 +24324,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -24219,8 +24378,8 @@
       <xdr:row>21</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="14" name="الحالة1">
@@ -24243,7 +24402,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -24291,23 +24450,23 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>274320</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>167640</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>53340</xdr:rowOff>
+      <xdr:rowOff>99060</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>167640</xdr:colOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>525780</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>129540</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="Rectangle: Rounded Corners 1">
+        <xdr:cNvPr id="3" name="Rectangle: Rounded Corners 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3BDF71C3-B6B0-E529-7464-4A1378A3B24D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F70B891-B77E-E83B-28CA-D33D893760EE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -24315,8 +24474,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3322320" y="53340"/>
-          <a:ext cx="7208520" cy="1303020"/>
+          <a:off x="167640" y="99060"/>
+          <a:ext cx="13769340" cy="1310640"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -24348,81 +24507,38 @@
         <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
         <a:lstStyle/>
         <a:p>
-          <a:pPr algn="ctr"/>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
           <a:r>
-            <a:rPr lang="en-GB" sz="5400" b="1">
+            <a:rPr lang="en-GB" sz="3600" b="1">
               <a:solidFill>
-                <a:srgbClr val="F2F2F2"/>
+                <a:schemeClr val="lt1"/>
               </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
             </a:rPr>
             <a:t>Sales Dashboard</a:t>
           </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>121920</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>434340</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>53340</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="Rectangle: Rounded Corners 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2F70B891-B77E-E83B-28CA-D33D893760EE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="121920" y="114300"/>
-          <a:ext cx="1531620" cy="9997440"/>
-        </a:xfrm>
-        <a:prstGeom prst="roundRect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="1E3151"/>
-        </a:solidFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr lang="en-GB" sz="1100"/>
+          <a:endParaRPr lang="en-GB" sz="3600">
+            <a:effectLst/>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -24431,15 +24547,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>365761</xdr:colOff>
+      <xdr:colOff>350521</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>121921</xdr:rowOff>
+      <xdr:rowOff>38101</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>121921</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:colOff>106681</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>99061</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -24468,7 +24584,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="365761" y="304801"/>
+          <a:off x="350521" y="220981"/>
           <a:ext cx="975360" cy="975360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -24480,16 +24596,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>167640</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>350520</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>60960</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>167640</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -24504,8 +24620,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3314700" y="1630680"/>
-          <a:ext cx="3131820" cy="807720"/>
+          <a:off x="8991600" y="533400"/>
+          <a:ext cx="1539240" cy="487680"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -24539,21 +24655,18 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="ar-EG" sz="1400" b="1">
+            <a:rPr lang="en-US" sz="1400" b="1">
               <a:solidFill>
                 <a:srgbClr val="F2F2F2"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>إجمالى</a:t>
+            <a:t>Total Sales</a:t>
           </a:r>
-          <a:r>
-            <a:rPr lang="ar-EG" sz="1400" b="1" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="F2F2F2"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> المبيعات</a:t>
-          </a:r>
+          <a:endParaRPr lang="ar-EG" sz="1400" b="1" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="F2F2F2"/>
+            </a:solidFill>
+          </a:endParaRPr>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -24561,10 +24674,10 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>60960</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>144780</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>541020</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1242060" cy="281940"/>
     <xdr:sp macro="" textlink="'Pivot tables'!G12">
@@ -24580,7 +24693,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4328160" y="1973580"/>
+          <a:off x="9075420" y="739140"/>
           <a:ext cx="1242060" cy="281940"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -24633,16 +24746,16 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>426720</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>137160</xdr:rowOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>198120</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>175260</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>45720</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>556260</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -24657,7 +24770,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7741920" y="1600200"/>
+          <a:off x="10561320" y="472440"/>
           <a:ext cx="2796540" cy="822960"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
@@ -24692,12 +24805,12 @@
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr lang="ar-EG" sz="1400" b="1">
+            <a:rPr lang="en-US" sz="1400" b="1">
               <a:solidFill>
                 <a:srgbClr val="F2F2F2"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>عدد الطلبات</a:t>
+            <a:t>Number of Requests</a:t>
           </a:r>
           <a:endParaRPr lang="ar-EG" sz="1400" b="1" baseline="0">
             <a:solidFill>
@@ -24711,10 +24824,10 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>99060</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>411480</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1120140" cy="264560"/>
     <xdr:sp macro="" textlink="'Pivot tables'!L12">
@@ -24730,7 +24843,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8610600" y="1927860"/>
+          <a:off x="11384280" y="815340"/>
           <a:ext cx="1120140" cy="264560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -24783,16 +24896,16 @@
   </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>144780</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>160020</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>312420</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>144780</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>464820</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -24807,8 +24920,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11590020" y="2705100"/>
-          <a:ext cx="2743200" cy="2743200"/>
+          <a:off x="9304020" y="3299460"/>
+          <a:ext cx="2743200" cy="1775460"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -24846,16 +24959,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>594360</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>548640</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>289560</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>99060</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -24870,8 +24983,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11567160" y="6987540"/>
-          <a:ext cx="2743200" cy="2743200"/>
+          <a:off x="2987040" y="3337560"/>
+          <a:ext cx="2537460" cy="1699260"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -24909,16 +25022,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>259080</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>167640</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>106680</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -24947,16 +25060,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>205740</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>68580</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>137160</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>53340</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>160020</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>594360</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -24985,16 +25098,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>99060</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>45720</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>510540</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>403860</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>137160</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>99060</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>121920</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -25009,8 +25122,78 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6804660" y="7543800"/>
-          <a:ext cx="4572000" cy="3200400"/>
+          <a:off x="12092940" y="1676400"/>
+          <a:ext cx="2026920" cy="3200400"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="1E3151"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="ar-EG" sz="1400" b="1" baseline="0">
+            <a:solidFill>
+              <a:srgbClr val="F2F2F2"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>91440</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="Rectangle: Rounded Corners 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC971AC8-0B4A-4CBF-AFF2-81D439406E84}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5577840" y="3345180"/>
+          <a:ext cx="3680460" cy="1706880"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -25056,22 +25239,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>106680</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>99060</xdr:rowOff>
+      <xdr:colOff>518160</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>129540</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>365760</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>144780</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="17" name="Rectangle: Rounded Corners 16">
+        <xdr:cNvPr id="18" name="Rectangle: Rounded Corners 17">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC971AC8-0B4A-4CBF-AFF2-81D439406E84}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44BCED26-9A5A-4E86-948A-48DA644F286C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -25079,8 +25262,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2545080" y="7597140"/>
-          <a:ext cx="3680460" cy="3124200"/>
+          <a:off x="2956560" y="1463040"/>
+          <a:ext cx="2895600" cy="1790700"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -25125,23 +25308,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>144780</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>68580</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>167640</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>53340</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>137160</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="18" name="Rectangle: Rounded Corners 17">
+        <xdr:cNvPr id="19" name="Rectangle: Rounded Corners 18">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44BCED26-9A5A-4E86-948A-48DA644F286C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F60FF8DE-F485-4FE4-BF6B-671E6D9A5BA9}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -25149,8 +25332,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7696200" y="2522220"/>
-          <a:ext cx="2895600" cy="1920240"/>
+          <a:off x="68580" y="1447800"/>
+          <a:ext cx="2827020" cy="1798320"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -25195,23 +25378,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>205740</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>137160</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>320040</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>160020</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>488063</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="19" name="Rectangle: Rounded Corners 18">
+        <xdr:cNvPr id="20" name="Rectangle: Rounded Corners 19">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F60FF8DE-F485-4FE4-BF6B-671E6D9A5BA9}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0CE54607-1AD8-4D0F-A59F-B398AC342578}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -25219,8 +25402,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3253740" y="2514600"/>
-          <a:ext cx="3162300" cy="1851660"/>
+          <a:off x="0" y="3291840"/>
+          <a:ext cx="2926463" cy="1752600"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -25265,23 +25448,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>525780</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>15240</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>518160</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>182879</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>106680</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>32982</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>350520</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>99060</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="20" name="Rectangle: Rounded Corners 19">
+        <xdr:cNvPr id="21" name="Rectangle: Rounded Corners 20">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0CE54607-1AD8-4D0F-A59F-B398AC342578}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0883AFB1-D609-4199-86D8-82231CA3EBC4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -25289,8 +25472,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1744980" y="4587240"/>
-          <a:ext cx="3238500" cy="2760942"/>
+          <a:off x="9052560" y="1463039"/>
+          <a:ext cx="2880360" cy="1744981"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -25335,23 +25518,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>175260</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>22859</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>411480</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>160021</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>25134</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>83820</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="21" name="Rectangle: Rounded Corners 20">
+        <xdr:cNvPr id="22" name="Rectangle: Rounded Corners 21">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0883AFB1-D609-4199-86D8-82231CA3EBC4}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DEC60C1A-1B4C-4D63-BD34-D13FE226F3F6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -25359,8 +25542,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5052060" y="4594859"/>
-          <a:ext cx="2880360" cy="2745475"/>
+          <a:off x="5897880" y="1440181"/>
+          <a:ext cx="3093720" cy="1752599"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst/>
@@ -25405,86 +25588,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>99060</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>129541</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>243840</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>205740</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>28205</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="22" name="Rectangle: Rounded Corners 21">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DEC60C1A-1B4C-4D63-BD34-D13FE226F3F6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8023860" y="4518661"/>
-          <a:ext cx="3154680" cy="2824744"/>
-        </a:xfrm>
-        <a:prstGeom prst="roundRect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="1E3151"/>
-        </a:solidFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:endParaRPr lang="ar-EG" sz="1400" b="1" baseline="0">
-            <a:solidFill>
-              <a:srgbClr val="F2F2F2"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>358140</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>335280</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>160816</xdr:rowOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -25513,16 +25626,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>396240</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>99060</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>45720</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -25551,16 +25664,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>502920</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>373380</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>83820</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>106680</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>274320</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>109220</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -25589,16 +25702,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>601980</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>53340</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>129540</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>137160</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>213360</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -25627,16 +25740,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>510540</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>83821</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>586740</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>30481</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>586740</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>124081</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>129540</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>175260</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -25665,16 +25778,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>388620</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>68580</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>373380</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>464820</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>449580</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>60960</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -25703,16 +25816,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>7620</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>137160</xdr:rowOff>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>594360</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>106680</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>502920</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>83820</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>30480</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -25741,15 +25854,15 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>205740</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>76201</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>335280</xdr:colOff>
-      <xdr:row>20</xdr:row>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>586740</xdr:colOff>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -25786,7 +25899,7 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="205740" y="2819401"/>
+              <a:off x="1676400" y="259081"/>
               <a:ext cx="1348740" cy="845819"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
@@ -25819,16 +25932,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>205740</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>396240</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>312420</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>121920</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>502920</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>53340</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
@@ -25864,86 +25977,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="205740" y="4099560"/>
+              <a:off x="3444240" y="190500"/>
               <a:ext cx="1325880" cy="1143000"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:prstClr val="white"/>
-            </a:solidFill>
-            <a:ln w="1">
-              <a:solidFill>
-                <a:prstClr val="green"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr lang="en-GB" sz="1100"/>
-                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
-If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
-              </a:r>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>182880</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>99061</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>274320</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>22860</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="36" name="Column1 1">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E5B527B6-B9CF-4CF9-B981-DDDBDB148844}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvGraphicFramePr/>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="0" y="0"/>
-            <a:ext cx="0" cy="0"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
-              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Column1 1"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="0" name=""/>
-            <xdr:cNvSpPr>
-              <a:spLocks noTextEdit="1"/>
-            </xdr:cNvSpPr>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="182880" y="5585461"/>
-              <a:ext cx="1310640" cy="1935479"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -29556,352 +29591,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{127F9CB2-2EE3-4282-A537-E4787544A1DC}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
-  <location ref="P8:Q15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="25">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="7">
-        <item x="1"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="5"/>
-  </rowFields>
-  <rowItems count="7">
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average of سعر البيع " fld="13" subtotal="average" baseField="4" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="37">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="5" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <chartFormats count="2">
-    <chartFormat chart="1" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7EC14D8C-D6EE-40CD-88B0-93D9FD818C12}" name="PivotTable12" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
-  <location ref="AY8:AZ11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="25">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" dataField="1" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Column3" fld="1" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="2">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{77F8C56E-BB2F-4D55-8594-818EA755D577}" name="PivotTable11" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
-  <location ref="AT8:AU18" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="25">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="11">
-        <item x="8"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="7"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="9"/>
-        <item x="2"/>
-        <item h="1" x="4"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="7">
-        <item h="1" x="4"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="10">
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Column1" fld="5" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="2">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="2" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{92DB980A-F19E-49E2-8901-B38900404D2B}" name="PivotTable10" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="AO8:AP12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="25">
@@ -30088,284 +29777,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{87181FC4-415C-467B-90FA-41AA1B856110}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="K8:K9" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="25">
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of أسم العميل" fld="0" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{324C3119-C2DC-4940-8ED6-98EE896D9AB4}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="F8:F9" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
-  <pivotFields count="25">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of سعر البيع " fld="13" baseField="0" baseItem="0" numFmtId="166"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="38">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{04A566D1-07E6-44FF-9618-E71648A4E8DD}" name="PivotTable9" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
-  <location ref="AJ8:AK12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="25">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="2"/>
-        <item m="1" x="3"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="21"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Column1" fld="5" subtotal="count" showDataAs="percentOfTotal" baseField="21" baseItem="0" numFmtId="9"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="39">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="8">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="21" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="2">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="21" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="3">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="21" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="9">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="21" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="10">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="21" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="11">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="21" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{824BE80A-DCA8-4BED-9EC5-1945884C3253}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A8:B15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="25">
@@ -30478,7 +29890,129 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{127F9CB2-2EE3-4282-A537-E4787544A1DC}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="P8:Q15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="25">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="7">
+        <item x="1"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of سعر البيع " fld="13" subtotal="average" baseField="4" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="26">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="5" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
+  <chartFormats count="2">
+    <chartFormat chart="1" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BEA5C7E8-1495-4E63-88A3-0CEBBAD7EF43}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="AE8:AF20" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="25">
@@ -30626,7 +30160,58 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{87181FC4-415C-467B-90FA-41AA1B856110}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="K8:K9" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="25">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of أسم العميل" fld="0" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1D36AB31-A780-402B-BE27-B58604B4923E}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="U8:V17" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="25">
@@ -30753,7 +30338,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3DFCF780-585B-4163-8AC6-31AD7200B7B5}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="Z8:AA20" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="25">
@@ -30907,6 +30492,456 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{324C3119-C2DC-4940-8ED6-98EE896D9AB4}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="F8:F9" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="25">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of سعر البيع " fld="13" baseField="0" baseItem="0" numFmtId="166"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="24">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7EC14D8C-D6EE-40CD-88B0-93D9FD818C12}" name="PivotTable12" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+  <location ref="AY8:AZ11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="25">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" dataField="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Column3" fld="1" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{04A566D1-07E6-44FF-9618-E71648A4E8DD}" name="PivotTable9" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="AJ8:AK12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="25">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item m="1" x="3"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="21"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Column1" fld="5" subtotal="count" showDataAs="percentOfTotal" baseField="21" baseItem="0" numFmtId="9"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="25">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="8">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="21" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="21" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="21" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="9">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="21" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="10">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="21" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="11">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="21" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{77F8C56E-BB2F-4D55-8594-818EA755D577}" name="PivotTable11" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="AT8:AU18" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="25">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="11">
+        <item x="8"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="7"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="9"/>
+        <item x="2"/>
+        <item h="1" x="4"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item h="1" x="4"/>
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="10">
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Column1" fld="5" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="2" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_المدينة" xr10:uid="{AA29A2A7-54EA-4FAF-8CA9-650351C1EA21}" sourceName="المدينة">
   <pivotTables>
@@ -30982,21 +31017,20 @@
 <file path=xl/slicers/slicer2.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
   <slicer name="المدينة 1" xr10:uid="{38E258BC-8397-4C2F-B000-533D86A5DBD5}" cache="Slicer_المدينة" caption="المدينة" rowHeight="234950"/>
-  <slicer name="Column1 1" xr10:uid="{2CD4CEAD-AE49-44BD-9BCB-10DBDA9DE804}" cache="Slicer_Column1" caption="Column1" rowHeight="234950"/>
-  <slicer name="الحالة1 1" xr10:uid="{8F68F08E-5FCD-4EC2-8197-F4D3EB0407DE}" cache="Slicer_الحالة1" caption="الحالة1" rowHeight="234950"/>
+  <slicer name="الحالة1 1" xr10:uid="{8F68F08E-5FCD-4EC2-8197-F4D3EB0407DE}" cache="Slicer_الحالة1" caption="الحالة1" startItem="1" rowHeight="234950"/>
 </slicers>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D2798A78-3521-436D-9BC5-851ED3CB5E63}" name="table1" displayName="table1" ref="A1:Y127" totalsRowShown="0" headerRowDxfId="36" headerRowBorderDxfId="35" tableBorderDxfId="34">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D2798A78-3521-436D-9BC5-851ED3CB5E63}" name="table1" displayName="table1" ref="A1:Y127" totalsRowShown="0" headerRowDxfId="39" headerRowBorderDxfId="38" tableBorderDxfId="37">
   <autoFilter ref="A1:Y127" xr:uid="{D2798A78-3521-436D-9BC5-851ED3CB5E63}"/>
   <tableColumns count="25">
     <tableColumn id="4" xr3:uid="{47BE3B96-D330-4BBC-A2D2-F81C95C9CDF8}" name="أسم العميل"/>
-    <tableColumn id="22" xr3:uid="{F15DAF27-78C1-4D92-9202-2C5CF008F705}" name="Column3" dataDxfId="33">
+    <tableColumn id="22" xr3:uid="{F15DAF27-78C1-4D92-9202-2C5CF008F705}" name="Column3" dataDxfId="36">
       <calculatedColumnFormula>IF(OR(table1[[#This Row],[أسم العميل]]="تاكى",table1[[#This Row],[أسم العميل]]="أوسكار راتن",table1[[#This Row],[أسم العميل]]="شيك هومز"),"شركات","أفراد")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{8A9922D2-A0CD-402D-B813-D91B1A5543A7}" name="العنوان"/>
-    <tableColumn id="1" xr3:uid="{AD1FFE34-51FD-4097-8C5F-4D6F46AC80A7}" name="المدينة" dataDxfId="32"/>
+    <tableColumn id="1" xr3:uid="{AD1FFE34-51FD-4097-8C5F-4D6F46AC80A7}" name="المدينة" dataDxfId="35"/>
     <tableColumn id="6" xr3:uid="{531866FB-239E-4CF3-9FE1-039571685D15}" name="منصة البيع "/>
     <tableColumn id="7" xr3:uid="{329594CA-08DA-45AC-A7F7-910A5361B134}" name="Column1"/>
     <tableColumn id="8" xr3:uid="{990A4B5E-F656-488D-9380-13FEF9368A58}" name="Column2"/>
@@ -31008,22 +31042,22 @@
     <tableColumn id="13" xr3:uid="{D1430ED2-4D5A-4B23-8A5C-34451686BB87}" name="المنتج"/>
     <tableColumn id="14" xr3:uid="{5C7E7829-EAB2-4268-9FAB-15FA3FD2CCF4}" name="سعر البيع "/>
     <tableColumn id="15" xr3:uid="{BACF5005-30BE-47C9-AAC1-9BDF38012149}" name="طريقه الدفع "/>
-    <tableColumn id="16" xr3:uid="{E2B28B8B-CFBC-439F-8D85-DC762E0967F1}" name="ميعاد الطلب" dataDxfId="31"/>
-    <tableColumn id="17" xr3:uid="{1A1B1E1B-A2CA-408E-8E56-91ED4C4CCBF5}" name="ميعاد التسليم" dataDxfId="30"/>
-    <tableColumn id="18" xr3:uid="{E1959E39-8CB9-4EDA-BBF2-E00B29924D1E}" name="تاريخ التسليم" dataDxfId="29"/>
-    <tableColumn id="2" xr3:uid="{5929C7DE-15D3-4F6B-BAA3-355C82794866}" name="عدد أيام التسليم الأصلى" dataDxfId="28">
+    <tableColumn id="16" xr3:uid="{E2B28B8B-CFBC-439F-8D85-DC762E0967F1}" name="ميعاد الطلب" dataDxfId="34"/>
+    <tableColumn id="17" xr3:uid="{1A1B1E1B-A2CA-408E-8E56-91ED4C4CCBF5}" name="ميعاد التسليم" dataDxfId="33"/>
+    <tableColumn id="18" xr3:uid="{E1959E39-8CB9-4EDA-BBF2-E00B29924D1E}" name="تاريخ التسليم" dataDxfId="32"/>
+    <tableColumn id="2" xr3:uid="{5929C7DE-15D3-4F6B-BAA3-355C82794866}" name="عدد أيام التسليم الأصلى" dataDxfId="31">
       <calculatedColumnFormula>IF(OR(ISBLANK(table1[[#This Row],[ميعاد الطلب]]),ISBLANK(table1[[#This Row],[ميعاد التسليم]])),0,table1[[#This Row],[ميعاد التسليم]]-table1[[#This Row],[ميعاد الطلب]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{2BEEC7D8-2A51-4F7A-9B83-7976B7B93352}" name="عدد أيام التسليم الفعلى" dataDxfId="27">
+    <tableColumn id="3" xr3:uid="{2BEEC7D8-2A51-4F7A-9B83-7976B7B93352}" name="عدد أيام التسليم الفعلى" dataDxfId="30">
       <calculatedColumnFormula>IF(OR(ISBLANK(table1[[#This Row],[تاريخ التسليم]]),ISBLANK(table1[[#This Row],[ميعاد الطلب]]),ISBLANK(table1[[#This Row],[ميعاد التسليم]])),0,table1[[#This Row],[تاريخ التسليم]]-table1[[#This Row],[ميعاد الطلب]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{FF4D0B8C-46CD-415E-BA7A-7DA012D5025D}" name="Column4" dataDxfId="26"/>
-    <tableColumn id="25" xr3:uid="{2CA249B4-2C38-4756-B217-A70D4BD8A8D0}" name="Column5" dataDxfId="25">
+    <tableColumn id="23" xr3:uid="{FF4D0B8C-46CD-415E-BA7A-7DA012D5025D}" name="Column4" dataDxfId="29"/>
+    <tableColumn id="25" xr3:uid="{2CA249B4-2C38-4756-B217-A70D4BD8A8D0}" name="Column5" dataDxfId="28">
       <calculatedColumnFormula array="1">_xlfn.IFS(OR(table1[[#This Row],[Column4]]=0,table1[[#This Row],[Column4]]="0"),"لا يوجد تاريخ", table1[[#This Row],[Column4]]&gt;0,"تم التسليم قبل الموعد",table1[[#This Row],[Column4]]&lt;0,"تم التسليم بعد الموعد")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="19" xr3:uid="{5F8B0FDB-1F35-4B52-9FA7-8035B2A836D7}" name="المسئول عن التسليم"/>
     <tableColumn id="20" xr3:uid="{064C9CE2-4190-4BB6-8764-5128D762D8E3}" name="الحالة"/>
-    <tableColumn id="26" xr3:uid="{8FF09841-496F-49DE-A608-039A5C21E43D}" name="الحالة1" dataDxfId="24">
+    <tableColumn id="26" xr3:uid="{8FF09841-496F-49DE-A608-039A5C21E43D}" name="الحالة1" dataDxfId="27">
       <calculatedColumnFormula>TRIM(table1[[#This Row],[الحالة]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -47592,256 +47626,256 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" x14ac:dyDescent="0.3">
-      <c r="A1" s="82" t="s">
+      <c r="A1" s="83" t="s">
         <v>371</v>
       </c>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="F1" s="82" t="s">
+      <c r="B1" s="83"/>
+      <c r="C1" s="83"/>
+      <c r="D1" s="83"/>
+      <c r="F1" s="83" t="s">
         <v>376</v>
       </c>
-      <c r="G1" s="82"/>
-      <c r="H1" s="82"/>
-      <c r="I1" s="82"/>
-      <c r="K1" s="82" t="s">
+      <c r="G1" s="83"/>
+      <c r="H1" s="83"/>
+      <c r="I1" s="83"/>
+      <c r="K1" s="83" t="s">
         <v>378</v>
       </c>
-      <c r="L1" s="82"/>
-      <c r="M1" s="82"/>
-      <c r="N1" s="82"/>
-      <c r="P1" s="82" t="s">
+      <c r="L1" s="83"/>
+      <c r="M1" s="83"/>
+      <c r="N1" s="83"/>
+      <c r="P1" s="83" t="s">
         <v>413</v>
       </c>
-      <c r="Q1" s="82"/>
-      <c r="R1" s="82"/>
-      <c r="S1" s="82"/>
-      <c r="U1" s="82" t="s">
+      <c r="Q1" s="83"/>
+      <c r="R1" s="83"/>
+      <c r="S1" s="83"/>
+      <c r="U1" s="83" t="s">
         <v>416</v>
       </c>
-      <c r="V1" s="82"/>
-      <c r="W1" s="82"/>
-      <c r="X1" s="82"/>
-      <c r="Z1" s="82" t="s">
+      <c r="V1" s="83"/>
+      <c r="W1" s="83"/>
+      <c r="X1" s="83"/>
+      <c r="Z1" s="83" t="s">
         <v>423</v>
       </c>
-      <c r="AA1" s="82"/>
-      <c r="AB1" s="82"/>
-      <c r="AC1" s="82"/>
-      <c r="AE1" s="82" t="s">
+      <c r="AA1" s="83"/>
+      <c r="AB1" s="83"/>
+      <c r="AC1" s="83"/>
+      <c r="AE1" s="83" t="s">
         <v>424</v>
       </c>
-      <c r="AF1" s="82"/>
-      <c r="AG1" s="82"/>
-      <c r="AH1" s="82"/>
-      <c r="AJ1" s="82" t="s">
+      <c r="AF1" s="83"/>
+      <c r="AG1" s="83"/>
+      <c r="AH1" s="83"/>
+      <c r="AJ1" s="83" t="s">
         <v>428</v>
       </c>
-      <c r="AK1" s="82"/>
-      <c r="AL1" s="82"/>
-      <c r="AM1" s="82"/>
-      <c r="AO1" s="82" t="s">
+      <c r="AK1" s="83"/>
+      <c r="AL1" s="83"/>
+      <c r="AM1" s="83"/>
+      <c r="AO1" s="83" t="s">
         <v>431</v>
       </c>
-      <c r="AP1" s="82"/>
-      <c r="AQ1" s="82"/>
-      <c r="AR1" s="82"/>
-      <c r="AT1" s="82" t="s">
+      <c r="AP1" s="83"/>
+      <c r="AQ1" s="83"/>
+      <c r="AR1" s="83"/>
+      <c r="AT1" s="83" t="s">
         <v>433</v>
       </c>
-      <c r="AU1" s="82"/>
-      <c r="AV1" s="82"/>
-      <c r="AW1" s="82"/>
-      <c r="AY1" s="81" t="s">
+      <c r="AU1" s="83"/>
+      <c r="AV1" s="83"/>
+      <c r="AW1" s="83"/>
+      <c r="AY1" s="84" t="s">
         <v>437</v>
       </c>
-      <c r="AZ1" s="81"/>
-      <c r="BA1" s="81"/>
-      <c r="BB1" s="81"/>
+      <c r="AZ1" s="84"/>
+      <c r="BA1" s="84"/>
+      <c r="BB1" s="84"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.3">
-      <c r="A2" s="82"/>
-      <c r="B2" s="82"/>
-      <c r="C2" s="82"/>
-      <c r="D2" s="82"/>
-      <c r="F2" s="82"/>
-      <c r="G2" s="82"/>
-      <c r="H2" s="82"/>
-      <c r="I2" s="82"/>
-      <c r="K2" s="82"/>
-      <c r="L2" s="82"/>
-      <c r="M2" s="82"/>
-      <c r="N2" s="82"/>
-      <c r="P2" s="82"/>
-      <c r="Q2" s="82"/>
-      <c r="R2" s="82"/>
-      <c r="S2" s="82"/>
-      <c r="U2" s="82"/>
-      <c r="V2" s="82"/>
-      <c r="W2" s="82"/>
-      <c r="X2" s="82"/>
-      <c r="Z2" s="82"/>
-      <c r="AA2" s="82"/>
-      <c r="AB2" s="82"/>
-      <c r="AC2" s="82"/>
-      <c r="AE2" s="82"/>
-      <c r="AF2" s="82"/>
-      <c r="AG2" s="82"/>
-      <c r="AH2" s="82"/>
-      <c r="AJ2" s="82"/>
-      <c r="AK2" s="82"/>
-      <c r="AL2" s="82"/>
-      <c r="AM2" s="82"/>
-      <c r="AO2" s="82"/>
-      <c r="AP2" s="82"/>
-      <c r="AQ2" s="82"/>
-      <c r="AR2" s="82"/>
-      <c r="AT2" s="82"/>
-      <c r="AU2" s="82"/>
-      <c r="AV2" s="82"/>
-      <c r="AW2" s="82"/>
-      <c r="AY2" s="81"/>
-      <c r="AZ2" s="81"/>
-      <c r="BA2" s="81"/>
-      <c r="BB2" s="81"/>
+      <c r="A2" s="83"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="83"/>
+      <c r="I2" s="83"/>
+      <c r="K2" s="83"/>
+      <c r="L2" s="83"/>
+      <c r="M2" s="83"/>
+      <c r="N2" s="83"/>
+      <c r="P2" s="83"/>
+      <c r="Q2" s="83"/>
+      <c r="R2" s="83"/>
+      <c r="S2" s="83"/>
+      <c r="U2" s="83"/>
+      <c r="V2" s="83"/>
+      <c r="W2" s="83"/>
+      <c r="X2" s="83"/>
+      <c r="Z2" s="83"/>
+      <c r="AA2" s="83"/>
+      <c r="AB2" s="83"/>
+      <c r="AC2" s="83"/>
+      <c r="AE2" s="83"/>
+      <c r="AF2" s="83"/>
+      <c r="AG2" s="83"/>
+      <c r="AH2" s="83"/>
+      <c r="AJ2" s="83"/>
+      <c r="AK2" s="83"/>
+      <c r="AL2" s="83"/>
+      <c r="AM2" s="83"/>
+      <c r="AO2" s="83"/>
+      <c r="AP2" s="83"/>
+      <c r="AQ2" s="83"/>
+      <c r="AR2" s="83"/>
+      <c r="AT2" s="83"/>
+      <c r="AU2" s="83"/>
+      <c r="AV2" s="83"/>
+      <c r="AW2" s="83"/>
+      <c r="AY2" s="84"/>
+      <c r="AZ2" s="84"/>
+      <c r="BA2" s="84"/>
+      <c r="BB2" s="84"/>
     </row>
     <row r="3" spans="1:54" x14ac:dyDescent="0.3">
-      <c r="A3" s="82"/>
-      <c r="B3" s="82"/>
-      <c r="C3" s="82"/>
-      <c r="D3" s="82"/>
-      <c r="F3" s="82"/>
-      <c r="G3" s="82"/>
-      <c r="H3" s="82"/>
-      <c r="I3" s="82"/>
-      <c r="K3" s="82"/>
-      <c r="L3" s="82"/>
-      <c r="M3" s="82"/>
-      <c r="N3" s="82"/>
-      <c r="P3" s="82"/>
-      <c r="Q3" s="82"/>
-      <c r="R3" s="82"/>
-      <c r="S3" s="82"/>
-      <c r="U3" s="82"/>
-      <c r="V3" s="82"/>
-      <c r="W3" s="82"/>
-      <c r="X3" s="82"/>
-      <c r="Z3" s="82"/>
-      <c r="AA3" s="82"/>
-      <c r="AB3" s="82"/>
-      <c r="AC3" s="82"/>
-      <c r="AE3" s="82"/>
-      <c r="AF3" s="82"/>
-      <c r="AG3" s="82"/>
-      <c r="AH3" s="82"/>
-      <c r="AJ3" s="82"/>
-      <c r="AK3" s="82"/>
-      <c r="AL3" s="82"/>
-      <c r="AM3" s="82"/>
-      <c r="AO3" s="82"/>
-      <c r="AP3" s="82"/>
-      <c r="AQ3" s="82"/>
-      <c r="AR3" s="82"/>
-      <c r="AT3" s="82"/>
-      <c r="AU3" s="82"/>
-      <c r="AV3" s="82"/>
-      <c r="AW3" s="82"/>
-      <c r="AY3" s="81"/>
-      <c r="AZ3" s="81"/>
-      <c r="BA3" s="81"/>
-      <c r="BB3" s="81"/>
+      <c r="A3" s="83"/>
+      <c r="B3" s="83"/>
+      <c r="C3" s="83"/>
+      <c r="D3" s="83"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="83"/>
+      <c r="I3" s="83"/>
+      <c r="K3" s="83"/>
+      <c r="L3" s="83"/>
+      <c r="M3" s="83"/>
+      <c r="N3" s="83"/>
+      <c r="P3" s="83"/>
+      <c r="Q3" s="83"/>
+      <c r="R3" s="83"/>
+      <c r="S3" s="83"/>
+      <c r="U3" s="83"/>
+      <c r="V3" s="83"/>
+      <c r="W3" s="83"/>
+      <c r="X3" s="83"/>
+      <c r="Z3" s="83"/>
+      <c r="AA3" s="83"/>
+      <c r="AB3" s="83"/>
+      <c r="AC3" s="83"/>
+      <c r="AE3" s="83"/>
+      <c r="AF3" s="83"/>
+      <c r="AG3" s="83"/>
+      <c r="AH3" s="83"/>
+      <c r="AJ3" s="83"/>
+      <c r="AK3" s="83"/>
+      <c r="AL3" s="83"/>
+      <c r="AM3" s="83"/>
+      <c r="AO3" s="83"/>
+      <c r="AP3" s="83"/>
+      <c r="AQ3" s="83"/>
+      <c r="AR3" s="83"/>
+      <c r="AT3" s="83"/>
+      <c r="AU3" s="83"/>
+      <c r="AV3" s="83"/>
+      <c r="AW3" s="83"/>
+      <c r="AY3" s="84"/>
+      <c r="AZ3" s="84"/>
+      <c r="BA3" s="84"/>
+      <c r="BB3" s="84"/>
     </row>
     <row r="4" spans="1:54" x14ac:dyDescent="0.3">
-      <c r="A4" s="82"/>
-      <c r="B4" s="82"/>
-      <c r="C4" s="82"/>
-      <c r="D4" s="82"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="82"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="K4" s="82"/>
-      <c r="L4" s="82"/>
-      <c r="M4" s="82"/>
-      <c r="N4" s="82"/>
-      <c r="P4" s="82"/>
-      <c r="Q4" s="82"/>
-      <c r="R4" s="82"/>
-      <c r="S4" s="82"/>
-      <c r="U4" s="82"/>
-      <c r="V4" s="82"/>
-      <c r="W4" s="82"/>
-      <c r="X4" s="82"/>
-      <c r="Z4" s="82"/>
-      <c r="AA4" s="82"/>
-      <c r="AB4" s="82"/>
-      <c r="AC4" s="82"/>
-      <c r="AE4" s="82"/>
-      <c r="AF4" s="82"/>
-      <c r="AG4" s="82"/>
-      <c r="AH4" s="82"/>
-      <c r="AJ4" s="82"/>
-      <c r="AK4" s="82"/>
-      <c r="AL4" s="82"/>
-      <c r="AM4" s="82"/>
-      <c r="AO4" s="82"/>
-      <c r="AP4" s="82"/>
-      <c r="AQ4" s="82"/>
-      <c r="AR4" s="82"/>
-      <c r="AT4" s="82"/>
-      <c r="AU4" s="82"/>
-      <c r="AV4" s="82"/>
-      <c r="AW4" s="82"/>
-      <c r="AY4" s="81"/>
-      <c r="AZ4" s="81"/>
-      <c r="BA4" s="81"/>
-      <c r="BB4" s="81"/>
+      <c r="A4" s="83"/>
+      <c r="B4" s="83"/>
+      <c r="C4" s="83"/>
+      <c r="D4" s="83"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="83"/>
+      <c r="H4" s="83"/>
+      <c r="I4" s="83"/>
+      <c r="K4" s="83"/>
+      <c r="L4" s="83"/>
+      <c r="M4" s="83"/>
+      <c r="N4" s="83"/>
+      <c r="P4" s="83"/>
+      <c r="Q4" s="83"/>
+      <c r="R4" s="83"/>
+      <c r="S4" s="83"/>
+      <c r="U4" s="83"/>
+      <c r="V4" s="83"/>
+      <c r="W4" s="83"/>
+      <c r="X4" s="83"/>
+      <c r="Z4" s="83"/>
+      <c r="AA4" s="83"/>
+      <c r="AB4" s="83"/>
+      <c r="AC4" s="83"/>
+      <c r="AE4" s="83"/>
+      <c r="AF4" s="83"/>
+      <c r="AG4" s="83"/>
+      <c r="AH4" s="83"/>
+      <c r="AJ4" s="83"/>
+      <c r="AK4" s="83"/>
+      <c r="AL4" s="83"/>
+      <c r="AM4" s="83"/>
+      <c r="AO4" s="83"/>
+      <c r="AP4" s="83"/>
+      <c r="AQ4" s="83"/>
+      <c r="AR4" s="83"/>
+      <c r="AT4" s="83"/>
+      <c r="AU4" s="83"/>
+      <c r="AV4" s="83"/>
+      <c r="AW4" s="83"/>
+      <c r="AY4" s="84"/>
+      <c r="AZ4" s="84"/>
+      <c r="BA4" s="84"/>
+      <c r="BB4" s="84"/>
     </row>
     <row r="5" spans="1:54" x14ac:dyDescent="0.3">
-      <c r="A5" s="82"/>
-      <c r="B5" s="82"/>
-      <c r="C5" s="82"/>
-      <c r="D5" s="82"/>
-      <c r="F5" s="82"/>
-      <c r="G5" s="82"/>
-      <c r="H5" s="82"/>
-      <c r="I5" s="82"/>
-      <c r="K5" s="82"/>
-      <c r="L5" s="82"/>
-      <c r="M5" s="82"/>
-      <c r="N5" s="82"/>
-      <c r="P5" s="82"/>
-      <c r="Q5" s="82"/>
-      <c r="R5" s="82"/>
-      <c r="S5" s="82"/>
-      <c r="U5" s="82"/>
-      <c r="V5" s="82"/>
-      <c r="W5" s="82"/>
-      <c r="X5" s="82"/>
-      <c r="Z5" s="82"/>
-      <c r="AA5" s="82"/>
-      <c r="AB5" s="82"/>
-      <c r="AC5" s="82"/>
-      <c r="AE5" s="82"/>
-      <c r="AF5" s="82"/>
-      <c r="AG5" s="82"/>
-      <c r="AH5" s="82"/>
-      <c r="AJ5" s="82"/>
-      <c r="AK5" s="82"/>
-      <c r="AL5" s="82"/>
-      <c r="AM5" s="82"/>
-      <c r="AO5" s="82"/>
-      <c r="AP5" s="82"/>
-      <c r="AQ5" s="82"/>
-      <c r="AR5" s="82"/>
-      <c r="AT5" s="82"/>
-      <c r="AU5" s="82"/>
-      <c r="AV5" s="82"/>
-      <c r="AW5" s="82"/>
-      <c r="AY5" s="81"/>
-      <c r="AZ5" s="81"/>
-      <c r="BA5" s="81"/>
-      <c r="BB5" s="81"/>
+      <c r="A5" s="83"/>
+      <c r="B5" s="83"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="83"/>
+      <c r="F5" s="83"/>
+      <c r="G5" s="83"/>
+      <c r="H5" s="83"/>
+      <c r="I5" s="83"/>
+      <c r="K5" s="83"/>
+      <c r="L5" s="83"/>
+      <c r="M5" s="83"/>
+      <c r="N5" s="83"/>
+      <c r="P5" s="83"/>
+      <c r="Q5" s="83"/>
+      <c r="R5" s="83"/>
+      <c r="S5" s="83"/>
+      <c r="U5" s="83"/>
+      <c r="V5" s="83"/>
+      <c r="W5" s="83"/>
+      <c r="X5" s="83"/>
+      <c r="Z5" s="83"/>
+      <c r="AA5" s="83"/>
+      <c r="AB5" s="83"/>
+      <c r="AC5" s="83"/>
+      <c r="AE5" s="83"/>
+      <c r="AF5" s="83"/>
+      <c r="AG5" s="83"/>
+      <c r="AH5" s="83"/>
+      <c r="AJ5" s="83"/>
+      <c r="AK5" s="83"/>
+      <c r="AL5" s="83"/>
+      <c r="AM5" s="83"/>
+      <c r="AO5" s="83"/>
+      <c r="AP5" s="83"/>
+      <c r="AQ5" s="83"/>
+      <c r="AR5" s="83"/>
+      <c r="AT5" s="83"/>
+      <c r="AU5" s="83"/>
+      <c r="AV5" s="83"/>
+      <c r="AW5" s="83"/>
+      <c r="AY5" s="84"/>
+      <c r="AZ5" s="84"/>
+      <c r="BA5" s="84"/>
+      <c r="BB5" s="84"/>
     </row>
     <row r="8" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A8" s="72" t="s">
@@ -47933,13 +47967,13 @@
       <c r="Z9" s="73" t="s">
         <v>334</v>
       </c>
-      <c r="AA9" s="85">
+      <c r="AA9">
         <v>46</v>
       </c>
       <c r="AE9" s="73" t="s">
         <v>170</v>
       </c>
-      <c r="AF9" s="85">
+      <c r="AF9">
         <v>7</v>
       </c>
       <c r="AJ9" s="73" t="s">
@@ -47989,13 +48023,13 @@
       <c r="Z10" s="73" t="s">
         <v>333</v>
       </c>
-      <c r="AA10" s="85">
+      <c r="AA10">
         <v>37</v>
       </c>
       <c r="AE10" s="73" t="s">
         <v>334</v>
       </c>
-      <c r="AF10" s="85">
+      <c r="AF10">
         <v>6</v>
       </c>
       <c r="AJ10" s="73" t="s">
@@ -48045,13 +48079,13 @@
       <c r="Z11" s="73" t="s">
         <v>170</v>
       </c>
-      <c r="AA11" s="85">
+      <c r="AA11">
         <v>6</v>
       </c>
       <c r="AE11" s="73" t="s">
         <v>300</v>
       </c>
-      <c r="AF11" s="85">
+      <c r="AF11">
         <v>3</v>
       </c>
       <c r="AJ11" s="73" t="s">
@@ -48086,7 +48120,7 @@
       <c r="B12">
         <v>1</v>
       </c>
-      <c r="G12" s="84">
+      <c r="G12" s="82">
         <f>GETPIVOTDATA("سعر البيع ",$F$8)</f>
         <v>1292885.81544</v>
       </c>
@@ -48109,13 +48143,13 @@
       <c r="Z12" s="73" t="s">
         <v>168</v>
       </c>
-      <c r="AA12" s="85">
+      <c r="AA12">
         <v>3</v>
       </c>
       <c r="AE12" s="73" t="s">
         <v>420</v>
       </c>
-      <c r="AF12" s="85">
+      <c r="AF12">
         <v>3</v>
       </c>
       <c r="AJ12" s="73" t="s">
@@ -48159,13 +48193,13 @@
       <c r="Z13" s="73" t="s">
         <v>245</v>
       </c>
-      <c r="AA13" s="85">
+      <c r="AA13">
         <v>3</v>
       </c>
       <c r="AE13" s="73" t="s">
         <v>257</v>
       </c>
-      <c r="AF13" s="85">
+      <c r="AF13">
         <v>3</v>
       </c>
       <c r="AT13" s="73" t="s">
@@ -48197,13 +48231,13 @@
       <c r="Z14" s="73" t="s">
         <v>232</v>
       </c>
-      <c r="AA14" s="85">
+      <c r="AA14">
         <v>2</v>
       </c>
       <c r="AE14" s="73" t="s">
         <v>333</v>
       </c>
-      <c r="AF14" s="85">
+      <c r="AF14">
         <v>2</v>
       </c>
       <c r="AT14" s="73" t="s">
@@ -48235,13 +48269,13 @@
       <c r="Z15" s="73" t="s">
         <v>174</v>
       </c>
-      <c r="AA15" s="85">
+      <c r="AA15">
         <v>2</v>
       </c>
       <c r="AE15" s="73" t="s">
         <v>216</v>
       </c>
-      <c r="AF15" s="85">
+      <c r="AF15">
         <v>2</v>
       </c>
       <c r="AT15" s="73" t="s">
@@ -48261,13 +48295,13 @@
       <c r="Z16" s="73" t="s">
         <v>417</v>
       </c>
-      <c r="AA16" s="85">
+      <c r="AA16">
         <v>2</v>
       </c>
       <c r="AE16" s="73" t="s">
         <v>243</v>
       </c>
-      <c r="AF16" s="85">
+      <c r="AF16">
         <v>1</v>
       </c>
       <c r="AT16" s="73" t="s">
@@ -48297,13 +48331,13 @@
       <c r="Z17" s="73" t="s">
         <v>171</v>
       </c>
-      <c r="AA17" s="85">
+      <c r="AA17">
         <v>2</v>
       </c>
       <c r="AE17" s="73" t="s">
         <v>316</v>
       </c>
-      <c r="AF17" s="85">
+      <c r="AF17">
         <v>1</v>
       </c>
       <c r="AT17" s="73" t="s">
@@ -48327,13 +48361,13 @@
       <c r="Z18" s="73" t="s">
         <v>420</v>
       </c>
-      <c r="AA18" s="85">
+      <c r="AA18">
         <v>1</v>
       </c>
       <c r="AE18" s="73" t="s">
         <v>214</v>
       </c>
-      <c r="AF18" s="85">
+      <c r="AF18">
         <v>1</v>
       </c>
       <c r="AT18" s="73" t="s">
@@ -48347,13 +48381,13 @@
       <c r="Z19" s="73" t="s">
         <v>212</v>
       </c>
-      <c r="AA19" s="85">
+      <c r="AA19">
         <v>1</v>
       </c>
       <c r="AE19" s="73" t="s">
         <v>418</v>
       </c>
-      <c r="AF19" s="85">
+      <c r="AF19">
         <v>1</v>
       </c>
     </row>
@@ -48361,29 +48395,29 @@
       <c r="Z20" s="73" t="s">
         <v>369</v>
       </c>
-      <c r="AA20" s="85">
+      <c r="AA20">
         <v>105</v>
       </c>
       <c r="AE20" s="73" t="s">
         <v>369</v>
       </c>
-      <c r="AF20" s="85">
+      <c r="AF20">
         <v>30</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A1:D5"/>
-    <mergeCell ref="F1:I5"/>
-    <mergeCell ref="K1:N5"/>
-    <mergeCell ref="P1:S5"/>
-    <mergeCell ref="U1:X5"/>
     <mergeCell ref="AY1:BB5"/>
     <mergeCell ref="Z1:AC5"/>
     <mergeCell ref="AE1:AH5"/>
     <mergeCell ref="AJ1:AM5"/>
     <mergeCell ref="AO1:AR5"/>
     <mergeCell ref="AT1:AW5"/>
+    <mergeCell ref="A1:D5"/>
+    <mergeCell ref="F1:I5"/>
+    <mergeCell ref="K1:N5"/>
+    <mergeCell ref="P1:S5"/>
+    <mergeCell ref="U1:X5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId12"/>
@@ -48403,1538 +48437,1538 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A1" s="83"/>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="E1" s="83"/>
-      <c r="F1" s="83"/>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="J1" s="83"/>
-      <c r="K1" s="83"/>
-      <c r="L1" s="83"/>
-      <c r="M1" s="83"/>
-      <c r="N1" s="83"/>
-      <c r="O1" s="83"/>
-      <c r="P1" s="83"/>
-      <c r="Q1" s="83"/>
-      <c r="R1" s="83"/>
-      <c r="S1" s="83"/>
-      <c r="T1" s="83"/>
-      <c r="U1" s="83"/>
-      <c r="V1" s="83"/>
-      <c r="W1" s="83"/>
-      <c r="X1" s="83"/>
+      <c r="A1" s="81"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
+      <c r="G1" s="81"/>
+      <c r="H1" s="81"/>
+      <c r="I1" s="81"/>
+      <c r="J1" s="81"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="81"/>
+      <c r="M1" s="81"/>
+      <c r="N1" s="81"/>
+      <c r="O1" s="81"/>
+      <c r="P1" s="81"/>
+      <c r="Q1" s="81"/>
+      <c r="R1" s="81"/>
+      <c r="S1" s="81"/>
+      <c r="T1" s="81"/>
+      <c r="U1" s="81"/>
+      <c r="V1" s="81"/>
+      <c r="W1" s="81"/>
+      <c r="X1" s="81"/>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A2" s="83"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="J2" s="83"/>
-      <c r="K2" s="83"/>
-      <c r="L2" s="83"/>
-      <c r="M2" s="83"/>
-      <c r="N2" s="83"/>
-      <c r="O2" s="83"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="83"/>
-      <c r="T2" s="83"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="83"/>
-      <c r="W2" s="83"/>
-      <c r="X2" s="83"/>
+      <c r="A2" s="81"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="81"/>
+      <c r="L2" s="81"/>
+      <c r="M2" s="81"/>
+      <c r="N2" s="81"/>
+      <c r="O2" s="81"/>
+      <c r="P2" s="81"/>
+      <c r="Q2" s="81"/>
+      <c r="R2" s="81"/>
+      <c r="S2" s="81"/>
+      <c r="T2" s="81"/>
+      <c r="U2" s="81"/>
+      <c r="V2" s="81"/>
+      <c r="W2" s="81"/>
+      <c r="X2" s="81"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A3" s="83"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="J3" s="83"/>
-      <c r="K3" s="83"/>
-      <c r="L3" s="83"/>
-      <c r="M3" s="83"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="83"/>
-      <c r="U3" s="83"/>
-      <c r="V3" s="83"/>
-      <c r="W3" s="83"/>
-      <c r="X3" s="83"/>
+      <c r="A3" s="81"/>
+      <c r="B3" s="81"/>
+      <c r="C3" s="81"/>
+      <c r="D3" s="81"/>
+      <c r="E3" s="81"/>
+      <c r="F3" s="81"/>
+      <c r="G3" s="81"/>
+      <c r="H3" s="81"/>
+      <c r="I3" s="81"/>
+      <c r="J3" s="81"/>
+      <c r="K3" s="81"/>
+      <c r="L3" s="81"/>
+      <c r="M3" s="81"/>
+      <c r="N3" s="81"/>
+      <c r="O3" s="81"/>
+      <c r="P3" s="81"/>
+      <c r="Q3" s="81"/>
+      <c r="R3" s="81"/>
+      <c r="S3" s="81"/>
+      <c r="T3" s="81"/>
+      <c r="U3" s="81"/>
+      <c r="V3" s="81"/>
+      <c r="W3" s="81"/>
+      <c r="X3" s="81"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A4" s="83"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="83"/>
-      <c r="K4" s="83"/>
-      <c r="L4" s="83"/>
-      <c r="M4" s="83"/>
-      <c r="N4" s="83"/>
-      <c r="O4" s="83"/>
-      <c r="P4" s="83"/>
-      <c r="Q4" s="83"/>
-      <c r="R4" s="83"/>
-      <c r="S4" s="83"/>
-      <c r="T4" s="83"/>
-      <c r="U4" s="83"/>
-      <c r="V4" s="83"/>
-      <c r="W4" s="83"/>
-      <c r="X4" s="83"/>
+      <c r="A4" s="81"/>
+      <c r="B4" s="81"/>
+      <c r="C4" s="81"/>
+      <c r="D4" s="81"/>
+      <c r="E4" s="81"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="81"/>
+      <c r="H4" s="81"/>
+      <c r="I4" s="81"/>
+      <c r="J4" s="81"/>
+      <c r="K4" s="81"/>
+      <c r="L4" s="81"/>
+      <c r="M4" s="81"/>
+      <c r="N4" s="81"/>
+      <c r="O4" s="81"/>
+      <c r="P4" s="81"/>
+      <c r="Q4" s="81"/>
+      <c r="R4" s="81"/>
+      <c r="S4" s="81"/>
+      <c r="T4" s="81"/>
+      <c r="U4" s="81"/>
+      <c r="V4" s="81"/>
+      <c r="W4" s="81"/>
+      <c r="X4" s="81"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A5" s="83"/>
-      <c r="B5" s="83"/>
-      <c r="C5" s="83"/>
-      <c r="D5" s="83"/>
-      <c r="E5" s="83"/>
-      <c r="F5" s="83"/>
-      <c r="G5" s="83"/>
-      <c r="H5" s="83"/>
-      <c r="I5" s="83"/>
-      <c r="J5" s="83"/>
-      <c r="K5" s="83"/>
-      <c r="L5" s="83"/>
-      <c r="M5" s="83"/>
-      <c r="N5" s="83"/>
-      <c r="O5" s="83"/>
-      <c r="P5" s="83"/>
-      <c r="Q5" s="83"/>
-      <c r="R5" s="83"/>
-      <c r="S5" s="83"/>
-      <c r="T5" s="83"/>
-      <c r="U5" s="83"/>
-      <c r="V5" s="83"/>
-      <c r="W5" s="83"/>
-      <c r="X5" s="83"/>
+      <c r="A5" s="81"/>
+      <c r="B5" s="81"/>
+      <c r="C5" s="81"/>
+      <c r="D5" s="81"/>
+      <c r="E5" s="81"/>
+      <c r="F5" s="81"/>
+      <c r="G5" s="81"/>
+      <c r="H5" s="81"/>
+      <c r="I5" s="81"/>
+      <c r="J5" s="81"/>
+      <c r="K5" s="81"/>
+      <c r="L5" s="81"/>
+      <c r="M5" s="81"/>
+      <c r="N5" s="81"/>
+      <c r="O5" s="81"/>
+      <c r="P5" s="81"/>
+      <c r="Q5" s="81"/>
+      <c r="R5" s="81"/>
+      <c r="S5" s="81"/>
+      <c r="T5" s="81"/>
+      <c r="U5" s="81"/>
+      <c r="V5" s="81"/>
+      <c r="W5" s="81"/>
+      <c r="X5" s="81"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A6" s="83"/>
-      <c r="B6" s="83"/>
-      <c r="C6" s="83"/>
-      <c r="D6" s="83"/>
-      <c r="E6" s="83"/>
-      <c r="F6" s="83"/>
-      <c r="G6" s="83"/>
-      <c r="H6" s="83"/>
-      <c r="I6" s="83"/>
-      <c r="J6" s="83"/>
-      <c r="K6" s="83"/>
-      <c r="L6" s="83"/>
-      <c r="M6" s="83"/>
-      <c r="N6" s="83"/>
-      <c r="O6" s="83"/>
-      <c r="P6" s="83"/>
-      <c r="Q6" s="83"/>
-      <c r="R6" s="83"/>
-      <c r="S6" s="83"/>
-      <c r="T6" s="83"/>
-      <c r="U6" s="83"/>
-      <c r="V6" s="83"/>
-      <c r="W6" s="83"/>
-      <c r="X6" s="83"/>
+      <c r="A6" s="81"/>
+      <c r="B6" s="81"/>
+      <c r="C6" s="81"/>
+      <c r="D6" s="81"/>
+      <c r="E6" s="81"/>
+      <c r="F6" s="81"/>
+      <c r="G6" s="81"/>
+      <c r="H6" s="81"/>
+      <c r="I6" s="81"/>
+      <c r="J6" s="81"/>
+      <c r="K6" s="81"/>
+      <c r="L6" s="81"/>
+      <c r="M6" s="81"/>
+      <c r="N6" s="81"/>
+      <c r="O6" s="81"/>
+      <c r="P6" s="81"/>
+      <c r="Q6" s="81"/>
+      <c r="R6" s="81"/>
+      <c r="S6" s="81"/>
+      <c r="T6" s="81"/>
+      <c r="U6" s="81"/>
+      <c r="V6" s="81"/>
+      <c r="W6" s="81"/>
+      <c r="X6" s="81"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A7" s="83"/>
-      <c r="B7" s="83"/>
-      <c r="C7" s="83"/>
-      <c r="D7" s="83"/>
-      <c r="E7" s="83"/>
-      <c r="F7" s="83"/>
-      <c r="G7" s="83"/>
-      <c r="H7" s="83"/>
-      <c r="I7" s="83"/>
-      <c r="J7" s="83"/>
-      <c r="K7" s="83"/>
-      <c r="L7" s="83"/>
-      <c r="M7" s="83"/>
-      <c r="N7" s="83"/>
-      <c r="O7" s="83"/>
-      <c r="P7" s="83"/>
-      <c r="Q7" s="83"/>
-      <c r="R7" s="83"/>
-      <c r="S7" s="83"/>
-      <c r="T7" s="83"/>
-      <c r="U7" s="83"/>
-      <c r="V7" s="83"/>
-      <c r="W7" s="83"/>
-      <c r="X7" s="83"/>
+      <c r="A7" s="81"/>
+      <c r="B7" s="81"/>
+      <c r="C7" s="81"/>
+      <c r="D7" s="81"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="81"/>
+      <c r="H7" s="81"/>
+      <c r="I7" s="81"/>
+      <c r="J7" s="81"/>
+      <c r="K7" s="81"/>
+      <c r="L7" s="81"/>
+      <c r="M7" s="81"/>
+      <c r="N7" s="81"/>
+      <c r="O7" s="81"/>
+      <c r="P7" s="81"/>
+      <c r="Q7" s="81"/>
+      <c r="R7" s="81"/>
+      <c r="S7" s="81"/>
+      <c r="T7" s="81"/>
+      <c r="U7" s="81"/>
+      <c r="V7" s="81"/>
+      <c r="W7" s="81"/>
+      <c r="X7" s="81"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A8" s="83"/>
-      <c r="B8" s="83"/>
-      <c r="C8" s="83"/>
-      <c r="D8" s="83"/>
-      <c r="E8" s="83"/>
-      <c r="F8" s="83"/>
-      <c r="G8" s="83"/>
-      <c r="H8" s="83"/>
-      <c r="I8" s="83"/>
-      <c r="J8" s="83"/>
-      <c r="K8" s="83"/>
-      <c r="L8" s="83"/>
-      <c r="M8" s="83"/>
-      <c r="N8" s="83"/>
-      <c r="O8" s="83"/>
-      <c r="P8" s="83"/>
-      <c r="Q8" s="83"/>
-      <c r="R8" s="83"/>
-      <c r="S8" s="83"/>
-      <c r="T8" s="83"/>
-      <c r="U8" s="83"/>
-      <c r="V8" s="83"/>
-      <c r="W8" s="83"/>
-      <c r="X8" s="83"/>
+      <c r="A8" s="81"/>
+      <c r="B8" s="81"/>
+      <c r="C8" s="81"/>
+      <c r="D8" s="81"/>
+      <c r="E8" s="81"/>
+      <c r="F8" s="81"/>
+      <c r="G8" s="81"/>
+      <c r="H8" s="81"/>
+      <c r="I8" s="81"/>
+      <c r="J8" s="81"/>
+      <c r="K8" s="81"/>
+      <c r="L8" s="81"/>
+      <c r="M8" s="81"/>
+      <c r="N8" s="81"/>
+      <c r="O8" s="81"/>
+      <c r="P8" s="81"/>
+      <c r="Q8" s="81"/>
+      <c r="R8" s="81"/>
+      <c r="S8" s="81"/>
+      <c r="T8" s="81"/>
+      <c r="U8" s="81"/>
+      <c r="V8" s="81"/>
+      <c r="W8" s="81"/>
+      <c r="X8" s="81"/>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A9" s="83"/>
-      <c r="B9" s="83"/>
-      <c r="C9" s="83"/>
-      <c r="D9" s="83"/>
-      <c r="E9" s="83"/>
-      <c r="F9" s="83"/>
-      <c r="G9" s="83"/>
-      <c r="H9" s="83"/>
-      <c r="I9" s="83"/>
-      <c r="J9" s="83"/>
-      <c r="K9" s="83"/>
-      <c r="L9" s="83"/>
-      <c r="M9" s="83"/>
-      <c r="N9" s="83"/>
-      <c r="O9" s="83"/>
-      <c r="P9" s="83"/>
-      <c r="Q9" s="83"/>
-      <c r="R9" s="83"/>
-      <c r="S9" s="83"/>
-      <c r="T9" s="83"/>
-      <c r="U9" s="83"/>
-      <c r="V9" s="83"/>
-      <c r="W9" s="83"/>
-      <c r="X9" s="83"/>
+      <c r="A9" s="81"/>
+      <c r="B9" s="81"/>
+      <c r="C9" s="81"/>
+      <c r="D9" s="81"/>
+      <c r="E9" s="81"/>
+      <c r="F9" s="81"/>
+      <c r="G9" s="81"/>
+      <c r="H9" s="81"/>
+      <c r="I9" s="81"/>
+      <c r="J9" s="81"/>
+      <c r="K9" s="81"/>
+      <c r="L9" s="81"/>
+      <c r="M9" s="81"/>
+      <c r="N9" s="81"/>
+      <c r="O9" s="81"/>
+      <c r="P9" s="81"/>
+      <c r="Q9" s="81"/>
+      <c r="R9" s="81"/>
+      <c r="S9" s="81"/>
+      <c r="T9" s="81"/>
+      <c r="U9" s="81"/>
+      <c r="V9" s="81"/>
+      <c r="W9" s="81"/>
+      <c r="X9" s="81"/>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A10" s="83"/>
-      <c r="B10" s="83"/>
-      <c r="C10" s="83"/>
-      <c r="D10" s="83"/>
-      <c r="E10" s="83"/>
-      <c r="F10" s="83"/>
-      <c r="G10" s="83"/>
-      <c r="H10" s="83"/>
-      <c r="I10" s="83"/>
-      <c r="J10" s="83"/>
-      <c r="K10" s="83"/>
-      <c r="L10" s="83"/>
-      <c r="M10" s="83"/>
-      <c r="N10" s="83"/>
-      <c r="O10" s="83"/>
-      <c r="P10" s="83"/>
-      <c r="Q10" s="83"/>
-      <c r="R10" s="83"/>
-      <c r="S10" s="83"/>
-      <c r="T10" s="83"/>
-      <c r="U10" s="83"/>
-      <c r="V10" s="83"/>
-      <c r="W10" s="83"/>
-      <c r="X10" s="83"/>
+      <c r="A10" s="81"/>
+      <c r="B10" s="81"/>
+      <c r="C10" s="81"/>
+      <c r="D10" s="81"/>
+      <c r="E10" s="81"/>
+      <c r="F10" s="81"/>
+      <c r="G10" s="81"/>
+      <c r="H10" s="81"/>
+      <c r="I10" s="81"/>
+      <c r="J10" s="81"/>
+      <c r="K10" s="81"/>
+      <c r="L10" s="81"/>
+      <c r="M10" s="81"/>
+      <c r="N10" s="81"/>
+      <c r="O10" s="81"/>
+      <c r="P10" s="81"/>
+      <c r="Q10" s="81"/>
+      <c r="R10" s="81"/>
+      <c r="S10" s="81"/>
+      <c r="T10" s="81"/>
+      <c r="U10" s="81"/>
+      <c r="V10" s="81"/>
+      <c r="W10" s="81"/>
+      <c r="X10" s="81"/>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A11" s="83"/>
-      <c r="B11" s="83"/>
-      <c r="C11" s="83"/>
-      <c r="D11" s="83"/>
-      <c r="E11" s="83"/>
-      <c r="F11" s="83"/>
-      <c r="G11" s="83"/>
-      <c r="H11" s="83"/>
-      <c r="I11" s="83"/>
-      <c r="J11" s="83"/>
-      <c r="K11" s="83"/>
-      <c r="L11" s="83"/>
-      <c r="M11" s="83"/>
-      <c r="N11" s="83"/>
-      <c r="O11" s="83"/>
-      <c r="P11" s="83"/>
-      <c r="Q11" s="83"/>
-      <c r="R11" s="83"/>
-      <c r="S11" s="83"/>
-      <c r="T11" s="83"/>
-      <c r="U11" s="83"/>
-      <c r="V11" s="83"/>
-      <c r="W11" s="83"/>
-      <c r="X11" s="83"/>
+      <c r="A11" s="81"/>
+      <c r="B11" s="81"/>
+      <c r="C11" s="81"/>
+      <c r="D11" s="81"/>
+      <c r="E11" s="81"/>
+      <c r="F11" s="81"/>
+      <c r="G11" s="81"/>
+      <c r="H11" s="81"/>
+      <c r="I11" s="81"/>
+      <c r="J11" s="81"/>
+      <c r="K11" s="81"/>
+      <c r="L11" s="81"/>
+      <c r="M11" s="81"/>
+      <c r="N11" s="81"/>
+      <c r="O11" s="81"/>
+      <c r="P11" s="81"/>
+      <c r="Q11" s="81"/>
+      <c r="R11" s="81"/>
+      <c r="S11" s="81"/>
+      <c r="T11" s="81"/>
+      <c r="U11" s="81"/>
+      <c r="V11" s="81"/>
+      <c r="W11" s="81"/>
+      <c r="X11" s="81"/>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A12" s="83"/>
-      <c r="B12" s="83"/>
-      <c r="C12" s="83"/>
-      <c r="D12" s="83"/>
-      <c r="E12" s="83"/>
-      <c r="F12" s="83"/>
-      <c r="G12" s="83"/>
-      <c r="H12" s="83"/>
-      <c r="I12" s="83"/>
-      <c r="J12" s="83"/>
-      <c r="K12" s="83"/>
-      <c r="L12" s="83"/>
-      <c r="M12" s="83"/>
-      <c r="N12" s="83"/>
-      <c r="O12" s="83"/>
-      <c r="P12" s="83"/>
-      <c r="Q12" s="83"/>
-      <c r="R12" s="83"/>
-      <c r="S12" s="83"/>
-      <c r="T12" s="83"/>
-      <c r="U12" s="83"/>
-      <c r="V12" s="83"/>
-      <c r="W12" s="83"/>
-      <c r="X12" s="83"/>
+      <c r="A12" s="81"/>
+      <c r="B12" s="81"/>
+      <c r="C12" s="81"/>
+      <c r="D12" s="81"/>
+      <c r="E12" s="81"/>
+      <c r="F12" s="81"/>
+      <c r="G12" s="81"/>
+      <c r="H12" s="81"/>
+      <c r="I12" s="81"/>
+      <c r="J12" s="81"/>
+      <c r="K12" s="81"/>
+      <c r="L12" s="81"/>
+      <c r="M12" s="81"/>
+      <c r="N12" s="81"/>
+      <c r="O12" s="81"/>
+      <c r="P12" s="81"/>
+      <c r="Q12" s="81"/>
+      <c r="R12" s="81"/>
+      <c r="S12" s="81"/>
+      <c r="T12" s="81"/>
+      <c r="U12" s="81"/>
+      <c r="V12" s="81"/>
+      <c r="W12" s="81"/>
+      <c r="X12" s="81"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A13" s="83"/>
-      <c r="B13" s="83"/>
-      <c r="C13" s="83"/>
-      <c r="D13" s="83"/>
-      <c r="E13" s="83"/>
-      <c r="F13" s="83"/>
-      <c r="G13" s="83"/>
-      <c r="H13" s="83"/>
-      <c r="I13" s="83"/>
-      <c r="J13" s="83"/>
-      <c r="K13" s="83"/>
-      <c r="L13" s="83"/>
-      <c r="M13" s="83"/>
-      <c r="N13" s="83"/>
-      <c r="O13" s="83"/>
-      <c r="P13" s="83"/>
-      <c r="Q13" s="83"/>
-      <c r="R13" s="83"/>
-      <c r="S13" s="83"/>
-      <c r="T13" s="83"/>
-      <c r="U13" s="83"/>
-      <c r="V13" s="83"/>
-      <c r="W13" s="83"/>
-      <c r="X13" s="83"/>
+      <c r="A13" s="81"/>
+      <c r="B13" s="81"/>
+      <c r="C13" s="81"/>
+      <c r="D13" s="81"/>
+      <c r="E13" s="81"/>
+      <c r="F13" s="81"/>
+      <c r="G13" s="81"/>
+      <c r="H13" s="81"/>
+      <c r="I13" s="81"/>
+      <c r="J13" s="81"/>
+      <c r="K13" s="81"/>
+      <c r="L13" s="81"/>
+      <c r="M13" s="81"/>
+      <c r="N13" s="81"/>
+      <c r="O13" s="81"/>
+      <c r="P13" s="81"/>
+      <c r="Q13" s="81"/>
+      <c r="R13" s="81"/>
+      <c r="S13" s="81"/>
+      <c r="T13" s="81"/>
+      <c r="U13" s="81"/>
+      <c r="V13" s="81"/>
+      <c r="W13" s="81"/>
+      <c r="X13" s="81"/>
     </row>
     <row r="14" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A14" s="83"/>
-      <c r="B14" s="83"/>
-      <c r="C14" s="83"/>
-      <c r="D14" s="83"/>
-      <c r="E14" s="83"/>
-      <c r="F14" s="83"/>
-      <c r="G14" s="83"/>
-      <c r="H14" s="83"/>
-      <c r="I14" s="83"/>
-      <c r="J14" s="83"/>
-      <c r="K14" s="83"/>
-      <c r="L14" s="83"/>
-      <c r="M14" s="83"/>
-      <c r="N14" s="83"/>
-      <c r="O14" s="83"/>
-      <c r="P14" s="83"/>
-      <c r="Q14" s="83"/>
-      <c r="R14" s="83"/>
-      <c r="S14" s="83"/>
-      <c r="T14" s="83"/>
-      <c r="U14" s="83"/>
-      <c r="V14" s="83"/>
-      <c r="W14" s="83"/>
-      <c r="X14" s="83"/>
+      <c r="A14" s="81"/>
+      <c r="B14" s="81"/>
+      <c r="C14" s="81"/>
+      <c r="D14" s="81"/>
+      <c r="E14" s="81"/>
+      <c r="F14" s="81"/>
+      <c r="G14" s="81"/>
+      <c r="H14" s="81"/>
+      <c r="I14" s="81"/>
+      <c r="J14" s="81"/>
+      <c r="K14" s="81"/>
+      <c r="L14" s="81"/>
+      <c r="M14" s="81"/>
+      <c r="N14" s="81"/>
+      <c r="O14" s="81"/>
+      <c r="P14" s="81"/>
+      <c r="Q14" s="81"/>
+      <c r="R14" s="81"/>
+      <c r="S14" s="81"/>
+      <c r="T14" s="81"/>
+      <c r="U14" s="81"/>
+      <c r="V14" s="81"/>
+      <c r="W14" s="81"/>
+      <c r="X14" s="81"/>
     </row>
     <row r="15" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A15" s="83"/>
-      <c r="B15" s="83"/>
-      <c r="C15" s="83"/>
-      <c r="D15" s="83"/>
-      <c r="E15" s="83"/>
-      <c r="F15" s="83"/>
-      <c r="G15" s="83"/>
-      <c r="H15" s="83"/>
-      <c r="I15" s="83"/>
-      <c r="J15" s="83"/>
-      <c r="K15" s="83"/>
-      <c r="L15" s="83"/>
-      <c r="M15" s="83"/>
-      <c r="N15" s="83"/>
-      <c r="O15" s="83"/>
-      <c r="P15" s="83"/>
-      <c r="Q15" s="83"/>
-      <c r="R15" s="83"/>
-      <c r="S15" s="83"/>
-      <c r="T15" s="83"/>
-      <c r="U15" s="83"/>
-      <c r="V15" s="83"/>
-      <c r="W15" s="83"/>
-      <c r="X15" s="83"/>
+      <c r="A15" s="81"/>
+      <c r="B15" s="81"/>
+      <c r="C15" s="81"/>
+      <c r="D15" s="81"/>
+      <c r="E15" s="81"/>
+      <c r="F15" s="81"/>
+      <c r="G15" s="81"/>
+      <c r="H15" s="81"/>
+      <c r="I15" s="81"/>
+      <c r="J15" s="81"/>
+      <c r="K15" s="81"/>
+      <c r="L15" s="81"/>
+      <c r="M15" s="81"/>
+      <c r="N15" s="81"/>
+      <c r="O15" s="81"/>
+      <c r="P15" s="81"/>
+      <c r="Q15" s="81"/>
+      <c r="R15" s="81"/>
+      <c r="S15" s="81"/>
+      <c r="T15" s="81"/>
+      <c r="U15" s="81"/>
+      <c r="V15" s="81"/>
+      <c r="W15" s="81"/>
+      <c r="X15" s="81"/>
     </row>
     <row r="16" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A16" s="83"/>
-      <c r="B16" s="83"/>
-      <c r="C16" s="83"/>
-      <c r="D16" s="83"/>
-      <c r="E16" s="83"/>
-      <c r="F16" s="83"/>
-      <c r="G16" s="83"/>
-      <c r="H16" s="83"/>
-      <c r="I16" s="83"/>
-      <c r="J16" s="83"/>
-      <c r="K16" s="83"/>
-      <c r="L16" s="83"/>
-      <c r="M16" s="83"/>
-      <c r="N16" s="83"/>
-      <c r="O16" s="83"/>
-      <c r="P16" s="83"/>
-      <c r="Q16" s="83"/>
-      <c r="R16" s="83"/>
-      <c r="S16" s="83"/>
-      <c r="T16" s="83"/>
-      <c r="U16" s="83"/>
-      <c r="V16" s="83"/>
-      <c r="W16" s="83"/>
-      <c r="X16" s="83"/>
+      <c r="A16" s="81"/>
+      <c r="B16" s="81"/>
+      <c r="C16" s="81"/>
+      <c r="D16" s="81"/>
+      <c r="E16" s="81"/>
+      <c r="F16" s="81"/>
+      <c r="G16" s="81"/>
+      <c r="H16" s="81"/>
+      <c r="I16" s="81"/>
+      <c r="J16" s="81"/>
+      <c r="K16" s="81"/>
+      <c r="L16" s="81"/>
+      <c r="M16" s="81"/>
+      <c r="N16" s="81"/>
+      <c r="O16" s="81"/>
+      <c r="P16" s="81"/>
+      <c r="Q16" s="81"/>
+      <c r="R16" s="81"/>
+      <c r="S16" s="81"/>
+      <c r="T16" s="81"/>
+      <c r="U16" s="81"/>
+      <c r="V16" s="81"/>
+      <c r="W16" s="81"/>
+      <c r="X16" s="81"/>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A17" s="83"/>
-      <c r="B17" s="83"/>
-      <c r="C17" s="83"/>
-      <c r="D17" s="83"/>
-      <c r="E17" s="83"/>
-      <c r="F17" s="83"/>
-      <c r="G17" s="83"/>
-      <c r="H17" s="83"/>
-      <c r="I17" s="83"/>
-      <c r="J17" s="83"/>
-      <c r="K17" s="83"/>
-      <c r="L17" s="83"/>
-      <c r="M17" s="83"/>
-      <c r="N17" s="83"/>
-      <c r="O17" s="83"/>
-      <c r="P17" s="83"/>
-      <c r="Q17" s="83"/>
-      <c r="R17" s="83"/>
-      <c r="S17" s="83"/>
-      <c r="T17" s="83"/>
-      <c r="U17" s="83"/>
-      <c r="V17" s="83"/>
-      <c r="W17" s="83"/>
-      <c r="X17" s="83"/>
+      <c r="A17" s="81"/>
+      <c r="B17" s="81"/>
+      <c r="C17" s="81"/>
+      <c r="D17" s="81"/>
+      <c r="E17" s="81"/>
+      <c r="F17" s="81"/>
+      <c r="G17" s="81"/>
+      <c r="H17" s="81"/>
+      <c r="I17" s="81"/>
+      <c r="J17" s="81"/>
+      <c r="K17" s="81"/>
+      <c r="L17" s="81"/>
+      <c r="M17" s="81"/>
+      <c r="N17" s="81"/>
+      <c r="O17" s="81"/>
+      <c r="P17" s="81"/>
+      <c r="Q17" s="81"/>
+      <c r="R17" s="81"/>
+      <c r="S17" s="81"/>
+      <c r="T17" s="81"/>
+      <c r="U17" s="81"/>
+      <c r="V17" s="81"/>
+      <c r="W17" s="81"/>
+      <c r="X17" s="81"/>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A18" s="83"/>
-      <c r="B18" s="83"/>
-      <c r="C18" s="83"/>
-      <c r="D18" s="83"/>
-      <c r="E18" s="83"/>
-      <c r="F18" s="83"/>
-      <c r="G18" s="83"/>
-      <c r="H18" s="83"/>
-      <c r="I18" s="83"/>
-      <c r="J18" s="83"/>
-      <c r="K18" s="83"/>
-      <c r="L18" s="83"/>
-      <c r="M18" s="83"/>
-      <c r="N18" s="83"/>
-      <c r="O18" s="83"/>
-      <c r="P18" s="83"/>
-      <c r="Q18" s="83"/>
-      <c r="R18" s="83"/>
-      <c r="S18" s="83"/>
-      <c r="T18" s="83"/>
-      <c r="U18" s="83"/>
-      <c r="V18" s="83"/>
-      <c r="W18" s="83"/>
-      <c r="X18" s="83"/>
+      <c r="A18" s="81"/>
+      <c r="B18" s="81"/>
+      <c r="C18" s="81"/>
+      <c r="D18" s="81"/>
+      <c r="E18" s="81"/>
+      <c r="F18" s="81"/>
+      <c r="G18" s="81"/>
+      <c r="H18" s="81"/>
+      <c r="I18" s="81"/>
+      <c r="J18" s="81"/>
+      <c r="K18" s="81"/>
+      <c r="L18" s="81"/>
+      <c r="M18" s="81"/>
+      <c r="N18" s="81"/>
+      <c r="O18" s="81"/>
+      <c r="P18" s="81"/>
+      <c r="Q18" s="81"/>
+      <c r="R18" s="81"/>
+      <c r="S18" s="81"/>
+      <c r="T18" s="81"/>
+      <c r="U18" s="81"/>
+      <c r="V18" s="81"/>
+      <c r="W18" s="81"/>
+      <c r="X18" s="81"/>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A19" s="83"/>
-      <c r="B19" s="83"/>
-      <c r="C19" s="83"/>
-      <c r="D19" s="83"/>
-      <c r="E19" s="83"/>
-      <c r="F19" s="83"/>
-      <c r="G19" s="83"/>
-      <c r="H19" s="83"/>
-      <c r="I19" s="83"/>
-      <c r="J19" s="83"/>
-      <c r="K19" s="83"/>
-      <c r="L19" s="83"/>
-      <c r="M19" s="83"/>
-      <c r="N19" s="83"/>
-      <c r="O19" s="83"/>
-      <c r="P19" s="83"/>
-      <c r="Q19" s="83"/>
-      <c r="R19" s="83"/>
-      <c r="S19" s="83"/>
-      <c r="T19" s="83"/>
-      <c r="U19" s="83"/>
-      <c r="V19" s="83"/>
-      <c r="W19" s="83"/>
-      <c r="X19" s="83"/>
+      <c r="A19" s="81"/>
+      <c r="B19" s="81"/>
+      <c r="C19" s="81"/>
+      <c r="D19" s="81"/>
+      <c r="E19" s="81"/>
+      <c r="F19" s="81"/>
+      <c r="G19" s="81"/>
+      <c r="H19" s="81"/>
+      <c r="I19" s="81"/>
+      <c r="J19" s="81"/>
+      <c r="K19" s="81"/>
+      <c r="L19" s="81"/>
+      <c r="M19" s="81"/>
+      <c r="N19" s="81"/>
+      <c r="O19" s="81"/>
+      <c r="P19" s="81"/>
+      <c r="Q19" s="81"/>
+      <c r="R19" s="81"/>
+      <c r="S19" s="81"/>
+      <c r="T19" s="81"/>
+      <c r="U19" s="81"/>
+      <c r="V19" s="81"/>
+      <c r="W19" s="81"/>
+      <c r="X19" s="81"/>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A20" s="83"/>
-      <c r="B20" s="83"/>
-      <c r="C20" s="83"/>
-      <c r="D20" s="83"/>
-      <c r="E20" s="83"/>
-      <c r="F20" s="83"/>
-      <c r="G20" s="83"/>
-      <c r="H20" s="83"/>
-      <c r="I20" s="83"/>
-      <c r="J20" s="83"/>
-      <c r="K20" s="83"/>
-      <c r="L20" s="83"/>
-      <c r="M20" s="83"/>
-      <c r="N20" s="83"/>
-      <c r="O20" s="83"/>
-      <c r="P20" s="83"/>
-      <c r="Q20" s="83"/>
-      <c r="R20" s="83"/>
-      <c r="S20" s="83"/>
-      <c r="T20" s="83"/>
-      <c r="U20" s="83"/>
-      <c r="V20" s="83"/>
-      <c r="W20" s="83"/>
-      <c r="X20" s="83"/>
+      <c r="A20" s="81"/>
+      <c r="B20" s="81"/>
+      <c r="C20" s="81"/>
+      <c r="D20" s="81"/>
+      <c r="E20" s="81"/>
+      <c r="F20" s="81"/>
+      <c r="G20" s="81"/>
+      <c r="H20" s="81"/>
+      <c r="I20" s="81"/>
+      <c r="J20" s="81"/>
+      <c r="K20" s="81"/>
+      <c r="L20" s="81"/>
+      <c r="M20" s="81"/>
+      <c r="N20" s="81"/>
+      <c r="O20" s="81"/>
+      <c r="P20" s="81"/>
+      <c r="Q20" s="81"/>
+      <c r="R20" s="81"/>
+      <c r="S20" s="81"/>
+      <c r="T20" s="81"/>
+      <c r="U20" s="81"/>
+      <c r="V20" s="81"/>
+      <c r="W20" s="81"/>
+      <c r="X20" s="81"/>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A21" s="83"/>
-      <c r="B21" s="83"/>
-      <c r="C21" s="83"/>
-      <c r="D21" s="83"/>
-      <c r="E21" s="83"/>
-      <c r="F21" s="83"/>
-      <c r="G21" s="83"/>
-      <c r="H21" s="83"/>
-      <c r="I21" s="83"/>
-      <c r="J21" s="83"/>
-      <c r="K21" s="83"/>
-      <c r="L21" s="83"/>
-      <c r="M21" s="83"/>
-      <c r="N21" s="83"/>
-      <c r="O21" s="83"/>
-      <c r="P21" s="83"/>
-      <c r="Q21" s="83"/>
-      <c r="R21" s="83"/>
-      <c r="S21" s="83"/>
-      <c r="T21" s="83"/>
-      <c r="U21" s="83"/>
-      <c r="V21" s="83"/>
-      <c r="W21" s="83"/>
-      <c r="X21" s="83"/>
+      <c r="A21" s="81"/>
+      <c r="B21" s="81"/>
+      <c r="C21" s="81"/>
+      <c r="D21" s="81"/>
+      <c r="E21" s="81"/>
+      <c r="F21" s="81"/>
+      <c r="G21" s="81"/>
+      <c r="H21" s="81"/>
+      <c r="I21" s="81"/>
+      <c r="J21" s="81"/>
+      <c r="K21" s="81"/>
+      <c r="L21" s="81"/>
+      <c r="M21" s="81"/>
+      <c r="N21" s="81"/>
+      <c r="O21" s="81"/>
+      <c r="P21" s="81"/>
+      <c r="Q21" s="81"/>
+      <c r="R21" s="81"/>
+      <c r="S21" s="81"/>
+      <c r="T21" s="81"/>
+      <c r="U21" s="81"/>
+      <c r="V21" s="81"/>
+      <c r="W21" s="81"/>
+      <c r="X21" s="81"/>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A22" s="83"/>
-      <c r="B22" s="83"/>
-      <c r="C22" s="83"/>
-      <c r="D22" s="83"/>
-      <c r="E22" s="83"/>
-      <c r="F22" s="83"/>
-      <c r="G22" s="83"/>
-      <c r="H22" s="83"/>
-      <c r="I22" s="83"/>
-      <c r="J22" s="83"/>
-      <c r="K22" s="83"/>
-      <c r="L22" s="83"/>
-      <c r="M22" s="83"/>
-      <c r="N22" s="83"/>
-      <c r="O22" s="83"/>
-      <c r="P22" s="83"/>
-      <c r="Q22" s="83"/>
-      <c r="R22" s="83"/>
-      <c r="S22" s="83"/>
-      <c r="T22" s="83"/>
-      <c r="U22" s="83"/>
-      <c r="V22" s="83"/>
-      <c r="W22" s="83"/>
-      <c r="X22" s="83"/>
+      <c r="A22" s="81"/>
+      <c r="B22" s="81"/>
+      <c r="C22" s="81"/>
+      <c r="D22" s="81"/>
+      <c r="E22" s="81"/>
+      <c r="F22" s="81"/>
+      <c r="G22" s="81"/>
+      <c r="H22" s="81"/>
+      <c r="I22" s="81"/>
+      <c r="J22" s="81"/>
+      <c r="K22" s="81"/>
+      <c r="L22" s="81"/>
+      <c r="M22" s="81"/>
+      <c r="N22" s="81"/>
+      <c r="O22" s="81"/>
+      <c r="P22" s="81"/>
+      <c r="Q22" s="81"/>
+      <c r="R22" s="81"/>
+      <c r="S22" s="81"/>
+      <c r="T22" s="81"/>
+      <c r="U22" s="81"/>
+      <c r="V22" s="81"/>
+      <c r="W22" s="81"/>
+      <c r="X22" s="81"/>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A23" s="83"/>
-      <c r="B23" s="83"/>
-      <c r="C23" s="83"/>
-      <c r="D23" s="83"/>
-      <c r="E23" s="83"/>
-      <c r="F23" s="83"/>
-      <c r="G23" s="83"/>
-      <c r="H23" s="83"/>
-      <c r="I23" s="83"/>
-      <c r="J23" s="83"/>
-      <c r="K23" s="83"/>
-      <c r="L23" s="83"/>
-      <c r="M23" s="83"/>
-      <c r="N23" s="83"/>
-      <c r="O23" s="83"/>
-      <c r="P23" s="83"/>
-      <c r="Q23" s="83"/>
-      <c r="R23" s="83"/>
-      <c r="S23" s="83"/>
-      <c r="T23" s="83"/>
-      <c r="U23" s="83"/>
-      <c r="V23" s="83"/>
-      <c r="W23" s="83"/>
-      <c r="X23" s="83"/>
+      <c r="A23" s="81"/>
+      <c r="B23" s="81"/>
+      <c r="C23" s="81"/>
+      <c r="D23" s="81"/>
+      <c r="E23" s="81"/>
+      <c r="F23" s="81"/>
+      <c r="G23" s="81"/>
+      <c r="H23" s="81"/>
+      <c r="I23" s="81"/>
+      <c r="J23" s="81"/>
+      <c r="K23" s="81"/>
+      <c r="L23" s="81"/>
+      <c r="M23" s="81"/>
+      <c r="N23" s="81"/>
+      <c r="O23" s="81"/>
+      <c r="P23" s="81"/>
+      <c r="Q23" s="81"/>
+      <c r="R23" s="81"/>
+      <c r="S23" s="81"/>
+      <c r="T23" s="81"/>
+      <c r="U23" s="81"/>
+      <c r="V23" s="81"/>
+      <c r="W23" s="81"/>
+      <c r="X23" s="81"/>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A24" s="83"/>
-      <c r="B24" s="83"/>
-      <c r="C24" s="83"/>
-      <c r="D24" s="83"/>
-      <c r="E24" s="83"/>
-      <c r="F24" s="83"/>
-      <c r="G24" s="83"/>
-      <c r="H24" s="83"/>
-      <c r="I24" s="83"/>
-      <c r="J24" s="83"/>
-      <c r="K24" s="83"/>
-      <c r="L24" s="83"/>
-      <c r="M24" s="83"/>
-      <c r="N24" s="83"/>
-      <c r="O24" s="83"/>
-      <c r="P24" s="83"/>
-      <c r="Q24" s="83"/>
-      <c r="R24" s="83"/>
-      <c r="S24" s="83"/>
-      <c r="T24" s="83"/>
-      <c r="U24" s="83"/>
-      <c r="V24" s="83"/>
-      <c r="W24" s="83"/>
-      <c r="X24" s="83"/>
+      <c r="A24" s="81"/>
+      <c r="B24" s="81"/>
+      <c r="C24" s="81"/>
+      <c r="D24" s="81"/>
+      <c r="E24" s="81"/>
+      <c r="F24" s="81"/>
+      <c r="G24" s="81"/>
+      <c r="H24" s="81"/>
+      <c r="I24" s="81"/>
+      <c r="J24" s="81"/>
+      <c r="K24" s="81"/>
+      <c r="L24" s="81"/>
+      <c r="M24" s="81"/>
+      <c r="N24" s="81"/>
+      <c r="O24" s="81"/>
+      <c r="P24" s="81"/>
+      <c r="Q24" s="81"/>
+      <c r="R24" s="81"/>
+      <c r="S24" s="81"/>
+      <c r="T24" s="81"/>
+      <c r="U24" s="81"/>
+      <c r="V24" s="81"/>
+      <c r="W24" s="81"/>
+      <c r="X24" s="81"/>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A25" s="83"/>
-      <c r="B25" s="83"/>
-      <c r="C25" s="83"/>
-      <c r="D25" s="83"/>
-      <c r="E25" s="83"/>
-      <c r="F25" s="83"/>
-      <c r="G25" s="83"/>
-      <c r="H25" s="83"/>
-      <c r="I25" s="83"/>
-      <c r="J25" s="83"/>
-      <c r="K25" s="83"/>
-      <c r="L25" s="83"/>
-      <c r="M25" s="83"/>
-      <c r="N25" s="83"/>
-      <c r="O25" s="83"/>
-      <c r="P25" s="83"/>
-      <c r="Q25" s="83"/>
-      <c r="R25" s="83"/>
-      <c r="S25" s="83"/>
-      <c r="T25" s="83"/>
-      <c r="U25" s="83"/>
-      <c r="V25" s="83"/>
-      <c r="W25" s="83"/>
-      <c r="X25" s="83"/>
+      <c r="A25" s="81"/>
+      <c r="B25" s="81"/>
+      <c r="C25" s="81"/>
+      <c r="D25" s="81"/>
+      <c r="E25" s="81"/>
+      <c r="F25" s="81"/>
+      <c r="G25" s="81"/>
+      <c r="H25" s="81"/>
+      <c r="I25" s="81"/>
+      <c r="J25" s="81"/>
+      <c r="K25" s="81"/>
+      <c r="L25" s="81"/>
+      <c r="M25" s="81"/>
+      <c r="N25" s="81"/>
+      <c r="O25" s="81"/>
+      <c r="P25" s="81"/>
+      <c r="Q25" s="81"/>
+      <c r="R25" s="81"/>
+      <c r="S25" s="81"/>
+      <c r="T25" s="81"/>
+      <c r="U25" s="81"/>
+      <c r="V25" s="81"/>
+      <c r="W25" s="81"/>
+      <c r="X25" s="81"/>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A26" s="83"/>
-      <c r="B26" s="83"/>
-      <c r="C26" s="83"/>
-      <c r="D26" s="83"/>
-      <c r="E26" s="83"/>
-      <c r="F26" s="83"/>
-      <c r="G26" s="83"/>
-      <c r="H26" s="83"/>
-      <c r="I26" s="83"/>
-      <c r="J26" s="83"/>
-      <c r="K26" s="83"/>
-      <c r="L26" s="83"/>
-      <c r="M26" s="83"/>
-      <c r="N26" s="83"/>
-      <c r="O26" s="83"/>
-      <c r="P26" s="83"/>
-      <c r="Q26" s="83"/>
-      <c r="R26" s="83"/>
-      <c r="S26" s="83"/>
-      <c r="T26" s="83"/>
-      <c r="U26" s="83"/>
-      <c r="V26" s="83"/>
-      <c r="W26" s="83"/>
-      <c r="X26" s="83"/>
+      <c r="A26" s="81"/>
+      <c r="B26" s="81"/>
+      <c r="C26" s="81"/>
+      <c r="D26" s="81"/>
+      <c r="E26" s="81"/>
+      <c r="F26" s="81"/>
+      <c r="G26" s="81"/>
+      <c r="H26" s="81"/>
+      <c r="I26" s="81"/>
+      <c r="J26" s="81"/>
+      <c r="K26" s="81"/>
+      <c r="L26" s="81"/>
+      <c r="M26" s="81"/>
+      <c r="N26" s="81"/>
+      <c r="O26" s="81"/>
+      <c r="P26" s="81"/>
+      <c r="Q26" s="81"/>
+      <c r="R26" s="81"/>
+      <c r="S26" s="81"/>
+      <c r="T26" s="81"/>
+      <c r="U26" s="81"/>
+      <c r="V26" s="81"/>
+      <c r="W26" s="81"/>
+      <c r="X26" s="81"/>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A27" s="83"/>
-      <c r="B27" s="83"/>
-      <c r="C27" s="83"/>
-      <c r="D27" s="83"/>
-      <c r="E27" s="83"/>
-      <c r="F27" s="83"/>
-      <c r="G27" s="83"/>
-      <c r="H27" s="83"/>
-      <c r="I27" s="83"/>
-      <c r="J27" s="83"/>
-      <c r="K27" s="83"/>
-      <c r="L27" s="83"/>
-      <c r="M27" s="83"/>
-      <c r="N27" s="83"/>
-      <c r="O27" s="83"/>
-      <c r="P27" s="83"/>
-      <c r="Q27" s="83"/>
-      <c r="R27" s="83"/>
-      <c r="S27" s="83"/>
-      <c r="T27" s="83"/>
-      <c r="U27" s="83"/>
-      <c r="V27" s="83"/>
-      <c r="W27" s="83"/>
-      <c r="X27" s="83"/>
+      <c r="A27" s="81"/>
+      <c r="B27" s="81"/>
+      <c r="C27" s="81"/>
+      <c r="D27" s="81"/>
+      <c r="E27" s="81"/>
+      <c r="F27" s="81"/>
+      <c r="G27" s="81"/>
+      <c r="H27" s="81"/>
+      <c r="I27" s="81"/>
+      <c r="J27" s="81"/>
+      <c r="K27" s="81"/>
+      <c r="L27" s="81"/>
+      <c r="M27" s="81"/>
+      <c r="N27" s="81"/>
+      <c r="O27" s="81"/>
+      <c r="P27" s="81"/>
+      <c r="Q27" s="81"/>
+      <c r="R27" s="81"/>
+      <c r="S27" s="81"/>
+      <c r="T27" s="81"/>
+      <c r="U27" s="81"/>
+      <c r="V27" s="81"/>
+      <c r="W27" s="81"/>
+      <c r="X27" s="81"/>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A28" s="83"/>
-      <c r="B28" s="83"/>
-      <c r="C28" s="83"/>
-      <c r="D28" s="83"/>
-      <c r="E28" s="83"/>
-      <c r="F28" s="83"/>
-      <c r="G28" s="83"/>
-      <c r="H28" s="83"/>
-      <c r="I28" s="83"/>
-      <c r="J28" s="83"/>
-      <c r="K28" s="83"/>
-      <c r="L28" s="83"/>
-      <c r="M28" s="83"/>
-      <c r="N28" s="83"/>
-      <c r="O28" s="83"/>
-      <c r="P28" s="83"/>
-      <c r="Q28" s="83"/>
-      <c r="R28" s="83"/>
-      <c r="S28" s="83"/>
-      <c r="T28" s="83"/>
-      <c r="U28" s="83"/>
-      <c r="V28" s="83"/>
-      <c r="W28" s="83"/>
-      <c r="X28" s="83"/>
+      <c r="A28" s="81"/>
+      <c r="B28" s="81"/>
+      <c r="C28" s="81"/>
+      <c r="D28" s="81"/>
+      <c r="E28" s="81"/>
+      <c r="F28" s="81"/>
+      <c r="G28" s="81"/>
+      <c r="H28" s="81"/>
+      <c r="I28" s="81"/>
+      <c r="J28" s="81"/>
+      <c r="K28" s="81"/>
+      <c r="L28" s="81"/>
+      <c r="M28" s="81"/>
+      <c r="N28" s="81"/>
+      <c r="O28" s="81"/>
+      <c r="P28" s="81"/>
+      <c r="Q28" s="81"/>
+      <c r="R28" s="81"/>
+      <c r="S28" s="81"/>
+      <c r="T28" s="81"/>
+      <c r="U28" s="81"/>
+      <c r="V28" s="81"/>
+      <c r="W28" s="81"/>
+      <c r="X28" s="81"/>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A29" s="83"/>
-      <c r="B29" s="83"/>
-      <c r="C29" s="83"/>
-      <c r="D29" s="83"/>
-      <c r="E29" s="83"/>
-      <c r="F29" s="83"/>
-      <c r="G29" s="83"/>
-      <c r="H29" s="83"/>
-      <c r="I29" s="83"/>
-      <c r="J29" s="83"/>
-      <c r="K29" s="83"/>
-      <c r="L29" s="83"/>
-      <c r="M29" s="83"/>
-      <c r="N29" s="83"/>
-      <c r="O29" s="83"/>
-      <c r="P29" s="83"/>
-      <c r="Q29" s="83"/>
-      <c r="R29" s="83"/>
-      <c r="S29" s="83"/>
-      <c r="T29" s="83"/>
-      <c r="U29" s="83"/>
-      <c r="V29" s="83"/>
-      <c r="W29" s="83"/>
-      <c r="X29" s="83"/>
+      <c r="A29" s="81"/>
+      <c r="B29" s="81"/>
+      <c r="C29" s="81"/>
+      <c r="D29" s="81"/>
+      <c r="E29" s="81"/>
+      <c r="F29" s="81"/>
+      <c r="G29" s="81"/>
+      <c r="H29" s="81"/>
+      <c r="I29" s="81"/>
+      <c r="J29" s="81"/>
+      <c r="K29" s="81"/>
+      <c r="L29" s="81"/>
+      <c r="M29" s="81"/>
+      <c r="N29" s="81"/>
+      <c r="O29" s="81"/>
+      <c r="P29" s="81"/>
+      <c r="Q29" s="81"/>
+      <c r="R29" s="81"/>
+      <c r="S29" s="81"/>
+      <c r="T29" s="81"/>
+      <c r="U29" s="81"/>
+      <c r="V29" s="81"/>
+      <c r="W29" s="81"/>
+      <c r="X29" s="81"/>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A30" s="83"/>
-      <c r="B30" s="83"/>
-      <c r="C30" s="83"/>
-      <c r="D30" s="83"/>
-      <c r="E30" s="83"/>
-      <c r="F30" s="83"/>
-      <c r="G30" s="83"/>
-      <c r="H30" s="83"/>
-      <c r="I30" s="83"/>
-      <c r="J30" s="83"/>
-      <c r="K30" s="83"/>
-      <c r="L30" s="83"/>
-      <c r="M30" s="83"/>
-      <c r="N30" s="83"/>
-      <c r="O30" s="83"/>
-      <c r="P30" s="83"/>
-      <c r="Q30" s="83"/>
-      <c r="R30" s="83"/>
-      <c r="S30" s="83"/>
-      <c r="T30" s="83"/>
-      <c r="U30" s="83"/>
-      <c r="V30" s="83"/>
-      <c r="W30" s="83"/>
-      <c r="X30" s="83"/>
+      <c r="A30" s="81"/>
+      <c r="B30" s="81"/>
+      <c r="C30" s="81"/>
+      <c r="D30" s="81"/>
+      <c r="E30" s="81"/>
+      <c r="F30" s="81"/>
+      <c r="G30" s="81"/>
+      <c r="H30" s="81"/>
+      <c r="I30" s="81"/>
+      <c r="J30" s="81"/>
+      <c r="K30" s="81"/>
+      <c r="L30" s="81"/>
+      <c r="M30" s="81"/>
+      <c r="N30" s="81"/>
+      <c r="O30" s="81"/>
+      <c r="P30" s="81"/>
+      <c r="Q30" s="81"/>
+      <c r="R30" s="81"/>
+      <c r="S30" s="81"/>
+      <c r="T30" s="81"/>
+      <c r="U30" s="81"/>
+      <c r="V30" s="81"/>
+      <c r="W30" s="81"/>
+      <c r="X30" s="81"/>
     </row>
     <row r="31" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A31" s="83"/>
-      <c r="B31" s="83"/>
-      <c r="C31" s="83"/>
-      <c r="D31" s="83"/>
-      <c r="E31" s="83"/>
-      <c r="F31" s="83"/>
-      <c r="G31" s="83"/>
-      <c r="H31" s="83"/>
-      <c r="I31" s="83"/>
-      <c r="J31" s="83"/>
-      <c r="K31" s="83"/>
-      <c r="L31" s="83"/>
-      <c r="M31" s="83"/>
-      <c r="N31" s="83"/>
-      <c r="O31" s="83"/>
-      <c r="P31" s="83"/>
-      <c r="Q31" s="83"/>
-      <c r="R31" s="83"/>
-      <c r="S31" s="83"/>
-      <c r="T31" s="83"/>
-      <c r="U31" s="83"/>
-      <c r="V31" s="83"/>
-      <c r="W31" s="83"/>
-      <c r="X31" s="83"/>
+      <c r="A31" s="81"/>
+      <c r="B31" s="81"/>
+      <c r="C31" s="81"/>
+      <c r="D31" s="81"/>
+      <c r="E31" s="81"/>
+      <c r="F31" s="81"/>
+      <c r="G31" s="81"/>
+      <c r="H31" s="81"/>
+      <c r="I31" s="81"/>
+      <c r="J31" s="81"/>
+      <c r="K31" s="81"/>
+      <c r="L31" s="81"/>
+      <c r="M31" s="81"/>
+      <c r="N31" s="81"/>
+      <c r="O31" s="81"/>
+      <c r="P31" s="81"/>
+      <c r="Q31" s="81"/>
+      <c r="R31" s="81"/>
+      <c r="S31" s="81"/>
+      <c r="T31" s="81"/>
+      <c r="U31" s="81"/>
+      <c r="V31" s="81"/>
+      <c r="W31" s="81"/>
+      <c r="X31" s="81"/>
     </row>
     <row r="32" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A32" s="83"/>
-      <c r="B32" s="83"/>
-      <c r="C32" s="83"/>
-      <c r="D32" s="83"/>
-      <c r="E32" s="83"/>
-      <c r="F32" s="83"/>
-      <c r="G32" s="83"/>
-      <c r="H32" s="83"/>
-      <c r="I32" s="83"/>
-      <c r="J32" s="83"/>
-      <c r="K32" s="83"/>
-      <c r="L32" s="83"/>
-      <c r="M32" s="83"/>
-      <c r="N32" s="83"/>
-      <c r="O32" s="83"/>
-      <c r="P32" s="83"/>
-      <c r="Q32" s="83"/>
-      <c r="R32" s="83"/>
-      <c r="S32" s="83"/>
-      <c r="T32" s="83"/>
-      <c r="U32" s="83"/>
-      <c r="V32" s="83"/>
-      <c r="W32" s="83"/>
-      <c r="X32" s="83"/>
+      <c r="A32" s="81"/>
+      <c r="B32" s="81"/>
+      <c r="C32" s="81"/>
+      <c r="D32" s="81"/>
+      <c r="E32" s="81"/>
+      <c r="F32" s="81"/>
+      <c r="G32" s="81"/>
+      <c r="H32" s="81"/>
+      <c r="I32" s="81"/>
+      <c r="J32" s="81"/>
+      <c r="K32" s="81"/>
+      <c r="L32" s="81"/>
+      <c r="M32" s="81"/>
+      <c r="N32" s="81"/>
+      <c r="O32" s="81"/>
+      <c r="P32" s="81"/>
+      <c r="Q32" s="81"/>
+      <c r="R32" s="81"/>
+      <c r="S32" s="81"/>
+      <c r="T32" s="81"/>
+      <c r="U32" s="81"/>
+      <c r="V32" s="81"/>
+      <c r="W32" s="81"/>
+      <c r="X32" s="81"/>
     </row>
     <row r="33" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A33" s="83"/>
-      <c r="B33" s="83"/>
-      <c r="C33" s="83"/>
-      <c r="D33" s="83"/>
-      <c r="E33" s="83"/>
-      <c r="F33" s="83"/>
-      <c r="G33" s="83"/>
-      <c r="H33" s="83"/>
-      <c r="I33" s="83"/>
-      <c r="J33" s="83"/>
-      <c r="K33" s="83"/>
-      <c r="L33" s="83"/>
-      <c r="M33" s="83"/>
-      <c r="N33" s="83"/>
-      <c r="O33" s="83"/>
-      <c r="P33" s="83"/>
-      <c r="Q33" s="83"/>
-      <c r="R33" s="83"/>
-      <c r="S33" s="83"/>
-      <c r="T33" s="83"/>
-      <c r="U33" s="83"/>
-      <c r="V33" s="83"/>
-      <c r="W33" s="83"/>
-      <c r="X33" s="83"/>
+      <c r="A33" s="81"/>
+      <c r="B33" s="81"/>
+      <c r="C33" s="81"/>
+      <c r="D33" s="81"/>
+      <c r="E33" s="81"/>
+      <c r="F33" s="81"/>
+      <c r="G33" s="81"/>
+      <c r="H33" s="81"/>
+      <c r="I33" s="81"/>
+      <c r="J33" s="81"/>
+      <c r="K33" s="81"/>
+      <c r="L33" s="81"/>
+      <c r="M33" s="81"/>
+      <c r="N33" s="81"/>
+      <c r="O33" s="81"/>
+      <c r="P33" s="81"/>
+      <c r="Q33" s="81"/>
+      <c r="R33" s="81"/>
+      <c r="S33" s="81"/>
+      <c r="T33" s="81"/>
+      <c r="U33" s="81"/>
+      <c r="V33" s="81"/>
+      <c r="W33" s="81"/>
+      <c r="X33" s="81"/>
     </row>
     <row r="34" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A34" s="83"/>
-      <c r="B34" s="83"/>
-      <c r="C34" s="83"/>
-      <c r="D34" s="83"/>
-      <c r="E34" s="83"/>
-      <c r="F34" s="83"/>
-      <c r="G34" s="83"/>
-      <c r="H34" s="83"/>
-      <c r="I34" s="83"/>
-      <c r="J34" s="83"/>
-      <c r="K34" s="83"/>
-      <c r="L34" s="83"/>
-      <c r="M34" s="83"/>
-      <c r="N34" s="83"/>
-      <c r="O34" s="83"/>
-      <c r="P34" s="83"/>
-      <c r="Q34" s="83"/>
-      <c r="R34" s="83"/>
-      <c r="S34" s="83"/>
-      <c r="T34" s="83"/>
-      <c r="U34" s="83"/>
-      <c r="V34" s="83"/>
-      <c r="W34" s="83"/>
-      <c r="X34" s="83"/>
+      <c r="A34" s="81"/>
+      <c r="B34" s="81"/>
+      <c r="C34" s="81"/>
+      <c r="D34" s="81"/>
+      <c r="E34" s="81"/>
+      <c r="F34" s="81"/>
+      <c r="G34" s="81"/>
+      <c r="H34" s="81"/>
+      <c r="I34" s="81"/>
+      <c r="J34" s="81"/>
+      <c r="K34" s="81"/>
+      <c r="L34" s="81"/>
+      <c r="M34" s="81"/>
+      <c r="N34" s="81"/>
+      <c r="O34" s="81"/>
+      <c r="P34" s="81"/>
+      <c r="Q34" s="81"/>
+      <c r="R34" s="81"/>
+      <c r="S34" s="81"/>
+      <c r="T34" s="81"/>
+      <c r="U34" s="81"/>
+      <c r="V34" s="81"/>
+      <c r="W34" s="81"/>
+      <c r="X34" s="81"/>
     </row>
     <row r="35" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A35" s="83"/>
-      <c r="B35" s="83"/>
-      <c r="C35" s="83"/>
-      <c r="D35" s="83"/>
-      <c r="E35" s="83"/>
-      <c r="F35" s="83"/>
-      <c r="G35" s="83"/>
-      <c r="H35" s="83"/>
-      <c r="I35" s="83"/>
-      <c r="J35" s="83"/>
-      <c r="K35" s="83"/>
-      <c r="L35" s="83"/>
-      <c r="M35" s="83"/>
-      <c r="N35" s="83"/>
-      <c r="O35" s="83"/>
-      <c r="P35" s="83"/>
-      <c r="Q35" s="83"/>
-      <c r="R35" s="83"/>
-      <c r="S35" s="83"/>
-      <c r="T35" s="83"/>
-      <c r="U35" s="83"/>
-      <c r="V35" s="83"/>
-      <c r="W35" s="83"/>
-      <c r="X35" s="83"/>
+      <c r="A35" s="81"/>
+      <c r="B35" s="81"/>
+      <c r="C35" s="81"/>
+      <c r="D35" s="81"/>
+      <c r="E35" s="81"/>
+      <c r="F35" s="81"/>
+      <c r="G35" s="81"/>
+      <c r="H35" s="81"/>
+      <c r="I35" s="81"/>
+      <c r="J35" s="81"/>
+      <c r="K35" s="81"/>
+      <c r="L35" s="81"/>
+      <c r="M35" s="81"/>
+      <c r="N35" s="81"/>
+      <c r="O35" s="81"/>
+      <c r="P35" s="81"/>
+      <c r="Q35" s="81"/>
+      <c r="R35" s="81"/>
+      <c r="S35" s="81"/>
+      <c r="T35" s="81"/>
+      <c r="U35" s="81"/>
+      <c r="V35" s="81"/>
+      <c r="W35" s="81"/>
+      <c r="X35" s="81"/>
     </row>
     <row r="36" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A36" s="83"/>
-      <c r="B36" s="83"/>
-      <c r="C36" s="83"/>
-      <c r="D36" s="83"/>
-      <c r="E36" s="83"/>
-      <c r="F36" s="83"/>
-      <c r="G36" s="83"/>
-      <c r="H36" s="83"/>
-      <c r="I36" s="83"/>
-      <c r="J36" s="83"/>
-      <c r="K36" s="83"/>
-      <c r="L36" s="83"/>
-      <c r="M36" s="83"/>
-      <c r="N36" s="83"/>
-      <c r="O36" s="83"/>
-      <c r="P36" s="83"/>
-      <c r="Q36" s="83"/>
-      <c r="R36" s="83"/>
-      <c r="S36" s="83"/>
-      <c r="T36" s="83"/>
-      <c r="U36" s="83"/>
-      <c r="V36" s="83"/>
-      <c r="W36" s="83"/>
-      <c r="X36" s="83"/>
+      <c r="A36" s="81"/>
+      <c r="B36" s="81"/>
+      <c r="C36" s="81"/>
+      <c r="D36" s="81"/>
+      <c r="E36" s="81"/>
+      <c r="F36" s="81"/>
+      <c r="G36" s="81"/>
+      <c r="H36" s="81"/>
+      <c r="I36" s="81"/>
+      <c r="J36" s="81"/>
+      <c r="K36" s="81"/>
+      <c r="L36" s="81"/>
+      <c r="M36" s="81"/>
+      <c r="N36" s="81"/>
+      <c r="O36" s="81"/>
+      <c r="P36" s="81"/>
+      <c r="Q36" s="81"/>
+      <c r="R36" s="81"/>
+      <c r="S36" s="81"/>
+      <c r="T36" s="81"/>
+      <c r="U36" s="81"/>
+      <c r="V36" s="81"/>
+      <c r="W36" s="81"/>
+      <c r="X36" s="81"/>
     </row>
     <row r="37" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A37" s="83"/>
-      <c r="B37" s="83"/>
-      <c r="C37" s="83"/>
-      <c r="D37" s="83"/>
-      <c r="E37" s="83"/>
-      <c r="F37" s="83"/>
-      <c r="G37" s="83"/>
-      <c r="H37" s="83"/>
-      <c r="I37" s="83"/>
-      <c r="J37" s="83"/>
-      <c r="K37" s="83"/>
-      <c r="L37" s="83"/>
-      <c r="M37" s="83"/>
-      <c r="N37" s="83"/>
-      <c r="O37" s="83"/>
-      <c r="P37" s="83"/>
-      <c r="Q37" s="83"/>
-      <c r="R37" s="83"/>
-      <c r="S37" s="83"/>
-      <c r="T37" s="83"/>
-      <c r="U37" s="83"/>
-      <c r="V37" s="83"/>
-      <c r="W37" s="83"/>
-      <c r="X37" s="83"/>
+      <c r="A37" s="81"/>
+      <c r="B37" s="81"/>
+      <c r="C37" s="81"/>
+      <c r="D37" s="81"/>
+      <c r="E37" s="81"/>
+      <c r="F37" s="81"/>
+      <c r="G37" s="81"/>
+      <c r="H37" s="81"/>
+      <c r="I37" s="81"/>
+      <c r="J37" s="81"/>
+      <c r="K37" s="81"/>
+      <c r="L37" s="81"/>
+      <c r="M37" s="81"/>
+      <c r="N37" s="81"/>
+      <c r="O37" s="81"/>
+      <c r="P37" s="81"/>
+      <c r="Q37" s="81"/>
+      <c r="R37" s="81"/>
+      <c r="S37" s="81"/>
+      <c r="T37" s="81"/>
+      <c r="U37" s="81"/>
+      <c r="V37" s="81"/>
+      <c r="W37" s="81"/>
+      <c r="X37" s="81"/>
     </row>
     <row r="38" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A38" s="83"/>
-      <c r="B38" s="83"/>
-      <c r="C38" s="83"/>
-      <c r="D38" s="83"/>
-      <c r="E38" s="83"/>
-      <c r="F38" s="83"/>
-      <c r="G38" s="83"/>
-      <c r="H38" s="83"/>
-      <c r="I38" s="83"/>
-      <c r="J38" s="83"/>
-      <c r="K38" s="83"/>
-      <c r="L38" s="83"/>
-      <c r="M38" s="83"/>
-      <c r="N38" s="83"/>
-      <c r="O38" s="83"/>
-      <c r="P38" s="83"/>
-      <c r="Q38" s="83"/>
-      <c r="R38" s="83"/>
-      <c r="S38" s="83"/>
-      <c r="T38" s="83"/>
-      <c r="U38" s="83"/>
-      <c r="V38" s="83"/>
-      <c r="W38" s="83"/>
-      <c r="X38" s="83"/>
+      <c r="A38" s="81"/>
+      <c r="B38" s="81"/>
+      <c r="C38" s="81"/>
+      <c r="D38" s="81"/>
+      <c r="E38" s="81"/>
+      <c r="F38" s="81"/>
+      <c r="G38" s="81"/>
+      <c r="H38" s="81"/>
+      <c r="I38" s="81"/>
+      <c r="J38" s="81"/>
+      <c r="K38" s="81"/>
+      <c r="L38" s="81"/>
+      <c r="M38" s="81"/>
+      <c r="N38" s="81"/>
+      <c r="O38" s="81"/>
+      <c r="P38" s="81"/>
+      <c r="Q38" s="81"/>
+      <c r="R38" s="81"/>
+      <c r="S38" s="81"/>
+      <c r="T38" s="81"/>
+      <c r="U38" s="81"/>
+      <c r="V38" s="81"/>
+      <c r="W38" s="81"/>
+      <c r="X38" s="81"/>
     </row>
     <row r="39" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A39" s="83"/>
-      <c r="B39" s="83"/>
-      <c r="C39" s="83"/>
-      <c r="D39" s="83"/>
-      <c r="E39" s="83"/>
-      <c r="F39" s="83"/>
-      <c r="G39" s="83"/>
-      <c r="H39" s="83"/>
-      <c r="I39" s="83"/>
-      <c r="J39" s="83"/>
-      <c r="K39" s="83"/>
-      <c r="L39" s="83"/>
-      <c r="M39" s="83"/>
-      <c r="N39" s="83"/>
-      <c r="O39" s="83"/>
-      <c r="P39" s="83"/>
-      <c r="Q39" s="83"/>
-      <c r="R39" s="83"/>
-      <c r="S39" s="83"/>
-      <c r="T39" s="83"/>
-      <c r="U39" s="83"/>
-      <c r="V39" s="83"/>
-      <c r="W39" s="83"/>
-      <c r="X39" s="83"/>
+      <c r="A39" s="81"/>
+      <c r="B39" s="81"/>
+      <c r="C39" s="81"/>
+      <c r="D39" s="81"/>
+      <c r="E39" s="81"/>
+      <c r="F39" s="81"/>
+      <c r="G39" s="81"/>
+      <c r="H39" s="81"/>
+      <c r="I39" s="81"/>
+      <c r="J39" s="81"/>
+      <c r="K39" s="81"/>
+      <c r="L39" s="81"/>
+      <c r="M39" s="81"/>
+      <c r="N39" s="81"/>
+      <c r="O39" s="81"/>
+      <c r="P39" s="81"/>
+      <c r="Q39" s="81"/>
+      <c r="R39" s="81"/>
+      <c r="S39" s="81"/>
+      <c r="T39" s="81"/>
+      <c r="U39" s="81"/>
+      <c r="V39" s="81"/>
+      <c r="W39" s="81"/>
+      <c r="X39" s="81"/>
     </row>
     <row r="40" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A40" s="83"/>
-      <c r="B40" s="83"/>
-      <c r="C40" s="83"/>
-      <c r="D40" s="83"/>
-      <c r="E40" s="83"/>
-      <c r="F40" s="83"/>
-      <c r="G40" s="83"/>
-      <c r="H40" s="83"/>
-      <c r="I40" s="83"/>
-      <c r="J40" s="83"/>
-      <c r="K40" s="83"/>
-      <c r="L40" s="83"/>
-      <c r="M40" s="83"/>
-      <c r="N40" s="83"/>
-      <c r="O40" s="83"/>
-      <c r="P40" s="83"/>
-      <c r="Q40" s="83"/>
-      <c r="R40" s="83"/>
-      <c r="S40" s="83"/>
-      <c r="T40" s="83"/>
-      <c r="U40" s="83"/>
-      <c r="V40" s="83"/>
-      <c r="W40" s="83"/>
-      <c r="X40" s="83"/>
+      <c r="A40" s="81"/>
+      <c r="B40" s="81"/>
+      <c r="C40" s="81"/>
+      <c r="D40" s="81"/>
+      <c r="E40" s="81"/>
+      <c r="F40" s="81"/>
+      <c r="G40" s="81"/>
+      <c r="H40" s="81"/>
+      <c r="I40" s="81"/>
+      <c r="J40" s="81"/>
+      <c r="K40" s="81"/>
+      <c r="L40" s="81"/>
+      <c r="M40" s="81"/>
+      <c r="N40" s="81"/>
+      <c r="O40" s="81"/>
+      <c r="P40" s="81"/>
+      <c r="Q40" s="81"/>
+      <c r="R40" s="81"/>
+      <c r="S40" s="81"/>
+      <c r="T40" s="81"/>
+      <c r="U40" s="81"/>
+      <c r="V40" s="81"/>
+      <c r="W40" s="81"/>
+      <c r="X40" s="81"/>
     </row>
     <row r="41" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A41" s="83"/>
-      <c r="B41" s="83"/>
-      <c r="C41" s="83"/>
-      <c r="D41" s="83"/>
-      <c r="E41" s="83"/>
-      <c r="F41" s="83"/>
-      <c r="G41" s="83"/>
-      <c r="H41" s="83"/>
-      <c r="I41" s="83"/>
-      <c r="J41" s="83"/>
-      <c r="K41" s="83"/>
-      <c r="L41" s="83"/>
-      <c r="M41" s="83"/>
-      <c r="N41" s="83"/>
-      <c r="O41" s="83"/>
-      <c r="P41" s="83"/>
-      <c r="Q41" s="83"/>
-      <c r="R41" s="83"/>
-      <c r="S41" s="83"/>
-      <c r="T41" s="83"/>
-      <c r="U41" s="83"/>
-      <c r="V41" s="83"/>
-      <c r="W41" s="83"/>
-      <c r="X41" s="83"/>
+      <c r="A41" s="81"/>
+      <c r="B41" s="81"/>
+      <c r="C41" s="81"/>
+      <c r="D41" s="81"/>
+      <c r="E41" s="81"/>
+      <c r="F41" s="81"/>
+      <c r="G41" s="81"/>
+      <c r="H41" s="81"/>
+      <c r="I41" s="81"/>
+      <c r="J41" s="81"/>
+      <c r="K41" s="81"/>
+      <c r="L41" s="81"/>
+      <c r="M41" s="81"/>
+      <c r="N41" s="81"/>
+      <c r="O41" s="81"/>
+      <c r="P41" s="81"/>
+      <c r="Q41" s="81"/>
+      <c r="R41" s="81"/>
+      <c r="S41" s="81"/>
+      <c r="T41" s="81"/>
+      <c r="U41" s="81"/>
+      <c r="V41" s="81"/>
+      <c r="W41" s="81"/>
+      <c r="X41" s="81"/>
     </row>
     <row r="42" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A42" s="83"/>
-      <c r="B42" s="83"/>
-      <c r="C42" s="83"/>
-      <c r="D42" s="83"/>
-      <c r="E42" s="83"/>
-      <c r="F42" s="83"/>
-      <c r="G42" s="83"/>
-      <c r="H42" s="83"/>
-      <c r="I42" s="83"/>
-      <c r="J42" s="83"/>
-      <c r="K42" s="83"/>
-      <c r="L42" s="83"/>
-      <c r="M42" s="83"/>
-      <c r="N42" s="83"/>
-      <c r="O42" s="83"/>
-      <c r="P42" s="83"/>
-      <c r="Q42" s="83"/>
-      <c r="R42" s="83"/>
-      <c r="S42" s="83"/>
-      <c r="T42" s="83"/>
-      <c r="U42" s="83"/>
-      <c r="V42" s="83"/>
-      <c r="W42" s="83"/>
-      <c r="X42" s="83"/>
+      <c r="A42" s="81"/>
+      <c r="B42" s="81"/>
+      <c r="C42" s="81"/>
+      <c r="D42" s="81"/>
+      <c r="E42" s="81"/>
+      <c r="F42" s="81"/>
+      <c r="G42" s="81"/>
+      <c r="H42" s="81"/>
+      <c r="I42" s="81"/>
+      <c r="J42" s="81"/>
+      <c r="K42" s="81"/>
+      <c r="L42" s="81"/>
+      <c r="M42" s="81"/>
+      <c r="N42" s="81"/>
+      <c r="O42" s="81"/>
+      <c r="P42" s="81"/>
+      <c r="Q42" s="81"/>
+      <c r="R42" s="81"/>
+      <c r="S42" s="81"/>
+      <c r="T42" s="81"/>
+      <c r="U42" s="81"/>
+      <c r="V42" s="81"/>
+      <c r="W42" s="81"/>
+      <c r="X42" s="81"/>
     </row>
     <row r="43" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A43" s="83"/>
-      <c r="B43" s="83"/>
-      <c r="C43" s="83"/>
-      <c r="D43" s="83"/>
-      <c r="E43" s="83"/>
-      <c r="F43" s="83"/>
-      <c r="G43" s="83"/>
-      <c r="H43" s="83"/>
-      <c r="I43" s="83"/>
-      <c r="J43" s="83"/>
-      <c r="K43" s="83"/>
-      <c r="L43" s="83"/>
-      <c r="M43" s="83"/>
-      <c r="N43" s="83"/>
-      <c r="O43" s="83"/>
-      <c r="P43" s="83"/>
-      <c r="Q43" s="83"/>
-      <c r="R43" s="83"/>
-      <c r="S43" s="83"/>
-      <c r="T43" s="83"/>
-      <c r="U43" s="83"/>
-      <c r="V43" s="83"/>
-      <c r="W43" s="83"/>
-      <c r="X43" s="83"/>
+      <c r="A43" s="81"/>
+      <c r="B43" s="81"/>
+      <c r="C43" s="81"/>
+      <c r="D43" s="81"/>
+      <c r="E43" s="81"/>
+      <c r="F43" s="81"/>
+      <c r="G43" s="81"/>
+      <c r="H43" s="81"/>
+      <c r="I43" s="81"/>
+      <c r="J43" s="81"/>
+      <c r="K43" s="81"/>
+      <c r="L43" s="81"/>
+      <c r="M43" s="81"/>
+      <c r="N43" s="81"/>
+      <c r="O43" s="81"/>
+      <c r="P43" s="81"/>
+      <c r="Q43" s="81"/>
+      <c r="R43" s="81"/>
+      <c r="S43" s="81"/>
+      <c r="T43" s="81"/>
+      <c r="U43" s="81"/>
+      <c r="V43" s="81"/>
+      <c r="W43" s="81"/>
+      <c r="X43" s="81"/>
     </row>
     <row r="44" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A44" s="83"/>
-      <c r="B44" s="83"/>
-      <c r="C44" s="83"/>
-      <c r="D44" s="83"/>
-      <c r="E44" s="83"/>
-      <c r="F44" s="83"/>
-      <c r="G44" s="83"/>
-      <c r="H44" s="83"/>
-      <c r="I44" s="83"/>
-      <c r="J44" s="83"/>
-      <c r="K44" s="83"/>
-      <c r="L44" s="83"/>
-      <c r="M44" s="83"/>
-      <c r="N44" s="83"/>
-      <c r="O44" s="83"/>
-      <c r="P44" s="83"/>
-      <c r="Q44" s="83"/>
-      <c r="R44" s="83"/>
-      <c r="S44" s="83"/>
-      <c r="T44" s="83"/>
-      <c r="U44" s="83"/>
-      <c r="V44" s="83"/>
-      <c r="W44" s="83"/>
-      <c r="X44" s="83"/>
+      <c r="A44" s="81"/>
+      <c r="B44" s="81"/>
+      <c r="C44" s="81"/>
+      <c r="D44" s="81"/>
+      <c r="E44" s="81"/>
+      <c r="F44" s="81"/>
+      <c r="G44" s="81"/>
+      <c r="H44" s="81"/>
+      <c r="I44" s="81"/>
+      <c r="J44" s="81"/>
+      <c r="K44" s="81"/>
+      <c r="L44" s="81"/>
+      <c r="M44" s="81"/>
+      <c r="N44" s="81"/>
+      <c r="O44" s="81"/>
+      <c r="P44" s="81"/>
+      <c r="Q44" s="81"/>
+      <c r="R44" s="81"/>
+      <c r="S44" s="81"/>
+      <c r="T44" s="81"/>
+      <c r="U44" s="81"/>
+      <c r="V44" s="81"/>
+      <c r="W44" s="81"/>
+      <c r="X44" s="81"/>
     </row>
     <row r="45" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A45" s="83"/>
-      <c r="B45" s="83"/>
-      <c r="C45" s="83"/>
-      <c r="D45" s="83"/>
-      <c r="E45" s="83"/>
-      <c r="F45" s="83"/>
-      <c r="G45" s="83"/>
-      <c r="H45" s="83"/>
-      <c r="I45" s="83"/>
-      <c r="J45" s="83"/>
-      <c r="K45" s="83"/>
-      <c r="L45" s="83"/>
-      <c r="M45" s="83"/>
-      <c r="N45" s="83"/>
-      <c r="O45" s="83"/>
-      <c r="P45" s="83"/>
-      <c r="Q45" s="83"/>
-      <c r="R45" s="83"/>
-      <c r="S45" s="83"/>
-      <c r="T45" s="83"/>
-      <c r="U45" s="83"/>
-      <c r="V45" s="83"/>
-      <c r="W45" s="83"/>
-      <c r="X45" s="83"/>
+      <c r="A45" s="81"/>
+      <c r="B45" s="81"/>
+      <c r="C45" s="81"/>
+      <c r="D45" s="81"/>
+      <c r="E45" s="81"/>
+      <c r="F45" s="81"/>
+      <c r="G45" s="81"/>
+      <c r="H45" s="81"/>
+      <c r="I45" s="81"/>
+      <c r="J45" s="81"/>
+      <c r="K45" s="81"/>
+      <c r="L45" s="81"/>
+      <c r="M45" s="81"/>
+      <c r="N45" s="81"/>
+      <c r="O45" s="81"/>
+      <c r="P45" s="81"/>
+      <c r="Q45" s="81"/>
+      <c r="R45" s="81"/>
+      <c r="S45" s="81"/>
+      <c r="T45" s="81"/>
+      <c r="U45" s="81"/>
+      <c r="V45" s="81"/>
+      <c r="W45" s="81"/>
+      <c r="X45" s="81"/>
     </row>
     <row r="46" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A46" s="83"/>
-      <c r="B46" s="83"/>
-      <c r="C46" s="83"/>
-      <c r="D46" s="83"/>
-      <c r="E46" s="83"/>
-      <c r="F46" s="83"/>
-      <c r="G46" s="83"/>
-      <c r="H46" s="83"/>
-      <c r="I46" s="83"/>
-      <c r="J46" s="83"/>
-      <c r="K46" s="83"/>
-      <c r="L46" s="83"/>
-      <c r="M46" s="83"/>
-      <c r="N46" s="83"/>
-      <c r="O46" s="83"/>
-      <c r="P46" s="83"/>
-      <c r="Q46" s="83"/>
-      <c r="R46" s="83"/>
-      <c r="S46" s="83"/>
-      <c r="T46" s="83"/>
-      <c r="U46" s="83"/>
-      <c r="V46" s="83"/>
-      <c r="W46" s="83"/>
-      <c r="X46" s="83"/>
+      <c r="A46" s="81"/>
+      <c r="B46" s="81"/>
+      <c r="C46" s="81"/>
+      <c r="D46" s="81"/>
+      <c r="E46" s="81"/>
+      <c r="F46" s="81"/>
+      <c r="G46" s="81"/>
+      <c r="H46" s="81"/>
+      <c r="I46" s="81"/>
+      <c r="J46" s="81"/>
+      <c r="K46" s="81"/>
+      <c r="L46" s="81"/>
+      <c r="M46" s="81"/>
+      <c r="N46" s="81"/>
+      <c r="O46" s="81"/>
+      <c r="P46" s="81"/>
+      <c r="Q46" s="81"/>
+      <c r="R46" s="81"/>
+      <c r="S46" s="81"/>
+      <c r="T46" s="81"/>
+      <c r="U46" s="81"/>
+      <c r="V46" s="81"/>
+      <c r="W46" s="81"/>
+      <c r="X46" s="81"/>
     </row>
     <row r="47" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A47" s="83"/>
-      <c r="B47" s="83"/>
-      <c r="C47" s="83"/>
-      <c r="D47" s="83"/>
-      <c r="E47" s="83"/>
-      <c r="F47" s="83"/>
-      <c r="G47" s="83"/>
-      <c r="H47" s="83"/>
-      <c r="I47" s="83"/>
-      <c r="J47" s="83"/>
-      <c r="K47" s="83"/>
-      <c r="L47" s="83"/>
-      <c r="M47" s="83"/>
-      <c r="N47" s="83"/>
-      <c r="O47" s="83"/>
-      <c r="P47" s="83"/>
-      <c r="Q47" s="83"/>
-      <c r="R47" s="83"/>
-      <c r="S47" s="83"/>
-      <c r="T47" s="83"/>
-      <c r="U47" s="83"/>
-      <c r="V47" s="83"/>
-      <c r="W47" s="83"/>
-      <c r="X47" s="83"/>
+      <c r="A47" s="81"/>
+      <c r="B47" s="81"/>
+      <c r="C47" s="81"/>
+      <c r="D47" s="81"/>
+      <c r="E47" s="81"/>
+      <c r="F47" s="81"/>
+      <c r="G47" s="81"/>
+      <c r="H47" s="81"/>
+      <c r="I47" s="81"/>
+      <c r="J47" s="81"/>
+      <c r="K47" s="81"/>
+      <c r="L47" s="81"/>
+      <c r="M47" s="81"/>
+      <c r="N47" s="81"/>
+      <c r="O47" s="81"/>
+      <c r="P47" s="81"/>
+      <c r="Q47" s="81"/>
+      <c r="R47" s="81"/>
+      <c r="S47" s="81"/>
+      <c r="T47" s="81"/>
+      <c r="U47" s="81"/>
+      <c r="V47" s="81"/>
+      <c r="W47" s="81"/>
+      <c r="X47" s="81"/>
     </row>
     <row r="48" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A48" s="83"/>
-      <c r="B48" s="83"/>
-      <c r="C48" s="83"/>
-      <c r="D48" s="83"/>
-      <c r="E48" s="83"/>
-      <c r="F48" s="83"/>
-      <c r="G48" s="83"/>
-      <c r="H48" s="83"/>
-      <c r="I48" s="83"/>
-      <c r="J48" s="83"/>
-      <c r="K48" s="83"/>
-      <c r="L48" s="83"/>
-      <c r="M48" s="83"/>
-      <c r="N48" s="83"/>
-      <c r="O48" s="83"/>
-      <c r="P48" s="83"/>
-      <c r="Q48" s="83"/>
-      <c r="R48" s="83"/>
-      <c r="S48" s="83"/>
-      <c r="T48" s="83"/>
-      <c r="U48" s="83"/>
-      <c r="V48" s="83"/>
-      <c r="W48" s="83"/>
-      <c r="X48" s="83"/>
+      <c r="A48" s="81"/>
+      <c r="B48" s="81"/>
+      <c r="C48" s="81"/>
+      <c r="D48" s="81"/>
+      <c r="E48" s="81"/>
+      <c r="F48" s="81"/>
+      <c r="G48" s="81"/>
+      <c r="H48" s="81"/>
+      <c r="I48" s="81"/>
+      <c r="J48" s="81"/>
+      <c r="K48" s="81"/>
+      <c r="L48" s="81"/>
+      <c r="M48" s="81"/>
+      <c r="N48" s="81"/>
+      <c r="O48" s="81"/>
+      <c r="P48" s="81"/>
+      <c r="Q48" s="81"/>
+      <c r="R48" s="81"/>
+      <c r="S48" s="81"/>
+      <c r="T48" s="81"/>
+      <c r="U48" s="81"/>
+      <c r="V48" s="81"/>
+      <c r="W48" s="81"/>
+      <c r="X48" s="81"/>
     </row>
     <row r="49" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A49" s="83"/>
-      <c r="B49" s="83"/>
-      <c r="C49" s="83"/>
-      <c r="D49" s="83"/>
-      <c r="E49" s="83"/>
-      <c r="F49" s="83"/>
-      <c r="G49" s="83"/>
-      <c r="H49" s="83"/>
-      <c r="I49" s="83"/>
-      <c r="J49" s="83"/>
-      <c r="K49" s="83"/>
-      <c r="L49" s="83"/>
-      <c r="M49" s="83"/>
-      <c r="N49" s="83"/>
-      <c r="O49" s="83"/>
-      <c r="P49" s="83"/>
-      <c r="Q49" s="83"/>
-      <c r="R49" s="83"/>
-      <c r="S49" s="83"/>
-      <c r="T49" s="83"/>
-      <c r="U49" s="83"/>
-      <c r="V49" s="83"/>
-      <c r="W49" s="83"/>
-      <c r="X49" s="83"/>
+      <c r="A49" s="81"/>
+      <c r="B49" s="81"/>
+      <c r="C49" s="81"/>
+      <c r="D49" s="81"/>
+      <c r="E49" s="81"/>
+      <c r="F49" s="81"/>
+      <c r="G49" s="81"/>
+      <c r="H49" s="81"/>
+      <c r="I49" s="81"/>
+      <c r="J49" s="81"/>
+      <c r="K49" s="81"/>
+      <c r="L49" s="81"/>
+      <c r="M49" s="81"/>
+      <c r="N49" s="81"/>
+      <c r="O49" s="81"/>
+      <c r="P49" s="81"/>
+      <c r="Q49" s="81"/>
+      <c r="R49" s="81"/>
+      <c r="S49" s="81"/>
+      <c r="T49" s="81"/>
+      <c r="U49" s="81"/>
+      <c r="V49" s="81"/>
+      <c r="W49" s="81"/>
+      <c r="X49" s="81"/>
     </row>
     <row r="50" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A50" s="83"/>
-      <c r="B50" s="83"/>
-      <c r="C50" s="83"/>
-      <c r="D50" s="83"/>
-      <c r="E50" s="83"/>
-      <c r="F50" s="83"/>
-      <c r="G50" s="83"/>
-      <c r="H50" s="83"/>
-      <c r="I50" s="83"/>
-      <c r="J50" s="83"/>
-      <c r="K50" s="83"/>
-      <c r="L50" s="83"/>
-      <c r="M50" s="83"/>
-      <c r="N50" s="83"/>
-      <c r="O50" s="83"/>
-      <c r="P50" s="83"/>
-      <c r="Q50" s="83"/>
-      <c r="R50" s="83"/>
-      <c r="S50" s="83"/>
-      <c r="T50" s="83"/>
-      <c r="U50" s="83"/>
-      <c r="V50" s="83"/>
-      <c r="W50" s="83"/>
-      <c r="X50" s="83"/>
+      <c r="A50" s="81"/>
+      <c r="B50" s="81"/>
+      <c r="C50" s="81"/>
+      <c r="D50" s="81"/>
+      <c r="E50" s="81"/>
+      <c r="F50" s="81"/>
+      <c r="G50" s="81"/>
+      <c r="H50" s="81"/>
+      <c r="I50" s="81"/>
+      <c r="J50" s="81"/>
+      <c r="K50" s="81"/>
+      <c r="L50" s="81"/>
+      <c r="M50" s="81"/>
+      <c r="N50" s="81"/>
+      <c r="O50" s="81"/>
+      <c r="P50" s="81"/>
+      <c r="Q50" s="81"/>
+      <c r="R50" s="81"/>
+      <c r="S50" s="81"/>
+      <c r="T50" s="81"/>
+      <c r="U50" s="81"/>
+      <c r="V50" s="81"/>
+      <c r="W50" s="81"/>
+      <c r="X50" s="81"/>
     </row>
     <row r="51" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A51" s="83"/>
-      <c r="B51" s="83"/>
-      <c r="C51" s="83"/>
-      <c r="D51" s="83"/>
-      <c r="E51" s="83"/>
-      <c r="F51" s="83"/>
-      <c r="G51" s="83"/>
-      <c r="H51" s="83"/>
-      <c r="I51" s="83"/>
-      <c r="J51" s="83"/>
-      <c r="K51" s="83"/>
-      <c r="L51" s="83"/>
-      <c r="M51" s="83"/>
-      <c r="N51" s="83"/>
-      <c r="O51" s="83"/>
-      <c r="P51" s="83"/>
-      <c r="Q51" s="83"/>
-      <c r="R51" s="83"/>
-      <c r="S51" s="83"/>
-      <c r="T51" s="83"/>
-      <c r="U51" s="83"/>
-      <c r="V51" s="83"/>
-      <c r="W51" s="83"/>
-      <c r="X51" s="83"/>
+      <c r="A51" s="81"/>
+      <c r="B51" s="81"/>
+      <c r="C51" s="81"/>
+      <c r="D51" s="81"/>
+      <c r="E51" s="81"/>
+      <c r="F51" s="81"/>
+      <c r="G51" s="81"/>
+      <c r="H51" s="81"/>
+      <c r="I51" s="81"/>
+      <c r="J51" s="81"/>
+      <c r="K51" s="81"/>
+      <c r="L51" s="81"/>
+      <c r="M51" s="81"/>
+      <c r="N51" s="81"/>
+      <c r="O51" s="81"/>
+      <c r="P51" s="81"/>
+      <c r="Q51" s="81"/>
+      <c r="R51" s="81"/>
+      <c r="S51" s="81"/>
+      <c r="T51" s="81"/>
+      <c r="U51" s="81"/>
+      <c r="V51" s="81"/>
+      <c r="W51" s="81"/>
+      <c r="X51" s="81"/>
     </row>
     <row r="52" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A52" s="83"/>
-      <c r="B52" s="83"/>
-      <c r="C52" s="83"/>
-      <c r="D52" s="83"/>
-      <c r="E52" s="83"/>
-      <c r="F52" s="83"/>
-      <c r="G52" s="83"/>
-      <c r="H52" s="83"/>
-      <c r="I52" s="83"/>
-      <c r="J52" s="83"/>
-      <c r="K52" s="83"/>
-      <c r="L52" s="83"/>
-      <c r="M52" s="83"/>
-      <c r="N52" s="83"/>
-      <c r="O52" s="83"/>
-      <c r="P52" s="83"/>
-      <c r="Q52" s="83"/>
-      <c r="R52" s="83"/>
-      <c r="S52" s="83"/>
-      <c r="T52" s="83"/>
-      <c r="U52" s="83"/>
-      <c r="V52" s="83"/>
-      <c r="W52" s="83"/>
-      <c r="X52" s="83"/>
+      <c r="A52" s="81"/>
+      <c r="B52" s="81"/>
+      <c r="C52" s="81"/>
+      <c r="D52" s="81"/>
+      <c r="E52" s="81"/>
+      <c r="F52" s="81"/>
+      <c r="G52" s="81"/>
+      <c r="H52" s="81"/>
+      <c r="I52" s="81"/>
+      <c r="J52" s="81"/>
+      <c r="K52" s="81"/>
+      <c r="L52" s="81"/>
+      <c r="M52" s="81"/>
+      <c r="N52" s="81"/>
+      <c r="O52" s="81"/>
+      <c r="P52" s="81"/>
+      <c r="Q52" s="81"/>
+      <c r="R52" s="81"/>
+      <c r="S52" s="81"/>
+      <c r="T52" s="81"/>
+      <c r="U52" s="81"/>
+      <c r="V52" s="81"/>
+      <c r="W52" s="81"/>
+      <c r="X52" s="81"/>
     </row>
     <row r="53" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A53" s="83"/>
-      <c r="B53" s="83"/>
-      <c r="C53" s="83"/>
-      <c r="D53" s="83"/>
-      <c r="E53" s="83"/>
-      <c r="F53" s="83"/>
-      <c r="G53" s="83"/>
-      <c r="H53" s="83"/>
-      <c r="I53" s="83"/>
-      <c r="J53" s="83"/>
-      <c r="K53" s="83"/>
-      <c r="L53" s="83"/>
-      <c r="M53" s="83"/>
-      <c r="N53" s="83"/>
-      <c r="O53" s="83"/>
-      <c r="P53" s="83"/>
-      <c r="Q53" s="83"/>
-      <c r="R53" s="83"/>
-      <c r="S53" s="83"/>
-      <c r="T53" s="83"/>
-      <c r="U53" s="83"/>
-      <c r="V53" s="83"/>
-      <c r="W53" s="83"/>
-      <c r="X53" s="83"/>
+      <c r="A53" s="81"/>
+      <c r="B53" s="81"/>
+      <c r="C53" s="81"/>
+      <c r="D53" s="81"/>
+      <c r="E53" s="81"/>
+      <c r="F53" s="81"/>
+      <c r="G53" s="81"/>
+      <c r="H53" s="81"/>
+      <c r="I53" s="81"/>
+      <c r="J53" s="81"/>
+      <c r="K53" s="81"/>
+      <c r="L53" s="81"/>
+      <c r="M53" s="81"/>
+      <c r="N53" s="81"/>
+      <c r="O53" s="81"/>
+      <c r="P53" s="81"/>
+      <c r="Q53" s="81"/>
+      <c r="R53" s="81"/>
+      <c r="S53" s="81"/>
+      <c r="T53" s="81"/>
+      <c r="U53" s="81"/>
+      <c r="V53" s="81"/>
+      <c r="W53" s="81"/>
+      <c r="X53" s="81"/>
     </row>
     <row r="54" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A54" s="83"/>
-      <c r="B54" s="83"/>
-      <c r="C54" s="83"/>
-      <c r="D54" s="83"/>
-      <c r="E54" s="83"/>
-      <c r="F54" s="83"/>
-      <c r="G54" s="83"/>
-      <c r="H54" s="83"/>
-      <c r="I54" s="83"/>
-      <c r="J54" s="83"/>
-      <c r="K54" s="83"/>
-      <c r="L54" s="83"/>
-      <c r="M54" s="83"/>
-      <c r="N54" s="83"/>
-      <c r="O54" s="83"/>
-      <c r="P54" s="83"/>
-      <c r="Q54" s="83"/>
-      <c r="R54" s="83"/>
-      <c r="S54" s="83"/>
-      <c r="T54" s="83"/>
-      <c r="U54" s="83"/>
-      <c r="V54" s="83"/>
-      <c r="W54" s="83"/>
-      <c r="X54" s="83"/>
+      <c r="A54" s="81"/>
+      <c r="B54" s="81"/>
+      <c r="C54" s="81"/>
+      <c r="D54" s="81"/>
+      <c r="E54" s="81"/>
+      <c r="F54" s="81"/>
+      <c r="G54" s="81"/>
+      <c r="H54" s="81"/>
+      <c r="I54" s="81"/>
+      <c r="J54" s="81"/>
+      <c r="K54" s="81"/>
+      <c r="L54" s="81"/>
+      <c r="M54" s="81"/>
+      <c r="N54" s="81"/>
+      <c r="O54" s="81"/>
+      <c r="P54" s="81"/>
+      <c r="Q54" s="81"/>
+      <c r="R54" s="81"/>
+      <c r="S54" s="81"/>
+      <c r="T54" s="81"/>
+      <c r="U54" s="81"/>
+      <c r="V54" s="81"/>
+      <c r="W54" s="81"/>
+      <c r="X54" s="81"/>
     </row>
     <row r="55" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A55" s="83"/>
-      <c r="B55" s="83"/>
-      <c r="C55" s="83"/>
-      <c r="D55" s="83"/>
-      <c r="E55" s="83"/>
-      <c r="F55" s="83"/>
-      <c r="G55" s="83"/>
-      <c r="H55" s="83"/>
-      <c r="I55" s="83"/>
-      <c r="J55" s="83"/>
-      <c r="K55" s="83"/>
-      <c r="L55" s="83"/>
-      <c r="M55" s="83"/>
-      <c r="N55" s="83"/>
-      <c r="O55" s="83"/>
-      <c r="P55" s="83"/>
-      <c r="Q55" s="83"/>
-      <c r="R55" s="83"/>
-      <c r="S55" s="83"/>
-      <c r="T55" s="83"/>
-      <c r="U55" s="83"/>
-      <c r="V55" s="83"/>
-      <c r="W55" s="83"/>
-      <c r="X55" s="83"/>
+      <c r="A55" s="81"/>
+      <c r="B55" s="81"/>
+      <c r="C55" s="81"/>
+      <c r="D55" s="81"/>
+      <c r="E55" s="81"/>
+      <c r="F55" s="81"/>
+      <c r="G55" s="81"/>
+      <c r="H55" s="81"/>
+      <c r="I55" s="81"/>
+      <c r="J55" s="81"/>
+      <c r="K55" s="81"/>
+      <c r="L55" s="81"/>
+      <c r="M55" s="81"/>
+      <c r="N55" s="81"/>
+      <c r="O55" s="81"/>
+      <c r="P55" s="81"/>
+      <c r="Q55" s="81"/>
+      <c r="R55" s="81"/>
+      <c r="S55" s="81"/>
+      <c r="T55" s="81"/>
+      <c r="U55" s="81"/>
+      <c r="V55" s="81"/>
+      <c r="W55" s="81"/>
+      <c r="X55" s="81"/>
     </row>
     <row r="56" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A56" s="83"/>
-      <c r="B56" s="83"/>
-      <c r="C56" s="83"/>
-      <c r="D56" s="83"/>
-      <c r="E56" s="83"/>
-      <c r="F56" s="83"/>
-      <c r="G56" s="83"/>
-      <c r="H56" s="83"/>
-      <c r="I56" s="83"/>
-      <c r="J56" s="83"/>
-      <c r="K56" s="83"/>
-      <c r="L56" s="83"/>
-      <c r="M56" s="83"/>
-      <c r="N56" s="83"/>
-      <c r="O56" s="83"/>
-      <c r="P56" s="83"/>
-      <c r="Q56" s="83"/>
-      <c r="R56" s="83"/>
-      <c r="S56" s="83"/>
-      <c r="T56" s="83"/>
-      <c r="U56" s="83"/>
-      <c r="V56" s="83"/>
-      <c r="W56" s="83"/>
-      <c r="X56" s="83"/>
+      <c r="A56" s="81"/>
+      <c r="B56" s="81"/>
+      <c r="C56" s="81"/>
+      <c r="D56" s="81"/>
+      <c r="E56" s="81"/>
+      <c r="F56" s="81"/>
+      <c r="G56" s="81"/>
+      <c r="H56" s="81"/>
+      <c r="I56" s="81"/>
+      <c r="J56" s="81"/>
+      <c r="K56" s="81"/>
+      <c r="L56" s="81"/>
+      <c r="M56" s="81"/>
+      <c r="N56" s="81"/>
+      <c r="O56" s="81"/>
+      <c r="P56" s="81"/>
+      <c r="Q56" s="81"/>
+      <c r="R56" s="81"/>
+      <c r="S56" s="81"/>
+      <c r="T56" s="81"/>
+      <c r="U56" s="81"/>
+      <c r="V56" s="81"/>
+      <c r="W56" s="81"/>
+      <c r="X56" s="81"/>
     </row>
     <row r="57" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A57" s="83"/>
-      <c r="B57" s="83"/>
-      <c r="C57" s="83"/>
-      <c r="D57" s="83"/>
-      <c r="E57" s="83"/>
-      <c r="F57" s="83"/>
-      <c r="G57" s="83"/>
-      <c r="H57" s="83"/>
-      <c r="I57" s="83"/>
-      <c r="J57" s="83"/>
-      <c r="K57" s="83"/>
-      <c r="L57" s="83"/>
-      <c r="M57" s="83"/>
-      <c r="N57" s="83"/>
-      <c r="O57" s="83"/>
-      <c r="P57" s="83"/>
-      <c r="Q57" s="83"/>
-      <c r="R57" s="83"/>
-      <c r="S57" s="83"/>
-      <c r="T57" s="83"/>
-      <c r="U57" s="83"/>
-      <c r="V57" s="83"/>
-      <c r="W57" s="83"/>
-      <c r="X57" s="83"/>
+      <c r="A57" s="81"/>
+      <c r="B57" s="81"/>
+      <c r="C57" s="81"/>
+      <c r="D57" s="81"/>
+      <c r="E57" s="81"/>
+      <c r="F57" s="81"/>
+      <c r="G57" s="81"/>
+      <c r="H57" s="81"/>
+      <c r="I57" s="81"/>
+      <c r="J57" s="81"/>
+      <c r="K57" s="81"/>
+      <c r="L57" s="81"/>
+      <c r="M57" s="81"/>
+      <c r="N57" s="81"/>
+      <c r="O57" s="81"/>
+      <c r="P57" s="81"/>
+      <c r="Q57" s="81"/>
+      <c r="R57" s="81"/>
+      <c r="S57" s="81"/>
+      <c r="T57" s="81"/>
+      <c r="U57" s="81"/>
+      <c r="V57" s="81"/>
+      <c r="W57" s="81"/>
+      <c r="X57" s="81"/>
     </row>
     <row r="58" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A58" s="83"/>
-      <c r="B58" s="83"/>
-      <c r="C58" s="83"/>
-      <c r="D58" s="83"/>
-      <c r="E58" s="83"/>
-      <c r="F58" s="83"/>
-      <c r="G58" s="83"/>
-      <c r="H58" s="83"/>
-      <c r="I58" s="83"/>
-      <c r="J58" s="83"/>
-      <c r="K58" s="83"/>
-      <c r="L58" s="83"/>
-      <c r="M58" s="83"/>
-      <c r="N58" s="83"/>
-      <c r="O58" s="83"/>
-      <c r="P58" s="83"/>
-      <c r="Q58" s="83"/>
-      <c r="R58" s="83"/>
-      <c r="S58" s="83"/>
-      <c r="T58" s="83"/>
-      <c r="U58" s="83"/>
-      <c r="V58" s="83"/>
-      <c r="W58" s="83"/>
-      <c r="X58" s="83"/>
+      <c r="A58" s="81"/>
+      <c r="B58" s="81"/>
+      <c r="C58" s="81"/>
+      <c r="D58" s="81"/>
+      <c r="E58" s="81"/>
+      <c r="F58" s="81"/>
+      <c r="G58" s="81"/>
+      <c r="H58" s="81"/>
+      <c r="I58" s="81"/>
+      <c r="J58" s="81"/>
+      <c r="K58" s="81"/>
+      <c r="L58" s="81"/>
+      <c r="M58" s="81"/>
+      <c r="N58" s="81"/>
+      <c r="O58" s="81"/>
+      <c r="P58" s="81"/>
+      <c r="Q58" s="81"/>
+      <c r="R58" s="81"/>
+      <c r="S58" s="81"/>
+      <c r="T58" s="81"/>
+      <c r="U58" s="81"/>
+      <c r="V58" s="81"/>
+      <c r="W58" s="81"/>
+      <c r="X58" s="81"/>
     </row>
     <row r="59" spans="1:24" x14ac:dyDescent="0.3">
-      <c r="A59" s="83"/>
-      <c r="B59" s="83"/>
-      <c r="C59" s="83"/>
-      <c r="D59" s="83"/>
-      <c r="E59" s="83"/>
-      <c r="F59" s="83"/>
-      <c r="G59" s="83"/>
-      <c r="H59" s="83"/>
-      <c r="I59" s="83"/>
-      <c r="J59" s="83"/>
-      <c r="K59" s="83"/>
-      <c r="L59" s="83"/>
-      <c r="M59" s="83"/>
-      <c r="N59" s="83"/>
-      <c r="O59" s="83"/>
-      <c r="P59" s="83"/>
-      <c r="Q59" s="83"/>
-      <c r="R59" s="83"/>
-      <c r="S59" s="83"/>
-      <c r="T59" s="83"/>
-      <c r="U59" s="83"/>
-      <c r="V59" s="83"/>
-      <c r="W59" s="83"/>
-      <c r="X59" s="83"/>
+      <c r="A59" s="81"/>
+      <c r="B59" s="81"/>
+      <c r="C59" s="81"/>
+      <c r="D59" s="81"/>
+      <c r="E59" s="81"/>
+      <c r="F59" s="81"/>
+      <c r="G59" s="81"/>
+      <c r="H59" s="81"/>
+      <c r="I59" s="81"/>
+      <c r="J59" s="81"/>
+      <c r="K59" s="81"/>
+      <c r="L59" s="81"/>
+      <c r="M59" s="81"/>
+      <c r="N59" s="81"/>
+      <c r="O59" s="81"/>
+      <c r="P59" s="81"/>
+      <c r="Q59" s="81"/>
+      <c r="R59" s="81"/>
+      <c r="S59" s="81"/>
+      <c r="T59" s="81"/>
+      <c r="U59" s="81"/>
+      <c r="V59" s="81"/>
+      <c r="W59" s="81"/>
+      <c r="X59" s="81"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/MISUO - Amr Mohamed Basyouni Shaaban.xlsx
+++ b/MISUO - Amr Mohamed Basyouni Shaaban.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr hidePivotFieldList="1"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AmrShaabanHPVictus\Desktop\data_analysis\projects\misuo_dashboard_dataanalysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C32B65A-3036-471D-AA1F-5877915E505C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A83B56D-793A-46DD-A92A-CF2DFC3970D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,7 +30,7 @@
   </definedNames>
   <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId7"/>
+    <pivotCache cacheId="12" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -90,7 +90,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3254" uniqueCount="439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3254" uniqueCount="447">
   <si>
     <t>أسم العميل</t>
   </si>
@@ -1431,6 +1431,30 @@
       <t xml:space="preserve"> شيزلونج</t>
     </r>
   </si>
+  <si>
+    <t>الجيزة</t>
+  </si>
+  <si>
+    <t>الإسكندرية</t>
+  </si>
+  <si>
+    <t>مطروح</t>
+  </si>
+  <si>
+    <t>البحر الأحمر</t>
+  </si>
+  <si>
+    <t>القاهرة</t>
+  </si>
+  <si>
+    <t>القليوبية</t>
+  </si>
+  <si>
+    <t>أسيوط</t>
+  </si>
+  <si>
+    <t>مخزن مركزى</t>
+  </si>
 </sst>
 </file>
 
@@ -1703,7 +1727,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="19" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1914,17 +1938,39 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="40">
+  <dxfs count="45">
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="13" formatCode="0%"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF223A59"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF1E3151"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2796,13 +2842,13 @@
       </border>
     </dxf>
     <dxf>
-      <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="13" formatCode="0%"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="166" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -2891,22 +2937,32 @@
       </border>
     </dxf>
   </dxfs>
-  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+  <tableStyles count="3" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
     <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{AA73528B-8D85-432A-9172-AA70B5E8C669}"/>
+    <tableStyle name="Slicer Style 1" pivot="0" table="0" count="1" xr9:uid="{310DE510-BCD1-481F-A8A9-F4E0FCBC6C94}">
+      <tableStyleElement type="wholeTable" dxfId="4"/>
+    </tableStyle>
+    <tableStyle name="Slicer Style 2" pivot="0" table="0" count="1" xr9:uid="{7F58BE56-F140-4D7D-8F85-23C5E765AA41}">
+      <tableStyleElement type="wholeTable" dxfId="3"/>
+    </tableStyle>
   </tableStyles>
   <colors>
     <mruColors>
       <color rgb="FFF2F2F2"/>
       <color rgb="FFF21B2D"/>
+      <color rgb="FF223A59"/>
+      <color rgb="FF1E3151"/>
       <color rgb="FF4A6B53"/>
-      <color rgb="FF1E3151"/>
       <color rgb="FF1B2B48"/>
       <color rgb="FFA60311"/>
     </mruColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1">
+        <x14:slicerStyle name="Slicer Style 1"/>
+        <x14:slicerStyle name="Slicer Style 2"/>
+      </x14:slicerStyles>
     </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
       <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
@@ -4748,7 +4804,6 @@
         <c14:dropZoneCategories val="1"/>
         <c14:dropZoneData val="1"/>
         <c14:dropZoneSeries val="1"/>
-        <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
     </c:ext>
     <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
@@ -5896,7 +5951,6 @@
         <c14:dropZoneCategories val="1"/>
         <c14:dropZoneData val="1"/>
         <c14:dropZoneSeries val="1"/>
-        <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
     </c:ext>
     <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
@@ -5909,600 +5963,6 @@
 </file>
 
 <file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-GB"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:pivotSource>
-    <c:name>[MISUO - Amr Mohamed Basyouni Shaaban.xlsx]Pivot tables!PivotTable11</c:name>
-    <c:fmtId val="2"/>
-  </c:pivotSource>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="F2F2F2"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="ar-EG"/>
-              <a:t>المدينة الأكثر مبيعا</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.47557813159790358"/>
-          <c:y val="5.9724677272483796E-2"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="F2F2F2"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:pivotFmts>
-      <c:pivotFmt>
-        <c:idx val="0"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:srgbClr val="1B2B48"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="1"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:srgbClr val="1B2B48"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="2"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:srgbClr val="F21B2D"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:srgbClr val="F2F2F2"/>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:dLblPos val="outEnd"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-    </c:pivotFmts>
-    <c:plotArea>
-      <c:layout>
-        <c:manualLayout>
-          <c:layoutTarget val="inner"/>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="5.783385909568875E-2"/>
-          <c:y val="0.27306634262605978"/>
-          <c:w val="0.66400266607052671"/>
-          <c:h val="0.13499986389084648"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Pivot tables'!$AU$8</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Total</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:srgbClr val="F21B2D"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:srgbClr val="F2F2F2"/>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="outEnd"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:cat>
-            <c:strRef>
-              <c:f>'Pivot tables'!$AT$9:$AT$18</c:f>
-              <c:strCache>
-                <c:ptCount val="9"/>
-                <c:pt idx="0">
-                  <c:v>القاهرة (Cairo)</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>الجيزة (Giza)</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>القليوبية (Qalyubia)</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>السويس (Suez)</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>الإسكندرية (Alexandria)</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>مستودع / مخزن مركزى (Central Warehouse)</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>البحر الأحمر (Red Sea)</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>مطروح (Matrouh)</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>أسيوط (Asyut)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>'Pivot tables'!$AU$9:$AU$18</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="9"/>
-                <c:pt idx="0">
-                  <c:v>60</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>24</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>11</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>8</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>4</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>3</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-DC8C-483B-A799-70F983544A56}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:overlap val="-27"/>
-        <c:axId val="66893568"/>
-        <c:axId val="66881088"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="66893568"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:srgbClr val="F2F2F2"/>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="66881088"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="66881088"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="1"/>
-        <c:axPos val="l"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="66893568"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.77967038426190405"/>
-          <c:y val="0.27028871391076115"/>
-          <c:w val="0.18878387441317471"/>
-          <c:h val="0.11989876265466817"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:srgbClr val="F2F2F2"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:noFill/>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:noFill/>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr>
-          <a:solidFill>
-            <a:srgbClr val="F2F2F2"/>
-          </a:solidFill>
-        </a:defRPr>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-  <c:extLst>
-    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
-      <c14:pivotOptions>
-        <c14:dropZoneFilter val="1"/>
-        <c14:dropZoneCategories val="1"/>
-        <c14:dropZoneData val="1"/>
-        <c14:dropZoneSeries val="1"/>
-        <c14:dropZonesVisible val="1"/>
-      </c14:pivotOptions>
-    </c:ext>
-    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
-      <c16:pivotOptions16>
-        <c16:showExpandCollapseFieldButtons val="1"/>
-      </c16:pivotOptions16>
-    </c:ext>
-  </c:extLst>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-GB"/>
@@ -7051,7 +6511,6 @@
         <c14:dropZoneCategories val="1"/>
         <c14:dropZoneData val="1"/>
         <c14:dropZoneSeries val="1"/>
-        <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
     </c:ext>
     <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
@@ -7063,7 +6522,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-GB"/>
@@ -7610,7 +7069,6 @@
         <c14:dropZoneCategories val="1"/>
         <c14:dropZoneData val="1"/>
         <c14:dropZoneSeries val="1"/>
-        <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
     </c:ext>
     <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
@@ -7622,7 +7080,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-GB"/>
@@ -7885,8 +7343,8 @@
           <c:yMode val="edge"/>
           <c:x val="0.46779543418099928"/>
           <c:y val="0.24166284432892488"/>
-          <c:w val="0.20390647921275701"/>
-          <c:h val="0.45898440486201358"/>
+          <c:w val="0.41538684175052132"/>
+          <c:h val="0.65235422920201269"/>
         </c:manualLayout>
       </c:layout>
       <c:barChart>
@@ -8087,7 +7545,7 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="800" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:srgbClr val="F2F2F2"/>
                 </a:solidFill>
@@ -8208,7 +7666,6 @@
         <c14:dropZoneCategories val="1"/>
         <c14:dropZoneData val="1"/>
         <c14:dropZoneSeries val="1"/>
-        <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
     </c:ext>
     <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
@@ -8220,7 +7677,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-GB"/>
@@ -8805,7 +8262,6 @@
         <c14:dropZoneCategories val="1"/>
         <c14:dropZoneData val="1"/>
         <c14:dropZoneSeries val="1"/>
-        <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
     </c:ext>
     <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
@@ -8817,7 +8273,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-GB"/>
@@ -9420,7 +8876,6 @@
         <c14:dropZoneCategories val="1"/>
         <c14:dropZoneData val="1"/>
         <c14:dropZoneSeries val="1"/>
-        <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
     </c:ext>
     <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
@@ -9432,7 +8887,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart17.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-GB"/>
@@ -9960,10 +9415,10 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="9.1804213248854155E-2"/>
-          <c:y val="0.69291027970616104"/>
-          <c:w val="0.1744737264984734"/>
-          <c:h val="8.6908866421283135E-2"/>
+          <c:x val="4.4570542042568558E-2"/>
+          <c:y val="0.6349779639844485"/>
+          <c:w val="0.26894067391373655"/>
+          <c:h val="0.10919056240964532"/>
         </c:manualLayout>
       </c:layout>
       <c:overlay val="0"/>
@@ -10033,7 +9488,608 @@
         <c14:dropZoneCategories val="1"/>
         <c14:dropZoneData val="1"/>
         <c14:dropZoneSeries val="1"/>
-        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart18.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-GB"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[MISUO - Amr Mohamed Basyouni Shaaban.xlsx]Pivot tables!PivotTable8</c:name>
+    <c:fmtId val="4"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="F2F2F2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ar-EG">
+                <a:solidFill>
+                  <a:srgbClr val="F2F2F2"/>
+                </a:solidFill>
+              </a:rPr>
+              <a:t>المدينة الأكثر مبيعا</a:t>
+            </a:r>
+            <a:endParaRPr lang="en-US">
+              <a:solidFill>
+                <a:srgbClr val="F2F2F2"/>
+              </a:solidFill>
+            </a:endParaRPr>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.35492032910779769"/>
+          <c:y val="3.9770420263732092E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="F2F2F2"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="F21B2D"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="F21B2D"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="F21B2D"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="F2F2F2"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.9101654846335699E-2"/>
+          <c:y val="0.16282869463652067"/>
+          <c:w val="0.6223008693062303"/>
+          <c:h val="0.26425694250147663"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Pivot tables'!$AU$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="F21B2D"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:srgbClr val="F2F2F2"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Pivot tables'!$AT$9:$AT$18</c:f>
+              <c:strCache>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>القاهرة</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>الجيزة</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>القليوبية</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>السويس</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>الإسكندرية</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>مخزن مركزى</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>البحر الأحمر</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>مطروح</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>أسيوط</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Pivot tables'!$AU$9:$AU$18</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="9"/>
+                <c:pt idx="0">
+                  <c:v>60</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-CF30-466C-8477-3991B06AB975}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="1190766848"/>
+        <c:axId val="1190765408"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1190766848"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:srgbClr val="F2F2F2"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1190765408"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1190765408"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="1190766848"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.79352946335168728"/>
+          <c:y val="0.22121054884613883"/>
+          <c:w val="0.20334924889707937"/>
+          <c:h val="0.13554311735129496"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:srgbClr val="F2F2F2"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:noFill/>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
       </c14:pivotOptions>
     </c:ext>
     <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
@@ -13574,7 +13630,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[MISUO - Amr Mohamed Basyouni Shaaban.xlsx]Pivot tables!PivotTable11</c:name>
+    <c:name>[MISUO - Amr Mohamed Basyouni Shaaban.xlsx]Pivot tables!PivotTable8</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -13605,6 +13661,14 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.44948289578361178"/>
+          <c:y val="3.1738207353405379E-2"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -13640,7 +13704,7 @@
         <c:idx val="0"/>
         <c:spPr>
           <a:solidFill>
-            <a:srgbClr val="1B2B48"/>
+            <a:srgbClr val="F21B2D"/>
           </a:solidFill>
           <a:ln>
             <a:noFill/>
@@ -13695,7 +13759,17 @@
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
-      <c:layout/>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.9101654846335699E-2"/>
+          <c:y val="0.16282869463652067"/>
+          <c:w val="0.6223008693062303"/>
+          <c:h val="0.26425694250147663"/>
+        </c:manualLayout>
+      </c:layout>
       <c:barChart>
         <c:barDir val="col"/>
         <c:grouping val="clustered"/>
@@ -13716,7 +13790,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="1B2B48"/>
+              <a:srgbClr val="F21B2D"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -13788,31 +13862,31 @@
               <c:strCache>
                 <c:ptCount val="9"/>
                 <c:pt idx="0">
-                  <c:v>القاهرة (Cairo)</c:v>
+                  <c:v>القاهرة</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>الجيزة (Giza)</c:v>
+                  <c:v>الجيزة</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>القليوبية (Qalyubia)</c:v>
+                  <c:v>القليوبية</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>السويس (Suez)</c:v>
+                  <c:v>السويس</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>الإسكندرية (Alexandria)</c:v>
+                  <c:v>الإسكندرية</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>مستودع / مخزن مركزى (Central Warehouse)</c:v>
+                  <c:v>مخزن مركزى</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>البحر الأحمر (Red Sea)</c:v>
+                  <c:v>البحر الأحمر</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>مطروح (Matrouh)</c:v>
+                  <c:v>مطروح</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>أسيوط (Asyut)</c:v>
+                  <c:v>أسيوط</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -13855,13 +13929,14 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-54CB-4AAB-8666-818508D79216}"/>
+              <c16:uniqueId val="{00000000-BF69-45BC-9D7E-AB6DBD357348}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
         <c:dLbls>
+          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -13869,11 +13944,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="66893568"/>
-        <c:axId val="66881088"/>
+        <c:axId val="1190766848"/>
+        <c:axId val="1190765408"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="66893568"/>
+        <c:axId val="1190766848"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13916,7 +13991,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66881088"/>
+        <c:crossAx val="1190765408"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -13924,7 +13999,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="66881088"/>
+        <c:axId val="1190765408"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13934,7 +14009,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="66893568"/>
+        <c:crossAx val="1190766848"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13948,6 +14023,16 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.79352946335168728"/>
+          <c:y val="0.22121054884613883"/>
+          <c:w val="0.20334924889707937"/>
+          <c:h val="0.13554311735129496"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -14025,7 +14110,6 @@
         <c14:dropZoneCategories val="1"/>
         <c14:dropZoneData val="1"/>
         <c14:dropZoneSeries val="1"/>
-        <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
     </c:ext>
     <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
@@ -17321,509 +17405,6 @@
 </file>
 
 <file path=xl/charts/style14.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style15.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -18296,6 +17877,509 @@
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style15.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -18832,509 +18916,6 @@
 </file>
 
 <file path=xl/charts/style17.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style18.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -19807,6 +19388,509 @@
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style18.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -24173,42 +24257,6 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>45</xdr:col>
-      <xdr:colOff>15240</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>48</xdr:col>
-      <xdr:colOff>259080</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="11" name="Chart 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5909F14D-7821-8CFB-E81C-962CB9DFF7C6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>26</xdr:col>
@@ -24441,6 +24489,42 @@
         </xdr:sp>
       </mc:Fallback>
     </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>44</xdr:col>
+      <xdr:colOff>365760</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>80010</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>1043940</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>15240</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D11EBF97-4EF3-C279-11D2-8141BB243708}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -25588,44 +25672,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>243840</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>60960</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>205740</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>175260</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="24" name="Chart 23">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5485FC6-FF9A-4339-9501-85DD68F552B9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>15</xdr:col>
       <xdr:colOff>99060</xdr:colOff>
       <xdr:row>8</xdr:row>
@@ -25656,7 +25702,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -25694,7 +25740,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -25732,7 +25778,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -25770,7 +25816,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -25808,7 +25854,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -25846,7 +25892,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -25865,8 +25911,8 @@
       <xdr:row>6</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="33" name="الحالة1 1">
@@ -25889,7 +25935,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -25943,8 +25989,8 @@
       <xdr:row>7</xdr:row>
       <xdr:rowOff>53340</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="34" name="المدينة 1">
@@ -25967,7 +26013,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -26008,11 +26054,49 @@
     </mc:AlternateContent>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>373380</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>83820</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>11430</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8D92D38E-7899-42CB-80C6-9A6D4AAA699C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="AmrShaabanHPVictus" refreshedDate="46266.880863078703" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="126" xr:uid="{9F83BBC7-C71E-497C-BEAB-A93E4532CB74}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="AmrShaabanHPVictus" refreshedDate="46268.809037847219" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="126" xr:uid="{9F83BBC7-C71E-497C-BEAB-A93E4532CB74}">
   <cacheSource type="worksheet">
     <worksheetSource name="table1"/>
   </cacheSource>
@@ -26030,17 +26114,26 @@
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="المدينة" numFmtId="0">
-      <sharedItems count="10">
-        <s v="الجيزة (Giza)"/>
-        <s v="الإسكندرية (Alexandria)"/>
-        <s v="مطروح (Matrouh)"/>
-        <s v="البحر الأحمر (Red Sea)"/>
+      <sharedItems count="19">
+        <s v="الجيزة"/>
+        <s v="الإسكندرية"/>
+        <s v="مطروح"/>
+        <s v="البحر الأحمر"/>
         <e v="#N/A"/>
-        <s v="القاهرة (Cairo)"/>
-        <s v="القليوبية (Qalyubia)"/>
-        <s v="السويس (Suez)"/>
-        <s v="أسيوط (Asyut)"/>
-        <s v="مستودع / مخزن مركزى (Central Warehouse)"/>
+        <s v="القاهرة"/>
+        <s v="القليوبية"/>
+        <s v="السويس"/>
+        <s v="أسيوط"/>
+        <s v="مخزن مركزى"/>
+        <s v="الجيزة (Giza)" u="1"/>
+        <s v="الإسكندرية (Alexandria)" u="1"/>
+        <s v="مطروح (Matrouh)" u="1"/>
+        <s v="البحر الأحمر (Red Sea)" u="1"/>
+        <s v="القاهرة (Cairo)" u="1"/>
+        <s v="القليوبية (Qalyubia)" u="1"/>
+        <s v="السويس (Suez)" u="1"/>
+        <s v="أسيوط (Asyut)" u="1"/>
+        <s v="مستودع / مخزن مركزى (Central Warehouse)" u="1"/>
       </sharedItems>
     </cacheField>
     <cacheField name="منصة البيع " numFmtId="0">
@@ -26154,15 +26247,7 @@
       <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="الحالة" numFmtId="0">
-      <sharedItems containsBlank="1" count="7">
-        <s v="تم التسليم"/>
-        <s v="فشل التسليم"/>
-        <s v="لاغى"/>
-        <s v="مرتجع"/>
-        <m/>
-        <s v="تم التسليم "/>
-        <s v="مرفوض "/>
-      </sharedItems>
+      <sharedItems containsBlank="1"/>
     </cacheField>
     <cacheField name="الحالة1" numFmtId="0">
       <sharedItems count="6">
@@ -26209,7 +26294,7 @@
     <s v="0"/>
     <x v="0"/>
     <s v="تم التسليم عن طريق شركه شحن "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -26236,7 +26321,7 @@
     <s v="0"/>
     <x v="0"/>
     <s v="تم التسليم عن طريق شركه شحن "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -26263,7 +26348,7 @@
     <s v="0"/>
     <x v="0"/>
     <s v="فشل التسليم "/>
-    <x v="1"/>
+    <s v="فشل التسليم"/>
     <x v="1"/>
   </r>
   <r>
@@ -26290,7 +26375,7 @@
     <n v="11"/>
     <x v="1"/>
     <s v="تم التسليم عن طريق شركه شحن "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -26317,7 +26402,7 @@
     <s v="0"/>
     <x v="0"/>
     <s v="فشل التسليم "/>
-    <x v="1"/>
+    <s v="فشل التسليم"/>
     <x v="1"/>
   </r>
   <r>
@@ -26344,7 +26429,7 @@
     <n v="-2"/>
     <x v="2"/>
     <s v="تم التسليم عن طريق شركه شحن "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -26371,7 +26456,7 @@
     <n v="1"/>
     <x v="1"/>
     <s v="تم التسليم عن طريق شركه شحن "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -26398,7 +26483,7 @@
     <n v="-7"/>
     <x v="2"/>
     <s v="تم التسليم عن طريق شركه شحن "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -26425,7 +26510,7 @@
     <n v="-16"/>
     <x v="2"/>
     <m/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -26452,7 +26537,7 @@
     <s v="0"/>
     <x v="0"/>
     <s v="ملغى "/>
-    <x v="2"/>
+    <s v="لاغى"/>
     <x v="2"/>
   </r>
   <r>
@@ -26479,7 +26564,7 @@
     <n v="-2"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -26506,7 +26591,7 @@
     <n v="-2"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -26533,7 +26618,7 @@
     <n v="8"/>
     <x v="1"/>
     <s v="تم التسليم عن طريق شركه شحن "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -26560,7 +26645,7 @@
     <s v="0"/>
     <x v="0"/>
     <m/>
-    <x v="2"/>
+    <s v="لاغى"/>
     <x v="2"/>
   </r>
   <r>
@@ -26587,7 +26672,7 @@
     <n v="-9"/>
     <x v="2"/>
     <s v="تم التسليم عن طريق شركه شحن "/>
-    <x v="3"/>
+    <s v="مرتجع"/>
     <x v="3"/>
   </r>
   <r>
@@ -26614,7 +26699,7 @@
     <n v="1"/>
     <x v="1"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -26641,7 +26726,7 @@
     <n v="1"/>
     <x v="1"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -26668,7 +26753,7 @@
     <s v="0"/>
     <x v="0"/>
     <m/>
-    <x v="2"/>
+    <s v="لاغى"/>
     <x v="2"/>
   </r>
   <r>
@@ -26695,7 +26780,7 @@
     <n v="-5"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -26722,7 +26807,7 @@
     <n v="-2"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -26749,7 +26834,7 @@
     <n v="-5"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -26776,7 +26861,7 @@
     <n v="-5"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -26803,7 +26888,7 @@
     <n v="-5"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -26830,7 +26915,7 @@
     <s v="0"/>
     <x v="0"/>
     <m/>
-    <x v="2"/>
+    <s v="لاغى"/>
     <x v="2"/>
   </r>
   <r>
@@ -26857,7 +26942,7 @@
     <n v="-4"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -26884,7 +26969,7 @@
     <n v="-2"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -26911,7 +26996,7 @@
     <n v="-2"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -26938,7 +27023,7 @@
     <n v="-1"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -26965,7 +27050,7 @@
     <n v="-1"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -26992,7 +27077,7 @@
     <n v="-1"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -27019,7 +27104,7 @@
     <n v="-1"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -27046,7 +27131,7 @@
     <s v="0"/>
     <x v="0"/>
     <s v="فشل التسليم "/>
-    <x v="1"/>
+    <s v="فشل التسليم"/>
     <x v="1"/>
   </r>
   <r>
@@ -27073,7 +27158,7 @@
     <n v="-2"/>
     <x v="2"/>
     <s v="تم التسليم عن طريق شركه شحن "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -27100,7 +27185,7 @@
     <n v="-6"/>
     <x v="2"/>
     <s v="تم التسليم عن طريق شركه شحن "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -27127,7 +27212,7 @@
     <s v="0"/>
     <x v="0"/>
     <s v="تم التسليم عن طريق شركه شحن "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -27154,7 +27239,7 @@
     <s v="0"/>
     <x v="0"/>
     <m/>
-    <x v="2"/>
+    <s v="لاغى"/>
     <x v="2"/>
   </r>
   <r>
@@ -27181,7 +27266,7 @@
     <n v="-7"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -27208,7 +27293,7 @@
     <n v="-7"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -27235,7 +27320,7 @@
     <n v="-5"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -27262,7 +27347,7 @@
     <s v="0"/>
     <x v="0"/>
     <m/>
-    <x v="4"/>
+    <m/>
     <x v="4"/>
   </r>
   <r>
@@ -27289,7 +27374,7 @@
     <n v="-3"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -27316,7 +27401,7 @@
     <n v="-3"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -27343,7 +27428,7 @@
     <n v="-3"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -27370,7 +27455,7 @@
     <n v="-16"/>
     <x v="2"/>
     <s v="تم التسليم عن طريق شركه شحن "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -27397,7 +27482,7 @@
     <n v="-3"/>
     <x v="2"/>
     <s v="تم التسليم عن طريق شركه شحن "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -27424,7 +27509,7 @@
     <n v="-20"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -27451,7 +27536,7 @@
     <s v="0"/>
     <x v="0"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -27478,7 +27563,7 @@
     <n v="-15"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -27505,7 +27590,7 @@
     <n v="-4"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -27532,7 +27617,7 @@
     <n v="-5"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -27559,7 +27644,7 @@
     <n v="-1"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -27586,7 +27671,7 @@
     <n v="14"/>
     <x v="1"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -27613,7 +27698,7 @@
     <n v="14"/>
     <x v="1"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -27640,7 +27725,7 @@
     <n v="10"/>
     <x v="1"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -27667,7 +27752,7 @@
     <s v="0"/>
     <x v="0"/>
     <m/>
-    <x v="2"/>
+    <s v="لاغى"/>
     <x v="2"/>
   </r>
   <r>
@@ -27694,7 +27779,7 @@
     <s v="0"/>
     <x v="0"/>
     <m/>
-    <x v="2"/>
+    <s v="لاغى"/>
     <x v="2"/>
   </r>
   <r>
@@ -27721,7 +27806,7 @@
     <n v="16"/>
     <x v="1"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -27748,7 +27833,7 @@
     <n v="16"/>
     <x v="1"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -27775,7 +27860,7 @@
     <n v="10"/>
     <x v="1"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -27802,7 +27887,7 @@
     <n v="34"/>
     <x v="1"/>
     <s v="تم التسليم عن طريق شركه شحن "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -27829,7 +27914,7 @@
     <s v="0"/>
     <x v="0"/>
     <m/>
-    <x v="2"/>
+    <s v="لاغى"/>
     <x v="2"/>
   </r>
   <r>
@@ -27856,7 +27941,7 @@
     <n v="50"/>
     <x v="1"/>
     <s v="تم التسليم عن طريق شركه شحن "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -27883,7 +27968,7 @@
     <n v="42"/>
     <x v="1"/>
     <s v="تم التسليم محمود على "/>
-    <x v="5"/>
+    <s v="تم التسليم "/>
     <x v="0"/>
   </r>
   <r>
@@ -27910,7 +27995,7 @@
     <n v="35"/>
     <x v="1"/>
     <s v="تم التسليم محمود على "/>
-    <x v="5"/>
+    <s v="تم التسليم "/>
     <x v="0"/>
   </r>
   <r>
@@ -27937,7 +28022,7 @@
     <n v="35"/>
     <x v="1"/>
     <s v="تم التسليم محمود على "/>
-    <x v="5"/>
+    <s v="تم التسليم "/>
     <x v="0"/>
   </r>
   <r>
@@ -27964,7 +28049,7 @@
     <n v="35"/>
     <x v="1"/>
     <s v="تم التسليم محمود على "/>
-    <x v="5"/>
+    <s v="تم التسليم "/>
     <x v="0"/>
   </r>
   <r>
@@ -27991,7 +28076,7 @@
     <n v="32"/>
     <x v="1"/>
     <s v="تم التسليم محمود على "/>
-    <x v="5"/>
+    <s v="تم التسليم "/>
     <x v="0"/>
   </r>
   <r>
@@ -28018,7 +28103,7 @@
     <n v="-15"/>
     <x v="2"/>
     <s v="تم التسليم عن طريق شركه شحن "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -28045,7 +28130,7 @@
     <n v="-7"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="5"/>
+    <s v="تم التسليم "/>
     <x v="0"/>
   </r>
   <r>
@@ -28072,7 +28157,7 @@
     <n v="-9"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="5"/>
+    <s v="تم التسليم "/>
     <x v="0"/>
   </r>
   <r>
@@ -28099,7 +28184,7 @@
     <n v="-9"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="5"/>
+    <s v="تم التسليم "/>
     <x v="0"/>
   </r>
   <r>
@@ -28126,7 +28211,7 @@
     <n v="31"/>
     <x v="1"/>
     <s v="تم التسليم محمود على "/>
-    <x v="5"/>
+    <s v="تم التسليم "/>
     <x v="0"/>
   </r>
   <r>
@@ -28153,7 +28238,7 @@
     <s v="0"/>
     <x v="0"/>
     <m/>
-    <x v="2"/>
+    <s v="لاغى"/>
     <x v="2"/>
   </r>
   <r>
@@ -28180,7 +28265,7 @@
     <n v="1"/>
     <x v="1"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -28207,7 +28292,7 @@
     <s v="0"/>
     <x v="0"/>
     <m/>
-    <x v="2"/>
+    <s v="لاغى"/>
     <x v="2"/>
   </r>
   <r>
@@ -28234,7 +28319,7 @@
     <n v="-1"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -28261,7 +28346,7 @@
     <n v="0"/>
     <x v="0"/>
     <s v="تم التسليم محمود على "/>
-    <x v="5"/>
+    <s v="تم التسليم "/>
     <x v="0"/>
   </r>
   <r>
@@ -28288,7 +28373,7 @@
     <n v="0"/>
     <x v="0"/>
     <s v="تم التسليم بمعرفه الحج سيد "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -28315,7 +28400,7 @@
     <n v="0"/>
     <x v="0"/>
     <s v="تم التسليم بمعرفه الحج سيد "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -28342,7 +28427,7 @@
     <n v="0"/>
     <x v="0"/>
     <s v="تم التسليم بمعرفه الحج سيد "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -28369,7 +28454,7 @@
     <n v="0"/>
     <x v="0"/>
     <s v="تم التسليم بمعرفه الحج سيد "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -28396,7 +28481,7 @@
     <s v="0"/>
     <x v="0"/>
     <m/>
-    <x v="4"/>
+    <m/>
     <x v="4"/>
   </r>
   <r>
@@ -28423,7 +28508,7 @@
     <n v="-1"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -28450,7 +28535,7 @@
     <n v="14"/>
     <x v="1"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -28477,7 +28562,7 @@
     <n v="-2"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -28504,7 +28589,7 @@
     <n v="45"/>
     <x v="1"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -28531,7 +28616,7 @@
     <n v="59"/>
     <x v="1"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -28558,7 +28643,7 @@
     <n v="19"/>
     <x v="1"/>
     <s v="تم التسليم عن طريق شركه شحن "/>
-    <x v="5"/>
+    <s v="تم التسليم "/>
     <x v="0"/>
   </r>
   <r>
@@ -28585,7 +28670,7 @@
     <n v="3"/>
     <x v="1"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -28612,7 +28697,7 @@
     <n v="-6"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -28639,7 +28724,7 @@
     <n v="-6"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -28666,7 +28751,7 @@
     <s v="0"/>
     <x v="0"/>
     <m/>
-    <x v="6"/>
+    <s v="مرفوض "/>
     <x v="5"/>
   </r>
   <r>
@@ -28693,7 +28778,7 @@
     <n v="-4"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -28720,7 +28805,7 @@
     <n v="15"/>
     <x v="1"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -28747,7 +28832,7 @@
     <s v="0"/>
     <x v="0"/>
     <m/>
-    <x v="2"/>
+    <s v="لاغى"/>
     <x v="2"/>
   </r>
   <r>
@@ -28774,7 +28859,7 @@
     <n v="-8"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -28801,7 +28886,7 @@
     <n v="-8"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -28828,7 +28913,7 @@
     <n v="-10"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -28855,7 +28940,7 @@
     <n v="-10"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -28882,7 +28967,7 @@
     <n v="-1"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -28909,7 +28994,7 @@
     <n v="19"/>
     <x v="1"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -28936,7 +29021,7 @@
     <n v="1"/>
     <x v="1"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -28963,7 +29048,7 @@
     <n v="1"/>
     <x v="1"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -28990,7 +29075,7 @@
     <n v="-3"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -29017,7 +29102,7 @@
     <n v="3"/>
     <x v="1"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -29044,7 +29129,7 @@
     <n v="2"/>
     <x v="1"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -29071,7 +29156,7 @@
     <n v="2"/>
     <x v="1"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -29098,7 +29183,7 @@
     <n v="2"/>
     <x v="1"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -29125,7 +29210,7 @@
     <n v="9"/>
     <x v="1"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -29152,7 +29237,7 @@
     <s v="0"/>
     <x v="0"/>
     <m/>
-    <x v="4"/>
+    <m/>
     <x v="4"/>
   </r>
   <r>
@@ -29179,7 +29264,7 @@
     <n v="5"/>
     <x v="1"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -29206,7 +29291,7 @@
     <n v="-5"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -29233,7 +29318,7 @@
     <n v="15"/>
     <x v="1"/>
     <s v="تم التسليم م محمد "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -29260,7 +29345,7 @@
     <n v="-13"/>
     <x v="2"/>
     <s v="تم التسليم عن طريق شركه شحن "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -29287,7 +29372,7 @@
     <n v="-9"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -29314,7 +29399,7 @@
     <s v="0"/>
     <x v="0"/>
     <s v="العميل رفض الاستلام"/>
-    <x v="2"/>
+    <s v="لاغى"/>
     <x v="2"/>
   </r>
   <r>
@@ -29341,7 +29426,7 @@
     <s v="0"/>
     <x v="0"/>
     <m/>
-    <x v="2"/>
+    <s v="لاغى"/>
     <x v="2"/>
   </r>
   <r>
@@ -29368,7 +29453,7 @@
     <s v="0"/>
     <x v="0"/>
     <m/>
-    <x v="2"/>
+    <s v="لاغى"/>
     <x v="2"/>
   </r>
   <r>
@@ -29395,7 +29480,7 @@
     <s v="0"/>
     <x v="0"/>
     <m/>
-    <x v="4"/>
+    <m/>
     <x v="4"/>
   </r>
   <r>
@@ -29422,7 +29507,7 @@
     <s v="0"/>
     <x v="0"/>
     <m/>
-    <x v="2"/>
+    <s v="لاغى"/>
     <x v="2"/>
   </r>
   <r>
@@ -29449,7 +29534,7 @@
     <n v="4"/>
     <x v="1"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -29476,7 +29561,7 @@
     <n v="-5"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -29503,7 +29588,7 @@
     <n v="19"/>
     <x v="1"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -29530,7 +29615,7 @@
     <n v="5"/>
     <x v="1"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -29557,7 +29642,7 @@
     <n v="-1"/>
     <x v="2"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
   <r>
@@ -29584,14 +29669,205 @@
     <n v="7"/>
     <x v="1"/>
     <s v="تم التسليم محمود على "/>
-    <x v="0"/>
+    <s v="تم التسليم"/>
     <x v="0"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{92DB980A-F19E-49E2-8901-B38900404D2B}" name="PivotTable10" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{57AAB59A-A97A-4E54-83CD-56AAD2B21EA5}" name="PivotTable8" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+  <location ref="AT8:AU18" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="25">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="20">
+        <item x="8"/>
+        <item m="1" x="17"/>
+        <item x="1"/>
+        <item m="1" x="11"/>
+        <item x="3"/>
+        <item m="1" x="13"/>
+        <item x="0"/>
+        <item m="1" x="10"/>
+        <item x="7"/>
+        <item m="1" x="16"/>
+        <item x="5"/>
+        <item m="1" x="14"/>
+        <item x="6"/>
+        <item m="1" x="15"/>
+        <item x="9"/>
+        <item m="1" x="18"/>
+        <item x="2"/>
+        <item m="1" x="12"/>
+        <item h="1" x="4"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="10">
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Column1" fld="5" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="4" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{324C3119-C2DC-4940-8ED6-98EE896D9AB4}" name="PivotTable2" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="F8:F9" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+  <pivotFields count="25">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowItems count="1">
+    <i/>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of سعر البيع " fld="13" baseField="0" baseItem="0" numFmtId="166"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="31">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{92DB980A-F19E-49E2-8901-B38900404D2B}" name="PivotTable10" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="AO8:AP12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="25">
     <pivotField showAll="0"/>
@@ -29617,18 +29893,7 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="8">
-        <item x="0"/>
-        <item x="5"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="6"/>
-        <item h="1" x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0" sortType="descending">
       <items count="7">
         <item h="1" x="4"/>
@@ -29777,259 +30042,33 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable10.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{824BE80A-DCA8-4BED-9EC5-1945884C3253}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
-  <location ref="A8:B15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="25">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" dataField="1" showAll="0" sortType="descending">
-      <items count="7">
-        <item x="1"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="5"/>
-  </rowFields>
-  <rowItems count="7">
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Column1" fld="5" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="2">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable11.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{127F9CB2-2EE3-4282-A537-E4787544A1DC}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
-  <location ref="P8:Q15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="25">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="7">
-        <item x="1"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="5"/>
-        <item x="4"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="5"/>
-  </rowFields>
-  <rowItems count="7">
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Average of سعر البيع " fld="13" subtotal="average" baseField="4" baseItem="0"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="26">
-      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
-        <references count="1">
-          <reference field="5" count="0"/>
-        </references>
-      </pivotArea>
-    </format>
-  </formats>
-  <chartFormats count="2">
-    <chartFormat chart="1" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BEA5C7E8-1495-4E63-88A3-0CEBBAD7EF43}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{BEA5C7E8-1495-4E63-88A3-0CEBBAD7EF43}" name="PivotTable7" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="AE8:AF20" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="25">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0">
-      <items count="11">
+      <items count="20">
         <item x="8"/>
+        <item m="1" x="17"/>
         <item x="1"/>
+        <item m="1" x="11"/>
         <item x="3"/>
+        <item m="1" x="13"/>
         <item x="0"/>
+        <item m="1" x="10"/>
         <item x="7"/>
+        <item m="1" x="16"/>
         <item x="5"/>
+        <item m="1" x="14"/>
         <item x="6"/>
+        <item m="1" x="15"/>
         <item x="9"/>
+        <item m="1" x="18"/>
         <item x="2"/>
+        <item m="1" x="12"/>
         <item x="4"/>
         <item t="default"/>
       </items>
@@ -30161,7 +30200,95 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{87181FC4-415C-467B-90FA-41AA1B856110}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7EC14D8C-D6EE-40CD-88B0-93D9FD818C12}" name="PivotTable12" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
+  <location ref="AY8:AZ11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="25">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" dataField="1" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Column3" fld="1" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="5" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{87181FC4-415C-467B-90FA-41AA1B856110}" name="PivotTable3" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="K8:K9" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
   <pivotFields count="25">
     <pivotField dataField="1" showAll="0"/>
@@ -30211,8 +30338,178 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1D36AB31-A780-402B-BE27-B58604B4923E}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{04A566D1-07E6-44FF-9618-E71648A4E8DD}" name="PivotTable9" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="AJ8:AK12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="25">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="2"/>
+        <item m="1" x="3"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="21"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Column1" fld="5" subtotal="count" showDataAs="percentOfTotal" baseField="21" baseItem="0" numFmtId="9"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="29">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <chartFormats count="8">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="21" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="21" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="21" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="8" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="9">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="21" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="10">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="21" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="11">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="21" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1D36AB31-A780-402B-BE27-B58604B4923E}" name="PivotTable5" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="U8:V17" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="25">
     <pivotField showAll="0"/>
@@ -30338,8 +30635,121 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3DFCF780-585B-4163-8AC6-31AD7200B7B5}" name="PivotTable6" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{824BE80A-DCA8-4BED-9EC5-1945884C3253}" name="PivotTable1" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="A8:B15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="25">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" dataField="1" showAll="0" sortType="descending">
+      <items count="7">
+        <item x="1"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField numFmtId="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Column1" fld="5" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3DFCF780-585B-4163-8AC6-31AD7200B7B5}" name="PivotTable6" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="Z8:AA20" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="25">
     <pivotField showAll="0"/>
@@ -30492,16 +30902,35 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{324C3119-C2DC-4940-8ED6-98EE896D9AB4}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="F8:F9" firstHeaderRow="1" firstDataRow="1" firstDataCol="0"/>
+<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{127F9CB2-2EE3-4282-A537-E4787544A1DC}" name="PivotTable4" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+  <location ref="P8:Q15" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="25">
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0" sortType="descending">
+      <items count="7">
+        <item x="1"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="4"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+      <autoSortScope>
+        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
+          <references count="1">
+            <reference field="4294967294" count="1" selected="0">
+              <x v="0"/>
+            </reference>
+          </references>
+        </pivotArea>
+      </autoSortScope>
+    </pivotField>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -30522,357 +30951,13 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
   </pivotFields>
-  <rowItems count="1">
-    <i/>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of سعر البيع " fld="13" baseField="0" baseItem="0" numFmtId="166"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="24">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable7.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7EC14D8C-D6EE-40CD-88B0-93D9FD818C12}" name="PivotTable12" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
-  <location ref="AY8:AZ11" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="25">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" dataField="1" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
   <rowFields count="1">
-    <field x="1"/>
+    <field x="5"/>
   </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
+  <rowItems count="7">
     <i>
       <x v="1"/>
     </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Column3" fld="1" subtotal="count" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="2">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="5" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable8.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{04A566D1-07E6-44FF-9618-E71648A4E8DD}" name="PivotTable9" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
-  <location ref="AJ8:AK12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="25">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="5">
-        <item x="2"/>
-        <item m="1" x="3"/>
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="21"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of Column1" fld="5" subtotal="count" showDataAs="percentOfTotal" baseField="21" baseItem="0" numFmtId="9"/>
-  </dataFields>
-  <formats count="1">
-    <format dxfId="25">
-      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
-    </format>
-  </formats>
-  <chartFormats count="8">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="21" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="2">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="21" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="0" format="3">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="21" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="8" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="9">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="21" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="10">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="21" count="1" selected="0">
-            <x v="2"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="3" format="11">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="21" count="1" selected="0">
-            <x v="3"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable9.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{77F8C56E-BB2F-4D55-8594-818EA755D577}" name="PivotTable11" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
-  <location ref="AT8:AU18" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="25">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0" sortType="descending">
-      <items count="11">
-        <item x="8"/>
-        <item x="1"/>
-        <item x="3"/>
-        <item x="0"/>
-        <item x="7"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="9"/>
-        <item x="2"/>
-        <item h="1" x="4"/>
-        <item t="default"/>
-      </items>
-      <autoSortScope>
-        <pivotArea dataOnly="0" outline="0" fieldPosition="0">
-          <references count="1">
-            <reference field="4294967294" count="1" selected="0">
-              <x v="0"/>
-            </reference>
-          </references>
-        </pivotArea>
-      </autoSortScope>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="7">
-        <item h="1" x="4"/>
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="5"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="10">
     <i>
       <x v="5"/>
     </i>
@@ -30880,22 +30965,10 @@
       <x v="3"/>
     </i>
     <i>
-      <x v="6"/>
+      <x v="2"/>
     </i>
     <i>
       <x v="4"/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="8"/>
     </i>
     <i>
       <x/>
@@ -30908,10 +30981,19 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Count of Column1" fld="5" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Average of سعر البيع " fld="13" subtotal="average" baseField="4" baseItem="0"/>
   </dataFields>
+  <formats count="1">
+    <format dxfId="30">
+      <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="1">
+          <reference field="5" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
   <chartFormats count="2">
-    <chartFormat chart="0" format="0" series="1">
+    <chartFormat chart="1" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -30920,7 +31002,7 @@
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="2" format="2" series="1">
+    <chartFormat chart="3" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -30949,7 +31031,7 @@
   </pivotTables>
   <data>
     <tabular pivotCacheId="233969256">
-      <items count="10">
+      <items count="19">
         <i x="1" s="1"/>
         <i x="3" s="1"/>
         <i x="0" s="1"/>
@@ -30959,7 +31041,16 @@
         <i x="9" s="1"/>
         <i x="4" s="1"/>
         <i x="8" s="1" nd="1"/>
+        <i x="17" s="1" nd="1"/>
+        <i x="11" s="1" nd="1"/>
+        <i x="13" s="1" nd="1"/>
+        <i x="10" s="1" nd="1"/>
+        <i x="16" s="1" nd="1"/>
+        <i x="14" s="1" nd="1"/>
+        <i x="15" s="1" nd="1"/>
+        <i x="18" s="1" nd="1"/>
         <i x="2" s="1" nd="1"/>
+        <i x="12" s="1" nd="1"/>
       </items>
     </tabular>
   </data>
@@ -31016,21 +31107,21 @@
 
 <file path=xl/slicers/slicer2.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <slicer name="المدينة 1" xr10:uid="{38E258BC-8397-4C2F-B000-533D86A5DBD5}" cache="Slicer_المدينة" caption="المدينة" rowHeight="234950"/>
-  <slicer name="الحالة1 1" xr10:uid="{8F68F08E-5FCD-4EC2-8197-F4D3EB0407DE}" cache="Slicer_الحالة1" caption="الحالة1" startItem="1" rowHeight="234950"/>
+  <slicer name="المدينة 1" xr10:uid="{38E258BC-8397-4C2F-B000-533D86A5DBD5}" cache="Slicer_المدينة" caption="المدينة" style="Slicer Style 2" rowHeight="234950"/>
+  <slicer name="الحالة1 1" xr10:uid="{8F68F08E-5FCD-4EC2-8197-F4D3EB0407DE}" cache="Slicer_الحالة1" caption="الحالة1" startItem="1" style="Slicer Style 2" rowHeight="234950"/>
 </slicers>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D2798A78-3521-436D-9BC5-851ED3CB5E63}" name="table1" displayName="table1" ref="A1:Y127" totalsRowShown="0" headerRowDxfId="39" headerRowBorderDxfId="38" tableBorderDxfId="37">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D2798A78-3521-436D-9BC5-851ED3CB5E63}" name="table1" displayName="table1" ref="A1:Y127" totalsRowShown="0" headerRowDxfId="44" headerRowBorderDxfId="43" tableBorderDxfId="42">
   <autoFilter ref="A1:Y127" xr:uid="{D2798A78-3521-436D-9BC5-851ED3CB5E63}"/>
   <tableColumns count="25">
     <tableColumn id="4" xr3:uid="{47BE3B96-D330-4BBC-A2D2-F81C95C9CDF8}" name="أسم العميل"/>
-    <tableColumn id="22" xr3:uid="{F15DAF27-78C1-4D92-9202-2C5CF008F705}" name="Column3" dataDxfId="36">
+    <tableColumn id="22" xr3:uid="{F15DAF27-78C1-4D92-9202-2C5CF008F705}" name="Column3" dataDxfId="41">
       <calculatedColumnFormula>IF(OR(table1[[#This Row],[أسم العميل]]="تاكى",table1[[#This Row],[أسم العميل]]="أوسكار راتن",table1[[#This Row],[أسم العميل]]="شيك هومز"),"شركات","أفراد")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="5" xr3:uid="{8A9922D2-A0CD-402D-B813-D91B1A5543A7}" name="العنوان"/>
-    <tableColumn id="1" xr3:uid="{AD1FFE34-51FD-4097-8C5F-4D6F46AC80A7}" name="المدينة" dataDxfId="35"/>
+    <tableColumn id="1" xr3:uid="{AD1FFE34-51FD-4097-8C5F-4D6F46AC80A7}" name="المدينة" dataDxfId="40"/>
     <tableColumn id="6" xr3:uid="{531866FB-239E-4CF3-9FE1-039571685D15}" name="منصة البيع "/>
     <tableColumn id="7" xr3:uid="{329594CA-08DA-45AC-A7F7-910A5361B134}" name="Column1"/>
     <tableColumn id="8" xr3:uid="{990A4B5E-F656-488D-9380-13FEF9368A58}" name="Column2"/>
@@ -31042,22 +31133,22 @@
     <tableColumn id="13" xr3:uid="{D1430ED2-4D5A-4B23-8A5C-34451686BB87}" name="المنتج"/>
     <tableColumn id="14" xr3:uid="{5C7E7829-EAB2-4268-9FAB-15FA3FD2CCF4}" name="سعر البيع "/>
     <tableColumn id="15" xr3:uid="{BACF5005-30BE-47C9-AAC1-9BDF38012149}" name="طريقه الدفع "/>
-    <tableColumn id="16" xr3:uid="{E2B28B8B-CFBC-439F-8D85-DC762E0967F1}" name="ميعاد الطلب" dataDxfId="34"/>
-    <tableColumn id="17" xr3:uid="{1A1B1E1B-A2CA-408E-8E56-91ED4C4CCBF5}" name="ميعاد التسليم" dataDxfId="33"/>
-    <tableColumn id="18" xr3:uid="{E1959E39-8CB9-4EDA-BBF2-E00B29924D1E}" name="تاريخ التسليم" dataDxfId="32"/>
-    <tableColumn id="2" xr3:uid="{5929C7DE-15D3-4F6B-BAA3-355C82794866}" name="عدد أيام التسليم الأصلى" dataDxfId="31">
+    <tableColumn id="16" xr3:uid="{E2B28B8B-CFBC-439F-8D85-DC762E0967F1}" name="ميعاد الطلب" dataDxfId="39"/>
+    <tableColumn id="17" xr3:uid="{1A1B1E1B-A2CA-408E-8E56-91ED4C4CCBF5}" name="ميعاد التسليم" dataDxfId="38"/>
+    <tableColumn id="18" xr3:uid="{E1959E39-8CB9-4EDA-BBF2-E00B29924D1E}" name="تاريخ التسليم" dataDxfId="37"/>
+    <tableColumn id="2" xr3:uid="{5929C7DE-15D3-4F6B-BAA3-355C82794866}" name="عدد أيام التسليم الأصلى" dataDxfId="36">
       <calculatedColumnFormula>IF(OR(ISBLANK(table1[[#This Row],[ميعاد الطلب]]),ISBLANK(table1[[#This Row],[ميعاد التسليم]])),0,table1[[#This Row],[ميعاد التسليم]]-table1[[#This Row],[ميعاد الطلب]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{2BEEC7D8-2A51-4F7A-9B83-7976B7B93352}" name="عدد أيام التسليم الفعلى" dataDxfId="30">
+    <tableColumn id="3" xr3:uid="{2BEEC7D8-2A51-4F7A-9B83-7976B7B93352}" name="عدد أيام التسليم الفعلى" dataDxfId="35">
       <calculatedColumnFormula>IF(OR(ISBLANK(table1[[#This Row],[تاريخ التسليم]]),ISBLANK(table1[[#This Row],[ميعاد الطلب]]),ISBLANK(table1[[#This Row],[ميعاد التسليم]])),0,table1[[#This Row],[تاريخ التسليم]]-table1[[#This Row],[ميعاد الطلب]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{FF4D0B8C-46CD-415E-BA7A-7DA012D5025D}" name="Column4" dataDxfId="29"/>
-    <tableColumn id="25" xr3:uid="{2CA249B4-2C38-4756-B217-A70D4BD8A8D0}" name="Column5" dataDxfId="28">
+    <tableColumn id="23" xr3:uid="{FF4D0B8C-46CD-415E-BA7A-7DA012D5025D}" name="Column4" dataDxfId="34"/>
+    <tableColumn id="25" xr3:uid="{2CA249B4-2C38-4756-B217-A70D4BD8A8D0}" name="Column5" dataDxfId="33">
       <calculatedColumnFormula array="1">_xlfn.IFS(OR(table1[[#This Row],[Column4]]=0,table1[[#This Row],[Column4]]="0"),"لا يوجد تاريخ", table1[[#This Row],[Column4]]&gt;0,"تم التسليم قبل الموعد",table1[[#This Row],[Column4]]&lt;0,"تم التسليم بعد الموعد")</calculatedColumnFormula>
     </tableColumn>
     <tableColumn id="19" xr3:uid="{5F8B0FDB-1F35-4B52-9FA7-8035B2A836D7}" name="المسئول عن التسليم"/>
     <tableColumn id="20" xr3:uid="{064C9CE2-4190-4BB6-8764-5128D762D8E3}" name="الحالة"/>
-    <tableColumn id="26" xr3:uid="{8FF09841-496F-49DE-A608-039A5C21E43D}" name="الحالة1" dataDxfId="27">
+    <tableColumn id="26" xr3:uid="{8FF09841-496F-49DE-A608-039A5C21E43D}" name="الحالة1" dataDxfId="32">
       <calculatedColumnFormula>TRIM(table1[[#This Row],[الحالة]])</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -31066,29 +31157,29 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{9CE7BCED-47CB-49FB-8CE9-A7CAADBF39ED}" name="Table13" displayName="Table13" ref="A1:T127" totalsRowShown="0" headerRowDxfId="23" dataDxfId="21" headerRowBorderDxfId="22" tableBorderDxfId="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{9CE7BCED-47CB-49FB-8CE9-A7CAADBF39ED}" name="Table13" displayName="Table13" ref="A1:T127" totalsRowShown="0" headerRowDxfId="28" dataDxfId="26" headerRowBorderDxfId="27" tableBorderDxfId="25">
   <autoFilter ref="A1:T127" xr:uid="{D2798A78-3521-436D-9BC5-851ED3CB5E63}"/>
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{FD247F19-3F27-4CA0-9CA6-2E9AA3AA1742}" name="م" dataDxfId="19"/>
-    <tableColumn id="2" xr3:uid="{DAB48EC6-2FC2-4A35-A444-EC1023EC1CD3}" name="رقم العملية" dataDxfId="18"/>
-    <tableColumn id="3" xr3:uid="{BF828010-5F19-4960-BCCB-205E4D600EF9}" name="رقم الطلب" dataDxfId="17"/>
-    <tableColumn id="4" xr3:uid="{6DA41A06-DBA1-48DF-B696-C418EF2EED33}" name="أسم العميل" dataDxfId="16"/>
-    <tableColumn id="5" xr3:uid="{E02AFA9F-2EC2-43DD-8E57-ED4EB998289B}" name="العنوان" dataDxfId="15"/>
-    <tableColumn id="6" xr3:uid="{6B9A063D-E81A-4EF1-87F1-A3F2C37C7C6D}" name="منصة البيع " dataDxfId="14"/>
-    <tableColumn id="7" xr3:uid="{920D3B12-BA5A-4719-83B9-7E478E5E1089}" name="Column1" dataDxfId="13"/>
-    <tableColumn id="8" xr3:uid="{23A4FAD1-6646-4642-BA77-89503AB72E3D}" name="Column2" dataDxfId="12"/>
-    <tableColumn id="9" xr3:uid="{9CBE18CC-4213-4221-AF52-796CBE6DDE09}" name="الاسم" dataDxfId="11"/>
-    <tableColumn id="10" xr3:uid="{AE2B86EC-688E-475E-A55A-DF8950997F48}" name="المقاس" dataDxfId="10"/>
-    <tableColumn id="11" xr3:uid="{9536C914-4BBB-4072-88C4-80DBFDF841F8}" name="اللون المعدن" dataDxfId="9"/>
-    <tableColumn id="12" xr3:uid="{636FFDB4-9D38-46BA-8537-71742E623A31}" name="لون القماش" dataDxfId="8"/>
-    <tableColumn id="13" xr3:uid="{A677E1D6-CC68-4B08-B2E7-C2E26D1C60C8}" name="المنتج" dataDxfId="7"/>
-    <tableColumn id="14" xr3:uid="{0232CDCC-4B68-4890-A326-A9A0B4B234CD}" name="سعر البيع " dataDxfId="6"/>
-    <tableColumn id="15" xr3:uid="{DD47A556-C9C3-42BA-9081-C1C0F0A96FAD}" name="طريقه الدفع " dataDxfId="5"/>
-    <tableColumn id="16" xr3:uid="{558AED21-947F-44E1-A22B-D361F99B2520}" name="ميعاد الطلب" dataDxfId="4"/>
-    <tableColumn id="17" xr3:uid="{D2B3BA66-33AC-4DFC-961B-54EDC6B035A5}" name="ميعاد التسليم" dataDxfId="3"/>
-    <tableColumn id="18" xr3:uid="{D4AAE650-7808-427B-9274-A01097D07DD3}" name="تاريخ التسليم" dataDxfId="2"/>
-    <tableColumn id="19" xr3:uid="{E7A43F4D-8207-41F0-A02B-7E46F1B0AD90}" name="المسئول عن التسليم" dataDxfId="1"/>
-    <tableColumn id="20" xr3:uid="{B0DF1866-4DF9-439B-B6C2-C0437A111DEF}" name="الحالة" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{FD247F19-3F27-4CA0-9CA6-2E9AA3AA1742}" name="م" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{DAB48EC6-2FC2-4A35-A444-EC1023EC1CD3}" name="رقم العملية" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{BF828010-5F19-4960-BCCB-205E4D600EF9}" name="رقم الطلب" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{6DA41A06-DBA1-48DF-B696-C418EF2EED33}" name="أسم العميل" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{E02AFA9F-2EC2-43DD-8E57-ED4EB998289B}" name="العنوان" dataDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{6B9A063D-E81A-4EF1-87F1-A3F2C37C7C6D}" name="منصة البيع " dataDxfId="19"/>
+    <tableColumn id="7" xr3:uid="{920D3B12-BA5A-4719-83B9-7E478E5E1089}" name="Column1" dataDxfId="18"/>
+    <tableColumn id="8" xr3:uid="{23A4FAD1-6646-4642-BA77-89503AB72E3D}" name="Column2" dataDxfId="17"/>
+    <tableColumn id="9" xr3:uid="{9CBE18CC-4213-4221-AF52-796CBE6DDE09}" name="الاسم" dataDxfId="16"/>
+    <tableColumn id="10" xr3:uid="{AE2B86EC-688E-475E-A55A-DF8950997F48}" name="المقاس" dataDxfId="15"/>
+    <tableColumn id="11" xr3:uid="{9536C914-4BBB-4072-88C4-80DBFDF841F8}" name="اللون المعدن" dataDxfId="14"/>
+    <tableColumn id="12" xr3:uid="{636FFDB4-9D38-46BA-8537-71742E623A31}" name="لون القماش" dataDxfId="13"/>
+    <tableColumn id="13" xr3:uid="{A677E1D6-CC68-4B08-B2E7-C2E26D1C60C8}" name="المنتج" dataDxfId="12"/>
+    <tableColumn id="14" xr3:uid="{0232CDCC-4B68-4890-A326-A9A0B4B234CD}" name="سعر البيع " dataDxfId="11"/>
+    <tableColumn id="15" xr3:uid="{DD47A556-C9C3-42BA-9081-C1C0F0A96FAD}" name="طريقه الدفع " dataDxfId="10"/>
+    <tableColumn id="16" xr3:uid="{558AED21-947F-44E1-A22B-D361F99B2520}" name="ميعاد الطلب" dataDxfId="9"/>
+    <tableColumn id="17" xr3:uid="{D2B3BA66-33AC-4DFC-961B-54EDC6B035A5}" name="ميعاد التسليم" dataDxfId="8"/>
+    <tableColumn id="18" xr3:uid="{D4AAE650-7808-427B-9274-A01097D07DD3}" name="تاريخ التسليم" dataDxfId="7"/>
+    <tableColumn id="19" xr3:uid="{E7A43F4D-8207-41F0-A02B-7E46F1B0AD90}" name="المسئول عن التسليم" dataDxfId="6"/>
+    <tableColumn id="20" xr3:uid="{B0DF1866-4DF9-439B-B6C2-C0437A111DEF}" name="الحالة" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -31636,7 +31727,7 @@
         <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>339</v>
+        <v>439</v>
       </c>
       <c r="E2" t="s">
         <v>7</v>
@@ -31712,7 +31803,7 @@
         <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>340</v>
+        <v>440</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -31788,7 +31879,7 @@
         <v>341</v>
       </c>
       <c r="D4" t="s">
-        <v>342</v>
+        <v>441</v>
       </c>
       <c r="E4" t="s">
         <v>7</v>
@@ -31866,7 +31957,7 @@
         <v>115</v>
       </c>
       <c r="D5" t="s">
-        <v>343</v>
+        <v>442</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -31942,7 +32033,7 @@
         <v>341</v>
       </c>
       <c r="D6" t="s">
-        <v>342</v>
+        <v>441</v>
       </c>
       <c r="E6" t="s">
         <v>7</v>
@@ -32098,7 +32189,7 @@
         <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E8" t="s">
         <v>34</v>
@@ -32176,7 +32267,7 @@
         <v>276</v>
       </c>
       <c r="D9" t="s">
-        <v>339</v>
+        <v>439</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
@@ -32254,7 +32345,7 @@
         <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E10" t="s">
         <v>42</v>
@@ -32330,7 +32421,7 @@
         <v>41</v>
       </c>
       <c r="D11" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E11" t="s">
         <v>42</v>
@@ -32402,7 +32493,7 @@
         <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E12" t="s">
         <v>42</v>
@@ -32480,7 +32571,7 @@
         <v>41</v>
       </c>
       <c r="D13" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E13" t="s">
         <v>42</v>
@@ -32558,7 +32649,7 @@
         <v>48</v>
       </c>
       <c r="D14" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
@@ -32640,7 +32731,7 @@
         <v>276</v>
       </c>
       <c r="D15" t="s">
-        <v>339</v>
+        <v>439</v>
       </c>
       <c r="E15" t="s">
         <v>7</v>
@@ -32718,7 +32809,7 @@
         <v>345</v>
       </c>
       <c r="D16" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E16" t="s">
         <v>7</v>
@@ -32796,7 +32887,7 @@
         <v>33</v>
       </c>
       <c r="D17" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E17" t="s">
         <v>414</v>
@@ -32878,7 +32969,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E18" t="s">
         <v>414</v>
@@ -32960,7 +33051,7 @@
         <v>346</v>
       </c>
       <c r="D19" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E19" t="s">
         <v>7</v>
@@ -33038,7 +33129,7 @@
         <v>66</v>
       </c>
       <c r="D20" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E20" t="s">
         <v>7</v>
@@ -33120,7 +33211,7 @@
         <v>41</v>
       </c>
       <c r="D21" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E21" t="s">
         <v>42</v>
@@ -33198,7 +33289,7 @@
         <v>66</v>
       </c>
       <c r="D22" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E22" t="s">
         <v>7</v>
@@ -33280,7 +33371,7 @@
         <v>66</v>
       </c>
       <c r="D23" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E23" t="s">
         <v>7</v>
@@ -33362,7 +33453,7 @@
         <v>66</v>
       </c>
       <c r="D24" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E24" t="s">
         <v>7</v>
@@ -33444,7 +33535,7 @@
         <v>105</v>
       </c>
       <c r="D25" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E25" t="s">
         <v>7</v>
@@ -33518,7 +33609,7 @@
         <v>276</v>
       </c>
       <c r="D26" t="s">
-        <v>339</v>
+        <v>439</v>
       </c>
       <c r="E26" t="s">
         <v>7</v>
@@ -33760,7 +33851,7 @@
         <v>347</v>
       </c>
       <c r="D29" t="s">
-        <v>348</v>
+        <v>444</v>
       </c>
       <c r="E29" t="s">
         <v>414</v>
@@ -33842,7 +33933,7 @@
         <v>347</v>
       </c>
       <c r="D30" t="s">
-        <v>348</v>
+        <v>444</v>
       </c>
       <c r="E30" t="s">
         <v>414</v>
@@ -33924,7 +34015,7 @@
         <v>347</v>
       </c>
       <c r="D31" t="s">
-        <v>348</v>
+        <v>444</v>
       </c>
       <c r="E31" t="s">
         <v>414</v>
@@ -34006,7 +34097,7 @@
         <v>347</v>
       </c>
       <c r="D32" t="s">
-        <v>348</v>
+        <v>444</v>
       </c>
       <c r="E32" t="s">
         <v>414</v>
@@ -34088,7 +34179,7 @@
         <v>142</v>
       </c>
       <c r="D33" t="s">
-        <v>349</v>
+        <v>210</v>
       </c>
       <c r="E33" t="s">
         <v>7</v>
@@ -34161,7 +34252,7 @@
         <v>350</v>
       </c>
       <c r="D34" t="s">
-        <v>340</v>
+        <v>440</v>
       </c>
       <c r="E34" t="s">
         <v>7</v>
@@ -34239,7 +34330,7 @@
         <v>276</v>
       </c>
       <c r="D35" t="s">
-        <v>339</v>
+        <v>439</v>
       </c>
       <c r="E35" t="s">
         <v>7</v>
@@ -34317,7 +34408,7 @@
         <v>308</v>
       </c>
       <c r="D36" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E36" t="s">
         <v>7</v>
@@ -34393,7 +34484,7 @@
         <v>351</v>
       </c>
       <c r="D37" t="s">
-        <v>339</v>
+        <v>439</v>
       </c>
       <c r="E37" t="s">
         <v>34</v>
@@ -34471,7 +34562,7 @@
         <v>66</v>
       </c>
       <c r="D38" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E38" t="s">
         <v>7</v>
@@ -34553,7 +34644,7 @@
         <v>66</v>
       </c>
       <c r="D39" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E39" t="s">
         <v>7</v>
@@ -34635,7 +34726,7 @@
         <v>276</v>
       </c>
       <c r="D40" t="s">
-        <v>339</v>
+        <v>439</v>
       </c>
       <c r="E40" t="s">
         <v>7</v>
@@ -34717,7 +34808,7 @@
         <v>352</v>
       </c>
       <c r="D41" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E41" t="s">
         <v>7</v>
@@ -34793,7 +34884,7 @@
         <v>353</v>
       </c>
       <c r="D42" t="s">
-        <v>339</v>
+        <v>439</v>
       </c>
       <c r="E42" t="s">
         <v>7</v>
@@ -34875,7 +34966,7 @@
         <v>353</v>
       </c>
       <c r="D43" t="s">
-        <v>339</v>
+        <v>439</v>
       </c>
       <c r="E43" t="s">
         <v>7</v>
@@ -34957,7 +35048,7 @@
         <v>86</v>
       </c>
       <c r="D44" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E44" t="s">
         <v>7</v>
@@ -35039,7 +35130,7 @@
         <v>115</v>
       </c>
       <c r="D45" t="s">
-        <v>343</v>
+        <v>442</v>
       </c>
       <c r="E45" t="s">
         <v>7</v>
@@ -35121,7 +35212,7 @@
         <v>354</v>
       </c>
       <c r="D46" t="s">
-        <v>349</v>
+        <v>210</v>
       </c>
       <c r="E46" t="s">
         <v>7</v>
@@ -35203,7 +35294,7 @@
         <v>276</v>
       </c>
       <c r="D47" t="s">
-        <v>339</v>
+        <v>439</v>
       </c>
       <c r="E47" t="s">
         <v>7</v>
@@ -35285,7 +35376,7 @@
         <v>66</v>
       </c>
       <c r="D48" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E48" t="s">
         <v>7</v>
@@ -35361,7 +35452,7 @@
         <v>276</v>
       </c>
       <c r="D49" t="s">
-        <v>339</v>
+        <v>439</v>
       </c>
       <c r="E49" t="s">
         <v>7</v>
@@ -35443,7 +35534,7 @@
         <v>105</v>
       </c>
       <c r="D50" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E50" t="s">
         <v>7</v>
@@ -35525,7 +35616,7 @@
         <v>137</v>
       </c>
       <c r="D51" t="s">
-        <v>339</v>
+        <v>439</v>
       </c>
       <c r="E51" t="s">
         <v>7</v>
@@ -35603,7 +35694,7 @@
         <v>345</v>
       </c>
       <c r="D52" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E52" t="s">
         <v>7</v>
@@ -35681,7 +35772,7 @@
         <v>276</v>
       </c>
       <c r="D53" t="s">
-        <v>339</v>
+        <v>439</v>
       </c>
       <c r="E53" t="s">
         <v>7</v>
@@ -35759,7 +35850,7 @@
         <v>355</v>
       </c>
       <c r="D54" t="s">
-        <v>339</v>
+        <v>439</v>
       </c>
       <c r="E54" t="s">
         <v>7</v>
@@ -35841,7 +35932,7 @@
         <v>86</v>
       </c>
       <c r="D55" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E55" t="s">
         <v>7</v>
@@ -35919,7 +36010,7 @@
         <v>127</v>
       </c>
       <c r="D56" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E56" t="s">
         <v>7</v>
@@ -35997,7 +36088,7 @@
         <v>127</v>
       </c>
       <c r="D57" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E57" t="s">
         <v>7</v>
@@ -36075,7 +36166,7 @@
         <v>66</v>
       </c>
       <c r="D58" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E58" t="s">
         <v>7</v>
@@ -36157,7 +36248,7 @@
         <v>66</v>
       </c>
       <c r="D59" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E59" t="s">
         <v>7</v>
@@ -36239,7 +36330,7 @@
         <v>133</v>
       </c>
       <c r="D60" t="s">
-        <v>348</v>
+        <v>444</v>
       </c>
       <c r="E60" t="s">
         <v>7</v>
@@ -36317,7 +36408,7 @@
         <v>356</v>
       </c>
       <c r="D61" t="s">
-        <v>357</v>
+        <v>445</v>
       </c>
       <c r="E61" t="s">
         <v>7</v>
@@ -36399,7 +36490,7 @@
         <v>115</v>
       </c>
       <c r="D62" t="s">
-        <v>343</v>
+        <v>442</v>
       </c>
       <c r="E62" t="s">
         <v>7</v>
@@ -36473,7 +36564,7 @@
         <v>86</v>
       </c>
       <c r="D63" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E63" t="s">
         <v>7</v>
@@ -36555,7 +36646,7 @@
         <v>66</v>
       </c>
       <c r="D64" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E64" t="s">
         <v>7</v>
@@ -36633,7 +36724,7 @@
         <v>345</v>
       </c>
       <c r="D65" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E65" t="s">
         <v>7</v>
@@ -36715,7 +36806,7 @@
         <v>182</v>
       </c>
       <c r="D66" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E66" t="s">
         <v>7</v>
@@ -36795,7 +36886,7 @@
         <v>182</v>
       </c>
       <c r="D67" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E67" t="s">
         <v>7</v>
@@ -36875,7 +36966,7 @@
         <v>184</v>
       </c>
       <c r="D68" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E68" t="s">
         <v>7</v>
@@ -36951,7 +37042,7 @@
         <v>142</v>
       </c>
       <c r="D69" t="s">
-        <v>349</v>
+        <v>210</v>
       </c>
       <c r="E69" t="s">
         <v>7</v>
@@ -37027,7 +37118,7 @@
         <v>358</v>
       </c>
       <c r="D70" t="s">
-        <v>348</v>
+        <v>444</v>
       </c>
       <c r="E70" t="s">
         <v>414</v>
@@ -37107,7 +37198,7 @@
         <v>41</v>
       </c>
       <c r="D71" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E71" t="s">
         <v>42</v>
@@ -37187,7 +37278,7 @@
         <v>41</v>
       </c>
       <c r="D72" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E72" t="s">
         <v>42</v>
@@ -37267,7 +37358,7 @@
         <v>41</v>
       </c>
       <c r="D73" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E73" t="s">
         <v>7</v>
@@ -37347,7 +37438,7 @@
         <v>202</v>
       </c>
       <c r="D74" t="s">
-        <v>339</v>
+        <v>439</v>
       </c>
       <c r="E74" t="s">
         <v>7</v>
@@ -37419,7 +37510,7 @@
         <v>228</v>
       </c>
       <c r="D75" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E75" t="s">
         <v>51</v>
@@ -37647,7 +37738,7 @@
         <v>358</v>
       </c>
       <c r="D78" t="s">
-        <v>348</v>
+        <v>444</v>
       </c>
       <c r="E78" t="s">
         <v>414</v>
@@ -37727,7 +37818,7 @@
         <v>210</v>
       </c>
       <c r="D79" t="s">
-        <v>349</v>
+        <v>210</v>
       </c>
       <c r="E79" t="s">
         <v>210</v>
@@ -37805,7 +37896,7 @@
         <v>210</v>
       </c>
       <c r="D80" t="s">
-        <v>349</v>
+        <v>210</v>
       </c>
       <c r="E80" t="s">
         <v>210</v>
@@ -37879,7 +37970,7 @@
         <v>210</v>
       </c>
       <c r="D81" t="s">
-        <v>349</v>
+        <v>210</v>
       </c>
       <c r="E81" t="s">
         <v>210</v>
@@ -37953,7 +38044,7 @@
         <v>210</v>
       </c>
       <c r="D82" t="s">
-        <v>349</v>
+        <v>210</v>
       </c>
       <c r="E82" t="s">
         <v>210</v>
@@ -38025,7 +38116,7 @@
         <v>220</v>
       </c>
       <c r="D83" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E83" t="s">
         <v>7</v>
@@ -38095,7 +38186,7 @@
         <v>222</v>
       </c>
       <c r="D84" t="s">
-        <v>359</v>
+        <v>446</v>
       </c>
       <c r="E84" t="s">
         <v>51</v>
@@ -38171,7 +38262,7 @@
         <v>360</v>
       </c>
       <c r="D85" t="s">
-        <v>339</v>
+        <v>439</v>
       </c>
       <c r="E85" t="s">
         <v>51</v>
@@ -38321,7 +38412,7 @@
         <v>66</v>
       </c>
       <c r="D87" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E87" t="s">
         <v>7</v>
@@ -38401,7 +38492,7 @@
         <v>48</v>
       </c>
       <c r="D88" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E88" t="s">
         <v>7</v>
@@ -38481,7 +38572,7 @@
         <v>236</v>
       </c>
       <c r="D89" t="s">
-        <v>340</v>
+        <v>440</v>
       </c>
       <c r="E89" t="s">
         <v>7</v>
@@ -38561,7 +38652,7 @@
         <v>240</v>
       </c>
       <c r="D90" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E90" t="s">
         <v>261</v>
@@ -38641,7 +38732,7 @@
         <v>202</v>
       </c>
       <c r="D91" t="s">
-        <v>339</v>
+        <v>439</v>
       </c>
       <c r="E91" t="s">
         <v>51</v>
@@ -38721,7 +38812,7 @@
         <v>202</v>
       </c>
       <c r="D92" t="s">
-        <v>339</v>
+        <v>439</v>
       </c>
       <c r="E92" t="s">
         <v>51</v>
@@ -38801,7 +38892,7 @@
         <v>246</v>
       </c>
       <c r="D93" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E93" t="s">
         <v>414</v>
@@ -38875,7 +38966,7 @@
         <v>249</v>
       </c>
       <c r="D94" t="s">
-        <v>339</v>
+        <v>439</v>
       </c>
       <c r="E94" t="s">
         <v>7</v>
@@ -39103,7 +39194,7 @@
         <v>250</v>
       </c>
       <c r="D97" t="s">
-        <v>339</v>
+        <v>439</v>
       </c>
       <c r="E97" t="s">
         <v>7</v>
@@ -39183,7 +39274,7 @@
         <v>250</v>
       </c>
       <c r="D98" t="s">
-        <v>339</v>
+        <v>439</v>
       </c>
       <c r="E98" t="s">
         <v>7</v>
@@ -39263,7 +39354,7 @@
         <v>105</v>
       </c>
       <c r="D99" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E99" t="s">
         <v>7</v>
@@ -39343,7 +39434,7 @@
         <v>105</v>
       </c>
       <c r="D100" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E100" t="s">
         <v>7</v>
@@ -39423,7 +39514,7 @@
         <v>262</v>
       </c>
       <c r="D101" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E101" t="s">
         <v>7</v>
@@ -39503,7 +39594,7 @@
         <v>222</v>
       </c>
       <c r="D102" t="s">
-        <v>359</v>
+        <v>446</v>
       </c>
       <c r="E102" t="s">
         <v>51</v>
@@ -39581,7 +39672,7 @@
         <v>33</v>
       </c>
       <c r="D103" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E103" t="s">
         <v>261</v>
@@ -39661,7 +39752,7 @@
         <v>358</v>
       </c>
       <c r="D104" t="s">
-        <v>348</v>
+        <v>444</v>
       </c>
       <c r="E104" t="s">
         <v>414</v>
@@ -39741,7 +39832,7 @@
         <v>105</v>
       </c>
       <c r="D105" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E105" t="s">
         <v>7</v>
@@ -39821,7 +39912,7 @@
         <v>33</v>
       </c>
       <c r="D106" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E106" t="s">
         <v>7</v>
@@ -39901,7 +39992,7 @@
         <v>358</v>
       </c>
       <c r="D107" t="s">
-        <v>348</v>
+        <v>444</v>
       </c>
       <c r="E107" t="s">
         <v>414</v>
@@ -39981,7 +40072,7 @@
         <v>270</v>
       </c>
       <c r="D108" t="s">
-        <v>359</v>
+        <v>446</v>
       </c>
       <c r="E108" t="s">
         <v>414</v>
@@ -40061,7 +40152,7 @@
         <v>276</v>
       </c>
       <c r="D109" t="s">
-        <v>339</v>
+        <v>439</v>
       </c>
       <c r="E109" t="s">
         <v>415</v>
@@ -40141,7 +40232,7 @@
         <v>276</v>
       </c>
       <c r="D110" t="s">
-        <v>339</v>
+        <v>439</v>
       </c>
       <c r="E110" t="s">
         <v>7</v>
@@ -40221,7 +40312,7 @@
         <v>41</v>
       </c>
       <c r="D111" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E111" t="s">
         <v>42</v>
@@ -40295,7 +40386,7 @@
         <v>48</v>
       </c>
       <c r="D112" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E112" t="s">
         <v>34</v>
@@ -40375,7 +40466,7 @@
         <v>361</v>
       </c>
       <c r="D113" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E113" t="s">
         <v>7</v>
@@ -40455,7 +40546,7 @@
         <v>41</v>
       </c>
       <c r="D114" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E114" t="s">
         <v>42</v>
@@ -40533,7 +40624,7 @@
         <v>362</v>
       </c>
       <c r="D115" t="s">
-        <v>340</v>
+        <v>440</v>
       </c>
       <c r="E115" t="s">
         <v>7</v>
@@ -40609,7 +40700,7 @@
         <v>346</v>
       </c>
       <c r="D116" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E116" t="s">
         <v>7</v>
@@ -40687,7 +40778,7 @@
         <v>297</v>
       </c>
       <c r="D117" t="s">
-        <v>340</v>
+        <v>440</v>
       </c>
       <c r="E117" t="s">
         <v>7</v>
@@ -40765,7 +40856,7 @@
         <v>66</v>
       </c>
       <c r="D118" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E118" t="s">
         <v>7</v>
@@ -40839,7 +40930,7 @@
         <v>66</v>
       </c>
       <c r="D119" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E119" t="s">
         <v>7</v>
@@ -40911,7 +41002,7 @@
         <v>142</v>
       </c>
       <c r="D120" t="s">
-        <v>349</v>
+        <v>210</v>
       </c>
       <c r="E120" t="s">
         <v>7</v>
@@ -40981,7 +41072,7 @@
         <v>308</v>
       </c>
       <c r="D121" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E121" t="s">
         <v>7</v>
@@ -41057,7 +41148,7 @@
         <v>358</v>
       </c>
       <c r="D122" t="s">
-        <v>348</v>
+        <v>444</v>
       </c>
       <c r="E122" t="s">
         <v>414</v>
@@ -41137,7 +41228,7 @@
         <v>133</v>
       </c>
       <c r="D123" t="s">
-        <v>348</v>
+        <v>444</v>
       </c>
       <c r="E123" t="s">
         <v>7</v>
@@ -41213,7 +41304,7 @@
         <v>363</v>
       </c>
       <c r="D124" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E124" t="s">
         <v>51</v>
@@ -41291,7 +41382,7 @@
         <v>66</v>
       </c>
       <c r="D125" t="s">
-        <v>344</v>
+        <v>443</v>
       </c>
       <c r="E125" t="s">
         <v>7</v>
@@ -41369,7 +41460,7 @@
         <v>276</v>
       </c>
       <c r="D126" t="s">
-        <v>339</v>
+        <v>439</v>
       </c>
       <c r="E126" t="s">
         <v>7</v>
@@ -41449,7 +41540,7 @@
         <v>222</v>
       </c>
       <c r="D127" t="s">
-        <v>359</v>
+        <v>446</v>
       </c>
       <c r="E127" t="s">
         <v>51</v>
@@ -47615,7 +47706,7 @@
     <col min="41" max="41" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="42" max="42" width="16.44140625" bestFit="1" customWidth="1"/>
     <col min="45" max="45" width="8.88671875" style="74"/>
-    <col min="46" max="46" width="34.109375" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="12.5546875" bestFit="1" customWidth="1"/>
     <col min="47" max="47" width="16.44140625" bestFit="1" customWidth="1"/>
     <col min="48" max="48" width="10" bestFit="1" customWidth="1"/>
     <col min="49" max="49" width="3.88671875" bestFit="1" customWidth="1"/>
@@ -47626,256 +47717,256 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:54" x14ac:dyDescent="0.3">
-      <c r="A1" s="83" t="s">
+      <c r="A1" s="84" t="s">
         <v>371</v>
       </c>
-      <c r="B1" s="83"/>
-      <c r="C1" s="83"/>
-      <c r="D1" s="83"/>
-      <c r="F1" s="83" t="s">
+      <c r="B1" s="84"/>
+      <c r="C1" s="84"/>
+      <c r="D1" s="84"/>
+      <c r="F1" s="84" t="s">
         <v>376</v>
       </c>
-      <c r="G1" s="83"/>
-      <c r="H1" s="83"/>
-      <c r="I1" s="83"/>
-      <c r="K1" s="83" t="s">
+      <c r="G1" s="84"/>
+      <c r="H1" s="84"/>
+      <c r="I1" s="84"/>
+      <c r="K1" s="84" t="s">
         <v>378</v>
       </c>
-      <c r="L1" s="83"/>
-      <c r="M1" s="83"/>
-      <c r="N1" s="83"/>
-      <c r="P1" s="83" t="s">
+      <c r="L1" s="84"/>
+      <c r="M1" s="84"/>
+      <c r="N1" s="84"/>
+      <c r="P1" s="84" t="s">
         <v>413</v>
       </c>
-      <c r="Q1" s="83"/>
-      <c r="R1" s="83"/>
-      <c r="S1" s="83"/>
-      <c r="U1" s="83" t="s">
+      <c r="Q1" s="84"/>
+      <c r="R1" s="84"/>
+      <c r="S1" s="84"/>
+      <c r="U1" s="84" t="s">
         <v>416</v>
       </c>
-      <c r="V1" s="83"/>
-      <c r="W1" s="83"/>
-      <c r="X1" s="83"/>
-      <c r="Z1" s="83" t="s">
+      <c r="V1" s="84"/>
+      <c r="W1" s="84"/>
+      <c r="X1" s="84"/>
+      <c r="Z1" s="84" t="s">
         <v>423</v>
       </c>
-      <c r="AA1" s="83"/>
-      <c r="AB1" s="83"/>
-      <c r="AC1" s="83"/>
-      <c r="AE1" s="83" t="s">
+      <c r="AA1" s="84"/>
+      <c r="AB1" s="84"/>
+      <c r="AC1" s="84"/>
+      <c r="AE1" s="84" t="s">
         <v>424</v>
       </c>
-      <c r="AF1" s="83"/>
-      <c r="AG1" s="83"/>
-      <c r="AH1" s="83"/>
-      <c r="AJ1" s="83" t="s">
+      <c r="AF1" s="84"/>
+      <c r="AG1" s="84"/>
+      <c r="AH1" s="84"/>
+      <c r="AJ1" s="84" t="s">
         <v>428</v>
       </c>
-      <c r="AK1" s="83"/>
-      <c r="AL1" s="83"/>
-      <c r="AM1" s="83"/>
-      <c r="AO1" s="83" t="s">
+      <c r="AK1" s="84"/>
+      <c r="AL1" s="84"/>
+      <c r="AM1" s="84"/>
+      <c r="AO1" s="84" t="s">
         <v>431</v>
       </c>
-      <c r="AP1" s="83"/>
-      <c r="AQ1" s="83"/>
-      <c r="AR1" s="83"/>
-      <c r="AT1" s="83" t="s">
+      <c r="AP1" s="84"/>
+      <c r="AQ1" s="84"/>
+      <c r="AR1" s="84"/>
+      <c r="AT1" s="84" t="s">
         <v>433</v>
       </c>
-      <c r="AU1" s="83"/>
-      <c r="AV1" s="83"/>
-      <c r="AW1" s="83"/>
-      <c r="AY1" s="84" t="s">
+      <c r="AU1" s="84"/>
+      <c r="AV1" s="84"/>
+      <c r="AW1" s="84"/>
+      <c r="AY1" s="83" t="s">
         <v>437</v>
       </c>
-      <c r="AZ1" s="84"/>
-      <c r="BA1" s="84"/>
-      <c r="BB1" s="84"/>
+      <c r="AZ1" s="83"/>
+      <c r="BA1" s="83"/>
+      <c r="BB1" s="83"/>
     </row>
     <row r="2" spans="1:54" x14ac:dyDescent="0.3">
-      <c r="A2" s="83"/>
-      <c r="B2" s="83"/>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
-      <c r="H2" s="83"/>
-      <c r="I2" s="83"/>
-      <c r="K2" s="83"/>
-      <c r="L2" s="83"/>
-      <c r="M2" s="83"/>
-      <c r="N2" s="83"/>
-      <c r="P2" s="83"/>
-      <c r="Q2" s="83"/>
-      <c r="R2" s="83"/>
-      <c r="S2" s="83"/>
-      <c r="U2" s="83"/>
-      <c r="V2" s="83"/>
-      <c r="W2" s="83"/>
-      <c r="X2" s="83"/>
-      <c r="Z2" s="83"/>
-      <c r="AA2" s="83"/>
-      <c r="AB2" s="83"/>
-      <c r="AC2" s="83"/>
-      <c r="AE2" s="83"/>
-      <c r="AF2" s="83"/>
-      <c r="AG2" s="83"/>
-      <c r="AH2" s="83"/>
-      <c r="AJ2" s="83"/>
-      <c r="AK2" s="83"/>
-      <c r="AL2" s="83"/>
-      <c r="AM2" s="83"/>
-      <c r="AO2" s="83"/>
-      <c r="AP2" s="83"/>
-      <c r="AQ2" s="83"/>
-      <c r="AR2" s="83"/>
-      <c r="AT2" s="83"/>
-      <c r="AU2" s="83"/>
-      <c r="AV2" s="83"/>
-      <c r="AW2" s="83"/>
-      <c r="AY2" s="84"/>
-      <c r="AZ2" s="84"/>
-      <c r="BA2" s="84"/>
-      <c r="BB2" s="84"/>
+      <c r="A2" s="84"/>
+      <c r="B2" s="84"/>
+      <c r="C2" s="84"/>
+      <c r="D2" s="84"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
+      <c r="M2" s="84"/>
+      <c r="N2" s="84"/>
+      <c r="P2" s="84"/>
+      <c r="Q2" s="84"/>
+      <c r="R2" s="84"/>
+      <c r="S2" s="84"/>
+      <c r="U2" s="84"/>
+      <c r="V2" s="84"/>
+      <c r="W2" s="84"/>
+      <c r="X2" s="84"/>
+      <c r="Z2" s="84"/>
+      <c r="AA2" s="84"/>
+      <c r="AB2" s="84"/>
+      <c r="AC2" s="84"/>
+      <c r="AE2" s="84"/>
+      <c r="AF2" s="84"/>
+      <c r="AG2" s="84"/>
+      <c r="AH2" s="84"/>
+      <c r="AJ2" s="84"/>
+      <c r="AK2" s="84"/>
+      <c r="AL2" s="84"/>
+      <c r="AM2" s="84"/>
+      <c r="AO2" s="84"/>
+      <c r="AP2" s="84"/>
+      <c r="AQ2" s="84"/>
+      <c r="AR2" s="84"/>
+      <c r="AT2" s="84"/>
+      <c r="AU2" s="84"/>
+      <c r="AV2" s="84"/>
+      <c r="AW2" s="84"/>
+      <c r="AY2" s="83"/>
+      <c r="AZ2" s="83"/>
+      <c r="BA2" s="83"/>
+      <c r="BB2" s="83"/>
     </row>
     <row r="3" spans="1:54" x14ac:dyDescent="0.3">
-      <c r="A3" s="83"/>
-      <c r="B3" s="83"/>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="83"/>
-      <c r="H3" s="83"/>
-      <c r="I3" s="83"/>
-      <c r="K3" s="83"/>
-      <c r="L3" s="83"/>
-      <c r="M3" s="83"/>
-      <c r="N3" s="83"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
-      <c r="U3" s="83"/>
-      <c r="V3" s="83"/>
-      <c r="W3" s="83"/>
-      <c r="X3" s="83"/>
-      <c r="Z3" s="83"/>
-      <c r="AA3" s="83"/>
-      <c r="AB3" s="83"/>
-      <c r="AC3" s="83"/>
-      <c r="AE3" s="83"/>
-      <c r="AF3" s="83"/>
-      <c r="AG3" s="83"/>
-      <c r="AH3" s="83"/>
-      <c r="AJ3" s="83"/>
-      <c r="AK3" s="83"/>
-      <c r="AL3" s="83"/>
-      <c r="AM3" s="83"/>
-      <c r="AO3" s="83"/>
-      <c r="AP3" s="83"/>
-      <c r="AQ3" s="83"/>
-      <c r="AR3" s="83"/>
-      <c r="AT3" s="83"/>
-      <c r="AU3" s="83"/>
-      <c r="AV3" s="83"/>
-      <c r="AW3" s="83"/>
-      <c r="AY3" s="84"/>
-      <c r="AZ3" s="84"/>
-      <c r="BA3" s="84"/>
-      <c r="BB3" s="84"/>
+      <c r="A3" s="84"/>
+      <c r="B3" s="84"/>
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
+      <c r="F3" s="84"/>
+      <c r="G3" s="84"/>
+      <c r="H3" s="84"/>
+      <c r="I3" s="84"/>
+      <c r="K3" s="84"/>
+      <c r="L3" s="84"/>
+      <c r="M3" s="84"/>
+      <c r="N3" s="84"/>
+      <c r="P3" s="84"/>
+      <c r="Q3" s="84"/>
+      <c r="R3" s="84"/>
+      <c r="S3" s="84"/>
+      <c r="U3" s="84"/>
+      <c r="V3" s="84"/>
+      <c r="W3" s="84"/>
+      <c r="X3" s="84"/>
+      <c r="Z3" s="84"/>
+      <c r="AA3" s="84"/>
+      <c r="AB3" s="84"/>
+      <c r="AC3" s="84"/>
+      <c r="AE3" s="84"/>
+      <c r="AF3" s="84"/>
+      <c r="AG3" s="84"/>
+      <c r="AH3" s="84"/>
+      <c r="AJ3" s="84"/>
+      <c r="AK3" s="84"/>
+      <c r="AL3" s="84"/>
+      <c r="AM3" s="84"/>
+      <c r="AO3" s="84"/>
+      <c r="AP3" s="84"/>
+      <c r="AQ3" s="84"/>
+      <c r="AR3" s="84"/>
+      <c r="AT3" s="84"/>
+      <c r="AU3" s="84"/>
+      <c r="AV3" s="84"/>
+      <c r="AW3" s="84"/>
+      <c r="AY3" s="83"/>
+      <c r="AZ3" s="83"/>
+      <c r="BA3" s="83"/>
+      <c r="BB3" s="83"/>
     </row>
     <row r="4" spans="1:54" x14ac:dyDescent="0.3">
-      <c r="A4" s="83"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="83"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="K4" s="83"/>
-      <c r="L4" s="83"/>
-      <c r="M4" s="83"/>
-      <c r="N4" s="83"/>
-      <c r="P4" s="83"/>
-      <c r="Q4" s="83"/>
-      <c r="R4" s="83"/>
-      <c r="S4" s="83"/>
-      <c r="U4" s="83"/>
-      <c r="V4" s="83"/>
-      <c r="W4" s="83"/>
-      <c r="X4" s="83"/>
-      <c r="Z4" s="83"/>
-      <c r="AA4" s="83"/>
-      <c r="AB4" s="83"/>
-      <c r="AC4" s="83"/>
-      <c r="AE4" s="83"/>
-      <c r="AF4" s="83"/>
-      <c r="AG4" s="83"/>
-      <c r="AH4" s="83"/>
-      <c r="AJ4" s="83"/>
-      <c r="AK4" s="83"/>
-      <c r="AL4" s="83"/>
-      <c r="AM4" s="83"/>
-      <c r="AO4" s="83"/>
-      <c r="AP4" s="83"/>
-      <c r="AQ4" s="83"/>
-      <c r="AR4" s="83"/>
-      <c r="AT4" s="83"/>
-      <c r="AU4" s="83"/>
-      <c r="AV4" s="83"/>
-      <c r="AW4" s="83"/>
-      <c r="AY4" s="84"/>
-      <c r="AZ4" s="84"/>
-      <c r="BA4" s="84"/>
-      <c r="BB4" s="84"/>
+      <c r="A4" s="84"/>
+      <c r="B4" s="84"/>
+      <c r="C4" s="84"/>
+      <c r="D4" s="84"/>
+      <c r="F4" s="84"/>
+      <c r="G4" s="84"/>
+      <c r="H4" s="84"/>
+      <c r="I4" s="84"/>
+      <c r="K4" s="84"/>
+      <c r="L4" s="84"/>
+      <c r="M4" s="84"/>
+      <c r="N4" s="84"/>
+      <c r="P4" s="84"/>
+      <c r="Q4" s="84"/>
+      <c r="R4" s="84"/>
+      <c r="S4" s="84"/>
+      <c r="U4" s="84"/>
+      <c r="V4" s="84"/>
+      <c r="W4" s="84"/>
+      <c r="X4" s="84"/>
+      <c r="Z4" s="84"/>
+      <c r="AA4" s="84"/>
+      <c r="AB4" s="84"/>
+      <c r="AC4" s="84"/>
+      <c r="AE4" s="84"/>
+      <c r="AF4" s="84"/>
+      <c r="AG4" s="84"/>
+      <c r="AH4" s="84"/>
+      <c r="AJ4" s="84"/>
+      <c r="AK4" s="84"/>
+      <c r="AL4" s="84"/>
+      <c r="AM4" s="84"/>
+      <c r="AO4" s="84"/>
+      <c r="AP4" s="84"/>
+      <c r="AQ4" s="84"/>
+      <c r="AR4" s="84"/>
+      <c r="AT4" s="84"/>
+      <c r="AU4" s="84"/>
+      <c r="AV4" s="84"/>
+      <c r="AW4" s="84"/>
+      <c r="AY4" s="83"/>
+      <c r="AZ4" s="83"/>
+      <c r="BA4" s="83"/>
+      <c r="BB4" s="83"/>
     </row>
     <row r="5" spans="1:54" x14ac:dyDescent="0.3">
-      <c r="A5" s="83"/>
-      <c r="B5" s="83"/>
-      <c r="C5" s="83"/>
-      <c r="D5" s="83"/>
-      <c r="F5" s="83"/>
-      <c r="G5" s="83"/>
-      <c r="H5" s="83"/>
-      <c r="I5" s="83"/>
-      <c r="K5" s="83"/>
-      <c r="L5" s="83"/>
-      <c r="M5" s="83"/>
-      <c r="N5" s="83"/>
-      <c r="P5" s="83"/>
-      <c r="Q5" s="83"/>
-      <c r="R5" s="83"/>
-      <c r="S5" s="83"/>
-      <c r="U5" s="83"/>
-      <c r="V5" s="83"/>
-      <c r="W5" s="83"/>
-      <c r="X5" s="83"/>
-      <c r="Z5" s="83"/>
-      <c r="AA5" s="83"/>
-      <c r="AB5" s="83"/>
-      <c r="AC5" s="83"/>
-      <c r="AE5" s="83"/>
-      <c r="AF5" s="83"/>
-      <c r="AG5" s="83"/>
-      <c r="AH5" s="83"/>
-      <c r="AJ5" s="83"/>
-      <c r="AK5" s="83"/>
-      <c r="AL5" s="83"/>
-      <c r="AM5" s="83"/>
-      <c r="AO5" s="83"/>
-      <c r="AP5" s="83"/>
-      <c r="AQ5" s="83"/>
-      <c r="AR5" s="83"/>
-      <c r="AT5" s="83"/>
-      <c r="AU5" s="83"/>
-      <c r="AV5" s="83"/>
-      <c r="AW5" s="83"/>
-      <c r="AY5" s="84"/>
-      <c r="AZ5" s="84"/>
-      <c r="BA5" s="84"/>
-      <c r="BB5" s="84"/>
+      <c r="A5" s="84"/>
+      <c r="B5" s="84"/>
+      <c r="C5" s="84"/>
+      <c r="D5" s="84"/>
+      <c r="F5" s="84"/>
+      <c r="G5" s="84"/>
+      <c r="H5" s="84"/>
+      <c r="I5" s="84"/>
+      <c r="K5" s="84"/>
+      <c r="L5" s="84"/>
+      <c r="M5" s="84"/>
+      <c r="N5" s="84"/>
+      <c r="P5" s="84"/>
+      <c r="Q5" s="84"/>
+      <c r="R5" s="84"/>
+      <c r="S5" s="84"/>
+      <c r="U5" s="84"/>
+      <c r="V5" s="84"/>
+      <c r="W5" s="84"/>
+      <c r="X5" s="84"/>
+      <c r="Z5" s="84"/>
+      <c r="AA5" s="84"/>
+      <c r="AB5" s="84"/>
+      <c r="AC5" s="84"/>
+      <c r="AE5" s="84"/>
+      <c r="AF5" s="84"/>
+      <c r="AG5" s="84"/>
+      <c r="AH5" s="84"/>
+      <c r="AJ5" s="84"/>
+      <c r="AK5" s="84"/>
+      <c r="AL5" s="84"/>
+      <c r="AM5" s="84"/>
+      <c r="AO5" s="84"/>
+      <c r="AP5" s="84"/>
+      <c r="AQ5" s="84"/>
+      <c r="AR5" s="84"/>
+      <c r="AT5" s="84"/>
+      <c r="AU5" s="84"/>
+      <c r="AV5" s="84"/>
+      <c r="AW5" s="84"/>
+      <c r="AY5" s="83"/>
+      <c r="AZ5" s="83"/>
+      <c r="BA5" s="83"/>
+      <c r="BB5" s="83"/>
     </row>
     <row r="8" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A8" s="72" t="s">
@@ -47943,13 +48034,13 @@
       <c r="A9" s="73" t="s">
         <v>148</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="85">
         <v>88</v>
       </c>
       <c r="F9" s="76">
         <v>1292885.81544</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="85">
         <v>126</v>
       </c>
       <c r="P9" s="73" t="s">
@@ -47961,19 +48052,19 @@
       <c r="U9" s="73" t="s">
         <v>7</v>
       </c>
-      <c r="V9">
+      <c r="V9" s="85">
         <v>78</v>
       </c>
       <c r="Z9" s="73" t="s">
         <v>334</v>
       </c>
-      <c r="AA9">
+      <c r="AA9" s="85">
         <v>46</v>
       </c>
       <c r="AE9" s="73" t="s">
         <v>170</v>
       </c>
-      <c r="AF9">
+      <c r="AF9" s="85">
         <v>7</v>
       </c>
       <c r="AJ9" s="73" t="s">
@@ -47989,15 +48080,15 @@
         <v>0.85</v>
       </c>
       <c r="AT9" s="73" t="s">
-        <v>344</v>
-      </c>
-      <c r="AU9">
+        <v>443</v>
+      </c>
+      <c r="AU9" s="85">
         <v>60</v>
       </c>
       <c r="AY9" s="73" t="s">
         <v>434</v>
       </c>
-      <c r="AZ9">
+      <c r="AZ9" s="85">
         <v>91</v>
       </c>
     </row>
@@ -48005,7 +48096,7 @@
       <c r="A10" s="73" t="s">
         <v>159</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="85">
         <v>18</v>
       </c>
       <c r="P10" s="73" t="s">
@@ -48017,19 +48108,19 @@
       <c r="U10" s="73" t="s">
         <v>51</v>
       </c>
-      <c r="V10">
+      <c r="V10" s="85">
         <v>16</v>
       </c>
       <c r="Z10" s="73" t="s">
         <v>333</v>
       </c>
-      <c r="AA10">
+      <c r="AA10" s="85">
         <v>37</v>
       </c>
       <c r="AE10" s="73" t="s">
         <v>334</v>
       </c>
-      <c r="AF10">
+      <c r="AF10" s="85">
         <v>6</v>
       </c>
       <c r="AJ10" s="73" t="s">
@@ -48045,15 +48136,15 @@
         <v>0.125</v>
       </c>
       <c r="AT10" s="73" t="s">
-        <v>339</v>
-      </c>
-      <c r="AU10">
+        <v>439</v>
+      </c>
+      <c r="AU10" s="85">
         <v>24</v>
       </c>
       <c r="AY10" s="73" t="s">
         <v>435</v>
       </c>
-      <c r="AZ10">
+      <c r="AZ10" s="85">
         <v>35</v>
       </c>
     </row>
@@ -48061,7 +48152,7 @@
       <c r="A11" s="73" t="s">
         <v>155</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="85">
         <v>17</v>
       </c>
       <c r="P11" s="73" t="s">
@@ -48073,19 +48164,19 @@
       <c r="U11" s="73" t="s">
         <v>414</v>
       </c>
-      <c r="V11">
+      <c r="V11" s="85">
         <v>13</v>
       </c>
       <c r="Z11" s="73" t="s">
         <v>170</v>
       </c>
-      <c r="AA11">
+      <c r="AA11" s="85">
         <v>6</v>
       </c>
       <c r="AE11" s="73" t="s">
         <v>300</v>
       </c>
-      <c r="AF11">
+      <c r="AF11" s="85">
         <v>3</v>
       </c>
       <c r="AJ11" s="73" t="s">
@@ -48101,15 +48192,15 @@
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="AT11" s="73" t="s">
-        <v>348</v>
-      </c>
-      <c r="AU11">
+        <v>444</v>
+      </c>
+      <c r="AU11" s="85">
         <v>11</v>
       </c>
       <c r="AY11" s="73" t="s">
         <v>369</v>
       </c>
-      <c r="AZ11">
+      <c r="AZ11" s="85">
         <v>126</v>
       </c>
     </row>
@@ -48117,7 +48208,7 @@
       <c r="A12" s="73" t="s">
         <v>160</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="85">
         <v>1</v>
       </c>
       <c r="G12" s="82">
@@ -48137,19 +48228,19 @@
       <c r="U12" s="73" t="s">
         <v>42</v>
       </c>
-      <c r="V12">
+      <c r="V12" s="85">
         <v>9</v>
       </c>
       <c r="Z12" s="73" t="s">
         <v>168</v>
       </c>
-      <c r="AA12">
+      <c r="AA12" s="85">
         <v>3</v>
       </c>
       <c r="AE12" s="73" t="s">
         <v>420</v>
       </c>
-      <c r="AF12">
+      <c r="AF12" s="85">
         <v>3</v>
       </c>
       <c r="AJ12" s="73" t="s">
@@ -48165,9 +48256,9 @@
         <v>1</v>
       </c>
       <c r="AT12" s="73" t="s">
-        <v>349</v>
-      </c>
-      <c r="AU12">
+        <v>210</v>
+      </c>
+      <c r="AU12" s="85">
         <v>8</v>
       </c>
     </row>
@@ -48175,7 +48266,7 @@
       <c r="A13" s="73" t="s">
         <v>156</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="85">
         <v>1</v>
       </c>
       <c r="P13" s="73" t="s">
@@ -48187,25 +48278,25 @@
       <c r="U13" s="73" t="s">
         <v>210</v>
       </c>
-      <c r="V13">
+      <c r="V13" s="85">
         <v>4</v>
       </c>
       <c r="Z13" s="73" t="s">
         <v>245</v>
       </c>
-      <c r="AA13">
+      <c r="AA13" s="85">
         <v>3</v>
       </c>
       <c r="AE13" s="73" t="s">
         <v>257</v>
       </c>
-      <c r="AF13">
+      <c r="AF13" s="85">
         <v>3</v>
       </c>
       <c r="AT13" s="73" t="s">
-        <v>340</v>
-      </c>
-      <c r="AU13">
+        <v>440</v>
+      </c>
+      <c r="AU13" s="85">
         <v>5</v>
       </c>
     </row>
@@ -48213,7 +48304,7 @@
       <c r="A14" s="73" t="s">
         <v>217</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="85">
         <v>1</v>
       </c>
       <c r="P14" s="73" t="s">
@@ -48225,25 +48316,25 @@
       <c r="U14" s="73" t="s">
         <v>34</v>
       </c>
-      <c r="V14">
+      <c r="V14" s="85">
         <v>3</v>
       </c>
       <c r="Z14" s="73" t="s">
         <v>232</v>
       </c>
-      <c r="AA14">
+      <c r="AA14" s="85">
         <v>2</v>
       </c>
       <c r="AE14" s="73" t="s">
         <v>333</v>
       </c>
-      <c r="AF14">
+      <c r="AF14" s="85">
         <v>2</v>
       </c>
       <c r="AT14" s="73" t="s">
-        <v>359</v>
-      </c>
-      <c r="AU14">
+        <v>446</v>
+      </c>
+      <c r="AU14" s="85">
         <v>4</v>
       </c>
     </row>
@@ -48251,37 +48342,37 @@
       <c r="A15" s="73" t="s">
         <v>369</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="85">
         <v>126</v>
       </c>
       <c r="P15" s="73" t="s">
         <v>369</v>
       </c>
-      <c r="Q15">
+      <c r="Q15" s="85">
         <v>10260.998535238095</v>
       </c>
       <c r="U15" s="73" t="s">
         <v>261</v>
       </c>
-      <c r="V15">
+      <c r="V15" s="85">
         <v>2</v>
       </c>
       <c r="Z15" s="73" t="s">
         <v>174</v>
       </c>
-      <c r="AA15">
+      <c r="AA15" s="85">
         <v>2</v>
       </c>
       <c r="AE15" s="73" t="s">
         <v>216</v>
       </c>
-      <c r="AF15">
+      <c r="AF15" s="85">
         <v>2</v>
       </c>
       <c r="AT15" s="73" t="s">
-        <v>343</v>
-      </c>
-      <c r="AU15">
+        <v>442</v>
+      </c>
+      <c r="AU15" s="85">
         <v>3</v>
       </c>
     </row>
@@ -48289,25 +48380,25 @@
       <c r="U16" s="73" t="s">
         <v>415</v>
       </c>
-      <c r="V16">
+      <c r="V16" s="85">
         <v>1</v>
       </c>
       <c r="Z16" s="73" t="s">
         <v>417</v>
       </c>
-      <c r="AA16">
+      <c r="AA16" s="85">
         <v>2</v>
       </c>
       <c r="AE16" s="73" t="s">
         <v>243</v>
       </c>
-      <c r="AF16">
+      <c r="AF16" s="85">
         <v>1</v>
       </c>
       <c r="AT16" s="73" t="s">
-        <v>342</v>
-      </c>
-      <c r="AU16">
+        <v>441</v>
+      </c>
+      <c r="AU16" s="85">
         <v>2</v>
       </c>
     </row>
@@ -48325,25 +48416,25 @@
       <c r="U17" s="73" t="s">
         <v>369</v>
       </c>
-      <c r="V17">
+      <c r="V17" s="85">
         <v>126</v>
       </c>
       <c r="Z17" s="73" t="s">
         <v>171</v>
       </c>
-      <c r="AA17">
+      <c r="AA17" s="85">
         <v>2</v>
       </c>
       <c r="AE17" s="73" t="s">
         <v>316</v>
       </c>
-      <c r="AF17">
+      <c r="AF17" s="85">
         <v>1</v>
       </c>
       <c r="AT17" s="73" t="s">
-        <v>357</v>
-      </c>
-      <c r="AU17">
+        <v>445</v>
+      </c>
+      <c r="AU17" s="85">
         <v>1</v>
       </c>
     </row>
@@ -48361,19 +48452,19 @@
       <c r="Z18" s="73" t="s">
         <v>420</v>
       </c>
-      <c r="AA18">
+      <c r="AA18" s="85">
         <v>1</v>
       </c>
       <c r="AE18" s="73" t="s">
         <v>214</v>
       </c>
-      <c r="AF18">
+      <c r="AF18" s="85">
         <v>1</v>
       </c>
       <c r="AT18" s="73" t="s">
         <v>369</v>
       </c>
-      <c r="AU18">
+      <c r="AU18" s="85">
         <v>118</v>
       </c>
     </row>
@@ -48381,13 +48472,13 @@
       <c r="Z19" s="73" t="s">
         <v>212</v>
       </c>
-      <c r="AA19">
+      <c r="AA19" s="85">
         <v>1</v>
       </c>
       <c r="AE19" s="73" t="s">
         <v>418</v>
       </c>
-      <c r="AF19">
+      <c r="AF19" s="85">
         <v>1</v>
       </c>
     </row>
@@ -48395,29 +48486,29 @@
       <c r="Z20" s="73" t="s">
         <v>369</v>
       </c>
-      <c r="AA20">
+      <c r="AA20" s="85">
         <v>105</v>
       </c>
       <c r="AE20" s="73" t="s">
         <v>369</v>
       </c>
-      <c r="AF20">
+      <c r="AF20" s="85">
         <v>30</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:D5"/>
+    <mergeCell ref="F1:I5"/>
+    <mergeCell ref="K1:N5"/>
+    <mergeCell ref="P1:S5"/>
+    <mergeCell ref="U1:X5"/>
     <mergeCell ref="AY1:BB5"/>
     <mergeCell ref="Z1:AC5"/>
     <mergeCell ref="AE1:AH5"/>
     <mergeCell ref="AJ1:AM5"/>
     <mergeCell ref="AO1:AR5"/>
     <mergeCell ref="AT1:AW5"/>
-    <mergeCell ref="A1:D5"/>
-    <mergeCell ref="F1:I5"/>
-    <mergeCell ref="K1:N5"/>
-    <mergeCell ref="P1:S5"/>
-    <mergeCell ref="U1:X5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId12"/>
